--- a/revision_v3/human_eval/Gold_Test_Code_Review.xlsx
+++ b/revision_v3/human_eval/Gold_Test_Code_Review.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,8 +44,13 @@
       <name val="Consolas"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +81,16 @@
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF1FA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -89,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -125,6 +140,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -673,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y151"/>
+  <dimension ref="A1:AH151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -701,6 +722,15 @@
     <col width="45" customWidth="1" min="23" max="23"/>
     <col width="22" customWidth="1" min="24" max="24"/>
     <col width="45" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="80" customWidth="1" min="28" max="28"/>
+    <col width="18" customWidth="1" min="29" max="29"/>
+    <col width="80" customWidth="1" min="30" max="30"/>
+    <col width="80" customWidth="1" min="31" max="31"/>
+    <col width="60" customWidth="1" min="32" max="32"/>
+    <col width="50" customWidth="1" min="33" max="33"/>
+    <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -827,6 +857,51 @@
       <c r="Y1" s="5" t="inlineStr">
         <is>
           <t>final_rationale</t>
+        </is>
+      </c>
+      <c r="Z1" s="11" t="inlineStr">
+        <is>
+          <t>opus5_proposed_label</t>
+        </is>
+      </c>
+      <c r="AA1" s="11" t="inlineStr">
+        <is>
+          <t>opus5_confidence</t>
+        </is>
+      </c>
+      <c r="AB1" s="11" t="inlineStr">
+        <is>
+          <t>opus5_rationale</t>
+        </is>
+      </c>
+      <c r="AC1" s="11" t="inlineStr">
+        <is>
+          <t>source_static_analyzer_verdict</t>
+        </is>
+      </c>
+      <c r="AD1" s="11" t="inlineStr">
+        <is>
+          <t>source_static_analyzer_explanation</t>
+        </is>
+      </c>
+      <c r="AE1" s="11" t="inlineStr">
+        <is>
+          <t>opus5_relevant_code_summary</t>
+        </is>
+      </c>
+      <c r="AF1" s="11" t="inlineStr">
+        <is>
+          <t>guard_tracer_result</t>
+        </is>
+      </c>
+      <c r="AG1" s="11" t="inlineStr">
+        <is>
+          <t>project_and_onchain_evidence</t>
+        </is>
+      </c>
+      <c r="AH1" s="11" t="inlineStr">
+        <is>
+          <t>opus5_unresolved_questions</t>
         </is>
       </c>
     </row>
@@ -956,6 +1031,59 @@
       <c r="W2" s="6" t="inlineStr"/>
       <c r="X2" s="8" t="inlineStr"/>
       <c r="Y2" s="8" t="inlineStr"/>
+      <c r="Z2" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA2" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB2" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x7c332c84: CALL at pc=694 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC2" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD2" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 2 tuple(s) (enclosing function(s): fallback()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE2" s="12" t="inlineStr">
+        <is>
+          <t>3119-byte runtime on ethereum exposing 1 dispatched function(s): 0x7c332c84 Embedded strings mention: Safe.
+Concern(s) found: 0x7c332c84: CALL at pc=694 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call
+Instruction census (whole contract): ADDRESS×1, CALL×5, CALLER×1, SELFDESTRUCT×1, STATICCALL×4</t>
+        </is>
+      </c>
+      <c r="AF2" s="12" t="inlineStr">
+        <is>
+          <t>• 0x7c332c84: an unauthenticated path to a sensitive operation exists
+• COVERAGE GAP: the analysis never reached 3 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG2" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=3119 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 179, "address": "0xda5e1988097297dcdc1f90d4dfe7909e847cbef6"}]</t>
+        </is>
+      </c>
+      <c r="AH2" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [1294, 1676], 'SELFDESTRUCT': [3077]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
@@ -1083,6 +1211,59 @@
       <c r="W3" s="9" t="inlineStr"/>
       <c r="X3" s="8" t="inlineStr"/>
       <c r="Y3" s="8" t="inlineStr"/>
+      <c r="Z3" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA3" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB3" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x76f59d8b: msg.sender must equal the hardcoded address 0xe342b094d684e6d17ba127ae6eadf613de736554. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC3" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD3" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE3" s="12" t="inlineStr">
+        <is>
+          <t>3008-byte runtime on ethereum exposing 3 dispatched function(s): 0x76f59d8b, 0x773d5602, owner() Embedded strings mention: Executor, not authorized.
+Concern(s) found: 0x76f59d8b: msg.sender must equal the hardcoded address 0xe342b094d684e6d17ba127ae6eadf613de736554. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x76f59d8b: msg.sender must equal the hardcoded address 0xe342b094d684e6d17ba127ae6eadf613de736554. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×5, CALLER×3</t>
+        </is>
+      </c>
+      <c r="AF3" s="12" t="inlineStr">
+        <is>
+          <t>• 0x76f59d8b: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xe342b094d684e6d17ba127ae6eadf613de736554; hardcoded_address_check against 0xe342b094d684e6d17ba127ae6eadf613de736554
+• 0x773d5602: no sensitive operation reachable
+• owner(): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG3" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=3008 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH3" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1210,6 +1391,66 @@
       <c r="W4" s="6" t="inlineStr"/>
       <c r="X4" s="8" t="inlineStr"/>
       <c r="Y4" s="8" t="inlineStr"/>
+      <c r="Z4" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA4" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB4" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: sweepERC20(address): CALL at pc=1910 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC4" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD4" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE4" s="12" t="inlineStr">
+        <is>
+          <t>3249-byte runtime on ethereum exposing 9 dispatched function(s): tokensReceived(address,address,address,uint256,bytes,bytes), onERC721Received(address,address,uint256,bytes), transferEth(uint256), execute(address,uint256,bytes), onERC1155BatchReceived(address,address,uint256[],uint256[],bytes), sweepERC20(address), onERC1155Received(address,address,uint256,uint256,bytes), transferERC20(address,uint256), controller()
+Concern(s) found: sweepERC20(address): CALL at pc=1910 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; transferERC20(address,uint256): CALL at pc=1910 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; transferEth(uint256): CALL at pc=568 to 0xc5b9a29b9d3e60cc527bfd7ecc5e0985cee26d2f with value from calldata, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; execute(address,uint256,bytes): tx.origin must equal the hardcoded address 0xc5b9a29b9d3e60cc527bfd7ecc5e0985cee26d2f. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×4, CALL×6, CALLER×5, DELEGATECALL×1, ORIGIN×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF4" s="12" t="inlineStr">
+        <is>
+          <t>• tokensReceived(address,address,address,uint256,bytes,bytes): an unauthenticated path to a sensitive operation exists — check found: caller_check; caller_check [analysis incomplete for this function]
+• onERC721Received(address,address,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: caller_check; caller_check
+• transferEth(uint256): an unauthenticated path to a sensitive operation exists
+• execute(address,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xc5b9a29b9d3e60cc527bfd7ecc5e0985cee26d2f
+• onERC1155BatchReceived(address,address,uint256[],uint256[],bytes): every path to a sensitive operation passes an authorization check — check found: caller_check; caller_check
+• sweepERC20(address): an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• onERC1155Received(address,address,uint256,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: caller_check; caller_check
+• transferERC20(address,uint256): an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• controller(): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG4" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=3249 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH4" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: onERC721Received(address,address,uint256,bytes) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); onERC721Received(address,address,uint256,bytes) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); onERC1155BatchReceived(address,address,uint256[],uint256[],bytes) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); onERC1155BatchReceived(address,address,uint256[],uint256[],bytes) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); sensitive opcodes present in the bytecode that no traversal reached ({'DELEGATECALL': [3230]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: sweepERC20(address), tokensReceived(address,address,address,uint256,bytes,bytes), transferERC20(address,uint256); unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: tokensReceived(address,address,address,uint256,bytes,bytes) pc=1910 -&gt; unresolved (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -1337,6 +1578,61 @@
       <c r="W5" s="9" t="inlineStr"/>
       <c r="X5" s="8" t="inlineStr"/>
       <c r="Y5" s="8" t="inlineStr"/>
+      <c r="Z5" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA5" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB5" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: withdrawAllEther(): CALL at pc=860 to stored(sload) with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC5" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD5" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE5" s="12" t="inlineStr">
+        <is>
+          <t>1796-byte runtime on base exposing 3 dispatched function(s): withdrawToken(address,address,uint256), withdrawAllEther(), owner()
+Concern(s) found: withdrawAllEther(): CALL at pc=860 to stored(sload) with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 3}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx3 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×3</t>
+        </is>
+      </c>
+      <c r="AF5" s="12" t="inlineStr">
+        <is>
+          <t>• withdrawToken(address,address,uint256): no sensitive operation reachable
+• withdrawAllEther(): an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• owner(): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG5" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=1796 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 2, "n_writes": 0}]</t>
+        </is>
+      </c>
+      <c r="AH5" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [576]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1464,6 +1760,84 @@
       <c r="W6" s="6" t="inlineStr"/>
       <c r="X6" s="8" t="inlineStr"/>
       <c r="Y6" s="8" t="inlineStr"/>
+      <c r="Z6" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA6" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB6" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x5aaadaa5: CALL at pc=3709 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC6" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD6" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE6" s="12" t="inlineStr">
+        <is>
+          <t>8841-byte runtime on base exposing 27 dispatched function(s): 0x03f85793, destroyContract(), transferTokens(address), operators(address), emergencyWithdrawToken(address), 0x29cd3d04, 0x2c7bddf4, getTokenBalance(address), unpause(), 0x5aaadaa5
+Concern(s) found: 0x5aaadaa5: CALL at pc=3709 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0x29cd3d04: CALL at pc=1868 to stored(sload) with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; destroyContract(): msg.sender must equal the hardcoded address 0x0835001cec7823dfc41270ff0c6551c3f9422222. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; emergencyWithdrawToken(address): msg.sender must equal the hardcoded address 0x0835001cec7823dfc41270ff0c6551c3f9422222. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; unpause(): msg.sender must equal the hardcoded address 0x0835001cec7823dfc41270ff0c6551c3f9422222. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; emergencyWithdrawETH(): msg.sender must equal the hardcoded address 0x0835001cec7823dfc41270ff0c6551c3f9422222. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; pause(): msg.sender must equal the hardcoded address 0x0835001cec7823dfc41270ff0c6551c3f9422222. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; addOperator(address): msg.sender must equal the hardcoded address 0x0835001cec7823dfc41270ff0c6551c3f9422222. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; removeOperator(address): msg.sender must equal the hardcoded address 0x0835001cec7823dfc41270ff0c6551c3f9422222. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; setTargetAddress(address): msg.sender must equal the hardcoded address 0x0835001cec7823dfc41270ff0c6551c3f9422222. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; transferTokens(address): SSTORE to slot 0x0 at pc=2222 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; transferTokens(address): SSTORE to slot 0x0 at pc=2264 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x29cd3d04: SSTORE to slot 0x0 at pc=2860 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x2c7bddf4: SSTORE to slot 0x0 at pc=2900 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x2c7bddf4: SSTORE to slot 0x0 at pc=3004 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x5aaadaa5: SSTORE to slot 0x0 at pc=3388 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x74503517: SSTORE to slot 0x0 at pc=4218 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x74503517: SSTORE to slot 0x0 at pc=4319 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x8da137f5: SSTORE to slot 0x0 at pc=2264 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x8da137f5: SSTORE to slot 0x0 at pc=4798 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0xab7e4c70: SSTORE to slot 0x0 at pc=5158 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0xab7e4c70: SSTORE to slot 0x0 at pc=5204 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; executeCall(address,bytes): SSTORE to slot 0x0 at pc=5455 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; executeCall(address,bytes): SSTORE to slot 0x0 at pc=5500 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0xddd0fd06: SSTORE to slot 0x0 at pc=5605 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0xddd0fd06: SSTORE to slot 0x0 at pc=5649 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0xf4c306d0: SSTORE to slot 0x0 at pc=5204 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0xf4c306d0: SSTORE to slot 0x0 at pc=5753 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls
+Instruction census (whole contract): ADDRESS×19, CALL×8, CALLER×22, ORIGIN×12, SELFDESTRUCT×1, SSTORE×30, STATICCALL×5</t>
+        </is>
+      </c>
+      <c r="AF6" s="12" t="inlineStr">
+        <is>
+          <t>• 0x03f85793: no sensitive operation reachable
+• destroyContract(): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0835001cec7823dfc41270ff0c6551c3f9422222
+• transferTokens(address): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• operators(address): no sensitive operation reachable
+• emergencyWithdrawToken(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0835001cec7823dfc41270ff0c6551c3f9422222
+• 0x29cd3d04: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• 0x2c7bddf4: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• getTokenBalance(address): no sensitive operation reachable
+• unpause(): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0835001cec7823dfc41270ff0c6551c3f9422222
+• 0x5aaadaa5: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• paused(): no sensitive operation reachable
+• isOperator(address): no sensitive operation reachable — check found: storage_condition
+• getContractBalance(): no sensitive operation reachable
+• 0x74503517: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• 0x7c0c0743: no sensitive operation reachable
+• emergencyWithdrawETH(): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0835001cec7823dfc41270ff0c6551c3f9422222
+• pause(): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0835001cec7823dfc41270ff0c6551c3f9422222
+• getOwner(): no sensitive operation reachable
+• 0x8da137f5: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• addOperator(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0835001cec7823dfc41270ff0c6551c3f9422222
+• 0x9ac475cd: no sensitive operation reachable
+• 0xab7e4c70: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• removeOperator(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0835001cec7823dfc41270ff0c6551c3f9422222
+• executeCall(address,bytes): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• 0xddd0fd06: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• 0xf4c306d0: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• setTargetAddress(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0835001cec7823dfc41270ff0c6551c3f9422222</t>
+        </is>
+      </c>
+      <c r="AG6" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=8841 bytes
+verified source=True
+other chains with identical bytecode: ["base", "bnb", "polygon"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 13, "n_writes": 12}, {"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 20, "type": "uint8", "n_reads": 10, "n_writes": 10}, {"slot": "00000000</t>
+        </is>
+      </c>
+      <c r="AH6" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x5aaadaa5</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -1591,6 +1965,59 @@
       <c r="W7" s="9" t="inlineStr"/>
       <c r="X7" s="8" t="inlineStr"/>
       <c r="Y7" s="8" t="inlineStr"/>
+      <c r="Z7" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA7" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB7" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: destroyMe(): tx.origin must equal the hardcoded address 0xbe73ff07d6123a1f5110a16a11f95c21ce565827. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC7" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD7" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE7" s="12" t="inlineStr">
+        <is>
+          <t>2900-byte runtime on ethereum exposing 2 dispatched function(s): destroyMe(), aggregate((address,bytes)[]) Embedded strings mention: Multicall, not owner.
+Concern(s) found: destroyMe(): tx.origin must equal the hardcoded address 0xbe73ff07d6123a1f5110a16a11f95c21ce565827. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×1, CALL×3, CALLER×1, ORIGIN×2, SELFDESTRUCT×1</t>
+        </is>
+      </c>
+      <c r="AF7" s="12" t="inlineStr">
+        <is>
+          <t>• destroyMe(): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xbe73ff07d6123a1f5110a16a11f95c21ce565827
+• aggregate((address,bytes)[]): no sensitive operation reachable — check found: hardcoded_address_check against 0xbe73ff07d6123a1f5110a16a11f95c21ce565827 [analysis incomplete for this function]
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG7" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=2900 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH7" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [930]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: aggregate((address,bytes)[])</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1718,6 +2145,58 @@
       <c r="W8" s="6" t="inlineStr"/>
       <c r="X8" s="8" t="inlineStr"/>
       <c r="Y8" s="8" t="inlineStr"/>
+      <c r="Z8" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA8" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB8" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: withdraw(address,uint256): CALL at pc=478 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC8" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD8" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE8" s="12" t="inlineStr">
+        <is>
+          <t>1448-byte runtime on ethereum exposing 2 dispatched function(s): destination(), withdraw(address,uint256)
+Concern(s) found: withdraw(address,uint256): CALL at pc=478 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 2}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx2 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×2</t>
+        </is>
+      </c>
+      <c r="AF8" s="12" t="inlineStr">
+        <is>
+          <t>• destination(): no sensitive operation reachable
+• withdraw(address,uint256): an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG8" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=1448 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH8" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -1845,6 +2324,63 @@
       <c r="W9" s="9" t="inlineStr"/>
       <c r="X9" s="8" t="inlineStr"/>
       <c r="Y9" s="8" t="inlineStr"/>
+      <c r="Z9" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA9" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB9" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: withdrawERC721(address,uint256[]): CALL at pc=797 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC9" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD9" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE9" s="12" t="inlineStr">
+        <is>
+          <t>5301-byte runtime on ethereum exposing 6 dispatched function(s): withdrawERC721(address,uint256[]), execute(address,bytes), withdrawERC1155(address,uint256,uint256), 0x6ef42181, changeOwner(address), 0xdafd8013
+Concern(s) found: withdrawERC721(address,uint256[]): CALL at pc=797 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; withdrawERC1155(address,uint256,uint256): CALL at pc=1458 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0xdafd8013: CALL at pc=2806 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; execute(address,bytes): tx.origin must equal the hardcoded address 0x0bfb5ba84adb386083f3b782b2d926f8154f06c4. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x6ef42181: tx.origin must equal the hardcoded address 0x0bfb5ba84adb386083f3b782b2d926f8154f06c4. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; changeOwner(address): tx.origin must equal the hardcoded address 0x0bfb5ba84adb386083f3b782b2d926f8154f06c4. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×3, CALL×7, ORIGIN×3, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF9" s="12" t="inlineStr">
+        <is>
+          <t>• withdrawERC721(address,uint256[]): an unauthenticated path to a sensitive operation exists
+• execute(address,bytes): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0bfb5ba84adb386083f3b782b2d926f8154f06c4
+• withdrawERC1155(address,uint256,uint256): an unauthenticated path to a sensitive operation exists
+• 0x6ef42181: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0bfb5ba84adb386083f3b782b2d926f8154f06c4
+• changeOwner(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0bfb5ba84adb386083f3b782b2d926f8154f06c4
+• 0xdafd8013: an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG9" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=5301 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 107, "address": "0x0bfb5ba84adb386083f3b782b2d926f8154f06c4"}]</t>
+        </is>
+      </c>
+      <c r="AH9" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -1972,6 +2508,58 @@
       <c r="W10" s="6" t="inlineStr"/>
       <c r="X10" s="8" t="inlineStr"/>
       <c r="Y10" s="8" t="inlineStr"/>
+      <c r="Z10" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA10" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB10" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: setup(address[],uint256,address,bytes,address,address,uint256,address): DELEGATECALL at pc=435 to 0xcfaa26ad40bfc7e3b1642e1888620fc402b95dab reachable with no authorization branch — third-party code would execute against the EOA's own storage The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC10" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD10" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): fallback()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE10" s="12" t="inlineStr">
+        <is>
+          <t>889-byte runtime on optimism exposing 1 dispatched function(s): setup(address[],uint256,address,bytes,address,address,uint256,address)
+Concern(s) found: setup(address[],uint256,address,bytes,address,address,uint256,address): DELEGATECALL at pc=435 to 0xcfaa26ad40bfc7e3b1642e1888620fc402b95dab reachable with no authorization branch — third-party code would execute against the EOA's own storage; setup(address[],uint256,address,bytes,address,address,uint256,address): SSTORE to slot 0x0 at pc=421 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'DELEGATECALL': 2, 'SSTORE': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — DELEGATECALLx2 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): DELEGATECALL×2, SSTORE×1</t>
+        </is>
+      </c>
+      <c r="AF10" s="12" t="inlineStr">
+        <is>
+          <t>• setup(address[],uint256,address,bytes,address,address,uint256,address): an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG10" s="12" t="inlineStr">
+        <is>
+          <t>chain=optimism
+runtime size=889 bytes
+verified source=False
+other chains with identical bytecode: ["optimism"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "uint256", "n_reads": 0, "n_writes": 0}]</t>
+        </is>
+      </c>
+      <c r="AH10" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -2099,6 +2687,57 @@
       <c r="W11" s="9" t="inlineStr"/>
       <c r="X11" s="8" t="inlineStr"/>
       <c r="Y11" s="8" t="inlineStr"/>
+      <c r="Z11" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA11" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB11" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: every dispatched function analysed to completion with no reachable sensitive operation. The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC11" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD11" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE11" s="12" t="inlineStr">
+        <is>
+          <t>811-byte runtime on base exposing 1 dispatched function(s): OWNER()
+Instruction census (whole contract): CALL×2, CALLER×1</t>
+        </is>
+      </c>
+      <c r="AF11" s="12" t="inlineStr">
+        <is>
+          <t>• OWNER(): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG11" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=811 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+addresses embedded in the code: [{"bytecode_offset": 40, "address": "0x42cbb8ef996f83710c3d6169f4b3b4b70ed1971b"}]</t>
+        </is>
+      </c>
+      <c r="AH11" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -2226,6 +2865,61 @@
       <c r="W12" s="6" t="inlineStr"/>
       <c r="X12" s="8" t="inlineStr"/>
       <c r="Y12" s="8" t="inlineStr"/>
+      <c r="Z12" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA12" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB12" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: every dispatched function analysed to completion with no reachable sensitive operation. The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC12" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD12" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 2 tuple(s) (enclosing function(s): fallback()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE12" s="12" t="inlineStr">
+        <is>
+          <t>1035-byte runtime on ethereum exposing 5 dispatched function(s): proxyType(), isDepositable(), implementation(), appId(), kernel()
+Instruction census (whole contract): CALL×1, CALLER×1, DELEGATECALL×1, SSTORE×2</t>
+        </is>
+      </c>
+      <c r="AF12" s="12" t="inlineStr">
+        <is>
+          <t>• proxyType(): no sensitive operation reachable
+• isDepositable(): no sensitive operation reachable
+• implementation(): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• appId(): no sensitive operation reachable
+• kernel(): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG12" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=1035 bytes
+verified source=True
+other chains with identical bytecode: ["ethereum"]
+on-chain storage read during evidence collection: [{"slot": "4172f0f7d2289153072b0a6ca36959e0cbe2efc3afe50fc81636caa96338137b", "offset": 0, "type": "address", "n_reads": 2, "n_writes": 0}, {"slot": "665fd576fbbe6f247aff98f5c94a561e3f71ec2d3c988d56f12d342396c50cea", "offset": 0, "type": "bool", "n_reads": 1, "n_writes": 0}, {"slot": "d625496217aa6a</t>
+        </is>
+      </c>
+      <c r="AH12" s="12" t="inlineStr">
+        <is>
+          <t>unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: implementation() pc=870 -&gt; stored(sload) (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -2353,6 +3047,58 @@
       <c r="W13" s="9" t="inlineStr"/>
       <c r="X13" s="8" t="inlineStr"/>
       <c r="Y13" s="8" t="inlineStr"/>
+      <c r="Z13" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA13" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB13" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x87614bb9: msg.sender must equal the hardcoded address 0x000085bad5b016e5448a530cb3d4840d2cfd15bc. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC13" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD13" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE13" s="12" t="inlineStr">
+        <is>
+          <t>2774-byte runtime on ethereum exposing 2 dispatched function(s): 0x87614bb9, owner() Embedded strings mention: Multicall.
+Concern(s) found: 0x87614bb9: msg.sender must equal the hardcoded address 0x000085bad5b016e5448a530cb3d4840d2cfd15bc. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×3, CALLER×2, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF13" s="12" t="inlineStr">
+        <is>
+          <t>• 0x87614bb9: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x000085bad5b016e5448a530cb3d4840d2cfd15bc
+• owner(): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG13" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=2774 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH13" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -2480,6 +3226,66 @@
       <c r="W14" s="6" t="inlineStr"/>
       <c r="X14" s="8" t="inlineStr"/>
       <c r="Y14" s="8" t="inlineStr"/>
+      <c r="Z14" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA14" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB14" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: setDestination(address): tx.origin must equal the hardcoded address 0x59987dc305076a6043504916ef9d655583f7e0a0. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC14" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD14" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE14" s="12" t="inlineStr">
+        <is>
+          <t>5269-byte runtime on bnb exposing 7 dispatched function(s): setDestination(address), 0x2c1315e4, execute(address[],uint256[],bytes[]), 0xaee6ac73, destination(), 0xbf7c6576, 0xee179dbd
+Concern(s) found: setDestination(address): tx.origin must equal the hardcoded address 0x59987dc305076a6043504916ef9d655583f7e0a0. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x2c1315e4: tx.origin must equal the hardcoded address 0x59987dc305076a6043504916ef9d655583f7e0a0. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; execute(address[],uint256[],bytes[]): tx.origin must equal the hardcoded address 0x59987dc305076a6043504916ef9d655583f7e0a0. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0xbf7c6576: tx.origin must equal the hardcoded address 0x59987dc305076a6043504916ef9d655583f7e0a0. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×2, CALL×6, ORIGIN×6, SSTORE×1, STATICCALL×2</t>
+        </is>
+      </c>
+      <c r="AF14" s="12" t="inlineStr">
+        <is>
+          <t>• setDestination(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x59987dc305076a6043504916ef9d655583f7e0a0
+• 0x2c1315e4: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x59987dc305076a6043504916ef9d655583f7e0a0; storage_condition
+• execute(address[],uint256[],bytes[]): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x59987dc305076a6043504916ef9d655583f7e0a0
+• 0xaee6ac73: no sensitive operation reachable
+• destination(): no sensitive operation reachable
+• 0xbf7c6576: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x59987dc305076a6043504916ef9d655583f7e0a0
+• 0xee179dbd: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG14" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=5269 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 2, "n_writes": 1}]
+addresses embedded in the code: [{"bytecode_offset": 624, "address": "0x59987dc305076a6043504916ef9d655583f7e0a0"}]</t>
+        </is>
+      </c>
+      <c r="AH14" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: 0x2c1315e4 (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); 0x2c1315e4 (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [2263, 3192]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -2607,6 +3413,68 @@
       <c r="W15" s="9" t="inlineStr"/>
       <c r="X15" s="8" t="inlineStr"/>
       <c r="Y15" s="8" t="inlineStr"/>
+      <c r="Z15" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA15" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB15" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: rescue(): CALL at pc=4425 to unresolved with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time The source static analyzer's verdict was assessed as PARTIALLY_CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC15" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed PARTIALLY_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD15" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The reachability the rule asserts is reproduced (an external call is reachable from receive()/fallback()), but every such path passes an authorization branch. The rule is correct about capability and silent about authorization, which is its documented limitation — it has no guard predicate. This is capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
+      <c r="AE15" s="12" t="inlineStr">
+        <is>
+          <t>8059-byte runtime on ethereum exposing 10 dispatched function(s): 0x0ce66fc4, rescue(), 0x45407d71, rescue(uint256), revoke(address), 0x793d70f6, owner(), 0xb67b62b9, 0xb9b79301, 0xcd7e8be1
+Concern(s) found: rescue(): CALL at pc=4425 to unresolved with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; 0x45407d71: CALL at pc=4425 to unresolved with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; rescue(uint256): CALL at pc=4425 to unresolved with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time
+Instruction census (whole contract): ADDRESS×5, CALL×8, ORIGIN×3, STATICCALL×4</t>
+        </is>
+      </c>
+      <c r="AF15" s="12" t="inlineStr">
+        <is>
+          <t>• 0x0ce66fc4: no sensitive operation reachable
+• rescue(): an unauthenticated path to a sensitive operation exists
+• 0x45407d71: an unauthenticated path to a sensitive operation exists
+• rescue(uint256): an unauthenticated path to a sensitive operation exists
+• revoke(address): an unauthenticated path to a sensitive operation exists
+• 0x793d70f6: no sensitive operation reachable
+• owner(): no sensitive operation reachable
+• 0xb67b62b9: no sensitive operation reachable
+• 0xb9b79301: no sensitive operation reachable
+• 0xcd7e8be1: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 5 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG15" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=8059 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 2529, "address": "0xc02aaa39b223fe8d0a0e5c4f27ead9083c756cc2"}, {"bytecode_offset": 2553, "address": "0xe592427a0aece92de3edee1f18e0157c05861564"}, {"bytecode_offset": 7836, "address": "0x6665727265643e3e20526573637565466c617368"}, {"bytecode_offset": 7883, "address": "0x7761702</t>
+        </is>
+      </c>
+      <c r="AH15" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [2130, 2380, 2679, 3136]}) — capability here is a lower bound; unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: rescue() pc=1240 -&gt; 0x8be3460a480c80728a8c4d7a5d5303c85ba7b3b9 (value=0, data=memory); rescue(uint256) pc=1240 -&gt; 0x8be3460a480c80728a8c4d7a5d5303c85ba7b3b9 (value=0, data=memory); revoke(address) pc=4142 -&gt; 0x57e114b691db790c35207b2e685d4a43181e6061 (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -2734,6 +3602,59 @@
       <c r="W16" s="6" t="inlineStr"/>
       <c r="X16" s="8" t="inlineStr"/>
       <c r="Y16" s="8" t="inlineStr"/>
+      <c r="Z16" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA16" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB16" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x83347b37: CALL at pc=459 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as PARTIALLY_CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC16" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed PARTIALLY_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD16" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The reachability the rule asserts is reproduced (an external call is reachable from receive()/fallback()), but every such path passes an authorization branch. The rule is correct about capability and silent about authorization, which is its documented limitation — it has no guard predicate. This is capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
+      <c r="AE16" s="12" t="inlineStr">
+        <is>
+          <t>1172-byte runtime on base exposing 1 dispatched function(s): 0x83347b37
+Concern(s) found: 0x83347b37: CALL at pc=459 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call
+Instruction census (whole contract): ADDRESS×1, CALL×2, CALLER×2, CREATE2×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF16" s="12" t="inlineStr">
+        <is>
+          <t>• 0x83347b37: an unauthenticated path to a sensitive operation exists
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG16" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=1172 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+addresses embedded in the code: [{"bytecode_offset": 39, "address": "0xea459dde8dd4e1b28324ff1a1dcffedfec596db0"}]</t>
+        </is>
+      </c>
+      <c r="AH16" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CREATE2': [1133]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
@@ -2861,6 +3782,62 @@
       <c r="W17" s="9" t="inlineStr"/>
       <c r="X17" s="8" t="inlineStr"/>
       <c r="Y17" s="8" t="inlineStr"/>
+      <c r="Z17" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA17" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB17" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: destroyMe(): tx.origin must equal the hardcoded address 0x748e7f663fb13aa8607c22bb9d35d4c3f05277ff. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC17" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD17" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE17" s="12" t="inlineStr">
+        <is>
+          <t>7042-byte runtime on base exposing 5 dispatched function(s): destroyMe(), 0x286aefc7, 0x476fa0be, 0x584a5920, 0xedaeed51 Embedded strings mention: Safe, not owner.
+Concern(s) found: destroyMe(): tx.origin must equal the hardcoded address 0x748e7f663fb13aa8607c22bb9d35d4c3f05277ff. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x476fa0be: tx.origin must equal the hardcoded address 0x748e7f663fb13aa8607c22bb9d35d4c3f05277ff. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x584a5920: tx.origin must equal the hardcoded address 0x748e7f663fb13aa8607c22bb9d35d4c3f05277ff. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0xedaeed51: tx.origin must equal the hardcoded address 0x748e7f663fb13aa8607c22bb9d35d4c3f05277ff. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×5, CALL×6, CALLER×1, ORIGIN×5, SELFDESTRUCT×1, STATICCALL×3</t>
+        </is>
+      </c>
+      <c r="AF17" s="12" t="inlineStr">
+        <is>
+          <t>• destroyMe(): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x748e7f663fb13aa8607c22bb9d35d4c3f05277ff
+• 0x286aefc7: no sensitive operation reachable — check found: hardcoded_address_check against 0x748e7f663fb13aa8607c22bb9d35d4c3f05277ff [analysis incomplete for this function]
+• 0x476fa0be: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x748e7f663fb13aa8607c22bb9d35d4c3f05277ff
+• 0x584a5920: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x748e7f663fb13aa8607c22bb9d35d4c3f05277ff
+• 0xedaeed51: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x748e7f663fb13aa8607c22bb9d35d4c3f05277ff [analysis incomplete for this function]
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG17" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=7042 bytes
+verified source=False
+other chains with identical bytecode: ["base"]</t>
+        </is>
+      </c>
+      <c r="AH17" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [1086]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x286aefc7, 0xedaeed51</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -2988,6 +3965,59 @@
       <c r="W18" s="6" t="inlineStr"/>
       <c r="X18" s="8" t="inlineStr"/>
       <c r="Y18" s="8" t="inlineStr"/>
+      <c r="Z18" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA18" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB18" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: transfer(address,uint256): CALL at pc=441 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC18" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD18" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE18" s="12" t="inlineStr">
+        <is>
+          <t>1277-byte runtime on ethereum exposing 2 dispatched function(s): transfer(address,uint256), destination()
+Concern(s) found: transfer(address,uint256): CALL at pc=441 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call
+Instruction census (whole contract): CALL×2, CALLCODE×1, ORIGIN×1</t>
+        </is>
+      </c>
+      <c r="AF18" s="12" t="inlineStr">
+        <is>
+          <t>• transfer(address,uint256): an unauthenticated path to a sensitive operation exists
+• destination(): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG18" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=1277 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH18" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALLCODE': [1248]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
@@ -3115,6 +4145,64 @@
       <c r="W19" s="9" t="inlineStr"/>
       <c r="X19" s="8" t="inlineStr"/>
       <c r="Y19" s="8" t="inlineStr"/>
+      <c r="Z19" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA19" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB19" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x6be4f47f: msg.sender must equal the hardcoded address 0x3e577385fe768238d525b04cb25fae7c0e700000. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as PARTIALLY_CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC19" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed PARTIALLY_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD19" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The reachability the rule asserts is reproduced (an external call is reachable from receive()/fallback()), but every such path passes an authorization branch. The rule is correct about capability and silent about authorization, which is its documented limitation — it has no guard predicate. This is capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
+      <c r="AE19" s="12" t="inlineStr">
+        <is>
+          <t>2681-byte runtime on bnb exposing 5 dispatched function(s): 0x6be4f47f, 0x7a141f91, 0x92dabebb, isUserBlocked(address), 0xfb0404aa
+Concern(s) found: 0x6be4f47f: msg.sender must equal the hardcoded address 0x3e577385fe768238d525b04cb25fae7c0e700000. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x92dabebb: msg.sender must equal the hardcoded address 0x3e577385fe768238d525b04cb25fae7c0e700000. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0xfb0404aa: msg.sender must equal the hardcoded address 0x3e577385fe768238d525b04cb25fae7c0e700000. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×6, CALL×3, CALLER×8, DELEGATECALL×1, ORIGIN×2, SSTORE×2, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF19" s="12" t="inlineStr">
+        <is>
+          <t>• 0x6be4f47f: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x3e577385fe768238d525b04cb25fae7c0e700000 [analysis incomplete for this function]
+• 0x7a141f91: no sensitive operation reachable
+• 0x92dabebb: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x3e577385fe768238d525b04cb25fae7c0e700000
+• isUserBlocked(address): no sensitive operation reachable
+• 0xfb0404aa: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x3e577385fe768238d525b04cb25fae7c0e700000
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG19" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=2681 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "mapping(address =&gt; bool)", "n_reads": 1, "n_writes": 1}]
+addresses embedded in the code: [{"bytecode_offset": 308, "address": "0xd58fd9ccad6fdd0c3843d2fb70654a511becc5ea"}, {"bytecode_offset": 379, "address": "0x4791eb2224d272655e8d5da171bb07dd5a805ff6"}, {"bytecode_offset": 451, "address": "0xec10779407fb81cbf900b56398a8f31757b6a7cd"}, {"bytecode_offset": 523, "address": "0x6153884b6e5</t>
+        </is>
+      </c>
+      <c r="AH19" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'DELEGATECALL': [2650]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x6be4f47f</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -3242,6 +4330,62 @@
       <c r="W20" s="6" t="inlineStr"/>
       <c r="X20" s="8" t="inlineStr"/>
       <c r="Y20" s="8" t="inlineStr"/>
+      <c r="Z20" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA20" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB20" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: transferTokens(address): CALL at pc=2306 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC20" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD20" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE20" s="12" t="inlineStr">
+        <is>
+          <t>4328-byte runtime on base exposing 5 dispatched function(s): transferTokens(address), 0x29cd3d04, 0x2c7bddf4, 0xab7e4c70, executeCall(address,bytes) Embedded strings mention: ReentrancyGuard.
+Concern(s) found: transferTokens(address): CALL at pc=2306 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0xab7e4c70: CALL at pc=1514 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; executeCall(address,bytes): CALL at pc=2479 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0x2c7bddf4: CALL at pc=1058 to 0xd0e49dec126d0ac848389843917c5204aa2be5c2 with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; transferTokens(address): SSTORE to slot 0x0 at pc=610 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; transferTokens(address): SSTORE to slot 0x0 at pc=643 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x29cd3d04: SSTORE to slot 0x0 at pc=748 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x29cd3d04: SSTORE to slot 0x0 at pc=780 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x2c7bddf4: SSTORE to slot 0x0 at pc=884 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x2c7bddf4: SSTORE to slot 0x0 at pc=1198 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0xab7e4c70: SSTORE to slot 0x0 at pc=1302 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0xab7e4c70: SSTORE to slot 0x0 at pc=1749 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; executeCall(address,bytes): SSTORE to slot 0x0 at pc=1857 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; executeCall(address,bytes): SSTORE to slot 0x0 at pc=1900 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls
+Instruction census (whole contract): ADDRESS×1, CALL×5, CALLER×1, SSTORE×10, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF20" s="12" t="inlineStr">
+        <is>
+          <t>• transferTokens(address): an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• 0x29cd3d04: an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• 0x2c7bddf4: an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• 0xab7e4c70: an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• executeCall(address,bytes): an unauthenticated path to a sensitive operation exists — check found: storage_condition</t>
+        </is>
+      </c>
+      <c r="AG20" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=4328 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "uint8", "n_reads": 5, "n_writes": 5}]</t>
+        </is>
+      </c>
+      <c r="AH20" s="12" t="inlineStr">
+        <is>
+          <t>unauthenticated call(s) forwarding only msg.value to a fixed destination ([('0x29cd3d04', 391, '0xd0e49dec126d0ac848389843917c5204aa2be5c2'), ('0xab7e4c70', 391, '0xd0e49dec126d0ac848389843917c5204aa2be5c2'), ('executeCall(address,bytes)', 391, '0xd0e49dec126d0ac848389843917c5204aa2be5c2')]) — a caller can only donate their own ETH, so this is not by itself a path to the account's assets</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
@@ -3369,6 +4513,60 @@
       <c r="W21" s="9" t="inlineStr"/>
       <c r="X21" s="8" t="inlineStr"/>
       <c r="Y21" s="8" t="inlineStr"/>
+      <c r="Z21" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA21" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB21" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x3cc85aee: msg.sender must equal the hardcoded address 0x16d502b1e018f88f372c4633c449a4d0c6e51a26. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as PARTIALLY_CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC21" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed PARTIALLY_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD21" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The reachability the rule asserts is reproduced (an external call is reachable from receive()/fallback()), but every such path passes an authorization branch. The rule is correct about capability and silent about authorization, which is its documented limitation — it has no guard predicate. This is capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
+      <c r="AE21" s="12" t="inlineStr">
+        <is>
+          <t>5140-byte runtime on base exposing 4 dispatched function(s): 0x3cc85aee, noop(), 0x773d5602, owner() Embedded strings mention: Executor, not authorized.
+Concern(s) found: 0x3cc85aee: msg.sender must equal the hardcoded address 0x16d502b1e018f88f372c4633c449a4d0c6e51a26. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x3cc85aee: msg.sender must equal the hardcoded address 0x16d502b1e018f88f372c4633c449a4d0c6e51a26. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×2, CALL×4, CALLER×4</t>
+        </is>
+      </c>
+      <c r="AF21" s="12" t="inlineStr">
+        <is>
+          <t>• 0x3cc85aee: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x16d502b1e018f88f372c4633c449a4d0c6e51a26; hardcoded_address_check against 0x16d502b1e018f88f372c4633c449a4d0c6e51a26
+• noop(): no sensitive operation reachable
+• 0x773d5602: no sensitive operation reachable
+• owner(): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG21" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=5140 bytes
+verified source=False
+other chains with identical bytecode: ["base"]</t>
+        </is>
+      </c>
+      <c r="AH21" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -3496,6 +4694,58 @@
       <c r="W22" s="6" t="inlineStr"/>
       <c r="X22" s="8" t="inlineStr"/>
       <c r="Y22" s="8" t="inlineStr"/>
+      <c r="Z22" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA22" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB22" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: setup(address[],uint256,address,bytes,address,address,uint256,address): DELEGATECALL at pc=435 to 0xcfaa26ad40bfc7e3b1642e1888620fc402b95dab reachable with no authorization branch — third-party code would execute against the EOA's own storage The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC22" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD22" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): fallback()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE22" s="12" t="inlineStr">
+        <is>
+          <t>889-byte runtime on optimism exposing 1 dispatched function(s): setup(address[],uint256,address,bytes,address,address,uint256,address)
+Concern(s) found: setup(address[],uint256,address,bytes,address,address,uint256,address): DELEGATECALL at pc=435 to 0xcfaa26ad40bfc7e3b1642e1888620fc402b95dab reachable with no authorization branch — third-party code would execute against the EOA's own storage; setup(address[],uint256,address,bytes,address,address,uint256,address): SSTORE to slot 0x0 at pc=421 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'DELEGATECALL': 2, 'SSTORE': 1, 'STATICCALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — DELEGATECALLx2 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): DELEGATECALL×2, SSTORE×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF22" s="12" t="inlineStr">
+        <is>
+          <t>• setup(address[],uint256,address,bytes,address,address,uint256,address): an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG22" s="12" t="inlineStr">
+        <is>
+          <t>chain=optimism
+runtime size=889 bytes
+verified source=False
+other chains with identical bytecode: ["optimism"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "uint256", "n_reads": 0, "n_writes": 0}]</t>
+        </is>
+      </c>
+      <c r="AH22" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
@@ -3623,6 +4873,63 @@
       <c r="W23" s="9" t="inlineStr"/>
       <c r="X23" s="8" t="inlineStr"/>
       <c r="Y23" s="8" t="inlineStr"/>
+      <c r="Z23" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA23" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB23" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: multicall(address[],bytes[]): CALL at pc=1102 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC23" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD23" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE23" s="12" t="inlineStr">
+        <is>
+          <t>3838-byte runtime on arbitrum exposing 7 dispatched function(s): destroyContract(), multicall(address[],bytes[]), recipient(), 0x8b7228a6, sweepETH(uint256), executeCall(address,bytes), sweepTokens(address)
+Concern(s) found: multicall(address[],bytes[]): CALL at pc=1102 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; executeCall(address,bytes): CALL at pc=1420 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; sweepTokens(address): CALL at pc=1878 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; multicall(address[],bytes[]): CALL at pc=522 to 0xa21ce0ed08355a17d864670b86edee33f0fd026c with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; 0x8b7228a6: CALL at pc=522 to 0xa21ce0ed08355a17d864670b86edee33f0fd026c with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; sweepETH(uint256): CALL at pc=522 to 0xa21ce0ed08355a17d864670b86edee33f0fd026c with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; executeCall(address,bytes): CALL at pc=522 to 0xa21ce0ed08355a17d864670b86edee33f0fd026c with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; destroyContract(): msg.sender must equal the hardcoded address 0xa21ce0ed08355a17d864670b86edee33f0fd026c. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×1, CALL×4, CALLER×2, SELFDESTRUCT×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF23" s="12" t="inlineStr">
+        <is>
+          <t>• destroyContract(): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xa21ce0ed08355a17d864670b86edee33f0fd026c
+• multicall(address[],bytes[]): an unauthenticated path to a sensitive operation exists
+• recipient(): no sensitive operation reachable
+• 0x8b7228a6: an unauthenticated path to a sensitive operation exists
+• sweepETH(uint256): an unauthenticated path to a sensitive operation exists
+• executeCall(address,bytes): an unauthenticated path to a sensitive operation exists
+• sweepTokens(address): an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG23" s="12" t="inlineStr">
+        <is>
+          <t>chain=arbitrum
+runtime size=3838 bytes
+verified source=False
+other chains with identical bytecode: ["arbitrum", "ethereum", "polygon"]</t>
+        </is>
+      </c>
+      <c r="AH23" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -3750,6 +5057,63 @@
       <c r="W24" s="6" t="inlineStr"/>
       <c r="X24" s="8" t="inlineStr"/>
       <c r="Y24" s="8" t="inlineStr"/>
+      <c r="Z24" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA24" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB24" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: sweep(address[]): CALL at pc=1816 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC24" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD24" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE24" s="12" t="inlineStr">
+        <is>
+          <t>4821-byte runtime on ethereum exposing 5 dispatched function(s): 0x3f7e82d6, multicall(address[],uint256[],bytes[]), sweep(address[]), execute(address,uint256,bytes), receiver()
+Concern(s) found: sweep(address[]): CALL at pc=1816 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; multicall(address[],uint256[],bytes[]): msg.sender must equal the hardcoded address 0x8e3019679f45c933d11f4b7ba99d5bdeb4de6bfe. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; execute(address,uint256,bytes): msg.sender must equal the hardcoded address 0x8e3019679f45c933d11f4b7ba99d5bdeb4de6bfe. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×1, CALL×5, CALLER×3, CREATE×1, CREATE2×1, SSTORE×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF24" s="12" t="inlineStr">
+        <is>
+          <t>• 0x3f7e82d6: an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• multicall(address[],uint256[],bytes[]): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x8e3019679f45c933d11f4b7ba99d5bdeb4de6bfe
+• sweep(address[]): an unauthenticated path to a sensitive operation exists
+• execute(address,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x8e3019679f45c933d11f4b7ba99d5bdeb4de6bfe
+• receiver(): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG24" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=4821 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 4364, "address": "0xb3663df137cffb7680f9edcd0144bb3f9b5d48a4"}]</t>
+        </is>
+      </c>
+      <c r="AH24" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [4599], 'CREATE2': [4793]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x3f7e82d6; unrestricted CREATE/CREATE2 at [('0x3f7e82d6', 578)] — a capability whose concrete risk depends on what the created contract is given authority over, which bytecode alone does not establish</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
@@ -3877,6 +5241,58 @@
       <c r="W25" s="9" t="inlineStr"/>
       <c r="X25" s="8" t="inlineStr"/>
       <c r="Y25" s="8" t="inlineStr"/>
+      <c r="Z25" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA25" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB25" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: setup(address[],uint256,address,bytes,address,address,uint256,address): DELEGATECALL at pc=435 to 0xcfaa26ad40bfc7e3b1642e1888620fc402b95dab reachable with no authorization branch — third-party code would execute against the EOA's own storage The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC25" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD25" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): fallback()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE25" s="12" t="inlineStr">
+        <is>
+          <t>889-byte runtime on optimism exposing 1 dispatched function(s): setup(address[],uint256,address,bytes,address,address,uint256,address)
+Concern(s) found: setup(address[],uint256,address,bytes,address,address,uint256,address): DELEGATECALL at pc=435 to 0xcfaa26ad40bfc7e3b1642e1888620fc402b95dab reachable with no authorization branch — third-party code would execute against the EOA's own storage; setup(address[],uint256,address,bytes,address,address,uint256,address): SSTORE to slot 0x0 at pc=421 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'DELEGATECALL': 2, 'SSTORE': 1, 'STATICCALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — DELEGATECALLx2 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): DELEGATECALL×2, SSTORE×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF25" s="12" t="inlineStr">
+        <is>
+          <t>• setup(address[],uint256,address,bytes,address,address,uint256,address): an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG25" s="12" t="inlineStr">
+        <is>
+          <t>chain=optimism
+runtime size=889 bytes
+verified source=False
+other chains with identical bytecode: ["optimism"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "uint256", "n_reads": 0, "n_writes": 0}]</t>
+        </is>
+      </c>
+      <c r="AH25" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -4004,6 +5420,60 @@
       <c r="W26" s="6" t="inlineStr"/>
       <c r="X26" s="8" t="inlineStr"/>
       <c r="Y26" s="8" t="inlineStr"/>
+      <c r="Z26" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA26" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB26" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: withdrawToken(address,uint256): CALL at pc=801 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC26" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD26" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE26" s="12" t="inlineStr">
+        <is>
+          <t>1855-byte runtime on base exposing 3 dispatched function(s): withdrawAllEther(), owner(), withdrawToken(address,uint256)
+Concern(s) found: withdrawToken(address,uint256): CALL at pc=801 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; withdrawAllEther(): CALL at pc=538 to stored(sload) with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 3}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx3 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×3</t>
+        </is>
+      </c>
+      <c r="AF26" s="12" t="inlineStr">
+        <is>
+          <t>• withdrawAllEther(): an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• owner(): no sensitive operation reachable
+• withdrawToken(address,uint256): an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG26" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=1855 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 3, "n_writes": 0}]</t>
+        </is>
+      </c>
+      <c r="AH26" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
@@ -4131,6 +5601,58 @@
       <c r="W27" s="9" t="inlineStr"/>
       <c r="X27" s="8" t="inlineStr"/>
       <c r="Y27" s="8" t="inlineStr"/>
+      <c r="Z27" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA27" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB27" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: withdraw(address,uint256): CALL at pc=478 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC27" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD27" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE27" s="12" t="inlineStr">
+        <is>
+          <t>1448-byte runtime on ethereum exposing 2 dispatched function(s): destination(), withdraw(address,uint256)
+Concern(s) found: withdraw(address,uint256): CALL at pc=478 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 2}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx2 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×2</t>
+        </is>
+      </c>
+      <c r="AF27" s="12" t="inlineStr">
+        <is>
+          <t>• destination(): no sensitive operation reachable
+• withdraw(address,uint256): an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG27" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=1448 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH27" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -4258,6 +5780,62 @@
       <c r="W28" s="6" t="inlineStr"/>
       <c r="X28" s="8" t="inlineStr"/>
       <c r="Y28" s="8" t="inlineStr"/>
+      <c r="Z28" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA28" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB28" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: transferTokens(address): CALL at pc=1976 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC28" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD28" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE28" s="12" t="inlineStr">
+        <is>
+          <t>4893-byte runtime on base exposing 4 dispatched function(s): transferTokens(address), 0x29cd3d04, 0x535089e7, executeCall(address,bytes) Embedded strings mention: ReentrancyGuard, Signed Message.
+Concern(s) found: transferTokens(address): CALL at pc=1976 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; executeCall(address,bytes): CALL at pc=2443 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; transferTokens(address): SSTORE to slot 0x0 at pc=589 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; transferTokens(address): SSTORE to slot 0x0 at pc=630 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x29cd3d04: SSTORE to slot 0x0 at pc=735 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x29cd3d04: SSTORE to slot 0x0 at pc=767 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x535089e7: SSTORE to slot 0x0 at pc=871 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; executeCall(address,bytes): SSTORE to slot 0x0 at pc=1527 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; executeCall(address,bytes): SSTORE to slot 0x0 at pc=1570 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls
+Protection(s) found: signature-derived authorization branch (ecrecover) on 0x535089e7
+Instruction census (whole contract): ADDRESS×1, CALL×4, CALLER×1, SSTORE×8, STATICCALL×2</t>
+        </is>
+      </c>
+      <c r="AF28" s="12" t="inlineStr">
+        <is>
+          <t>• transferTokens(address): an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• 0x29cd3d04: an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• 0x535089e7: an unauthenticated path to a sensitive operation exists — check found: storage_condition; signature_authorization
+• executeCall(address,bytes): an unauthenticated path to a sensitive operation exists — check found: storage_condition</t>
+        </is>
+      </c>
+      <c r="AG28" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=4893 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "uint8", "n_reads": 4, "n_writes": 4}]</t>
+        </is>
+      </c>
+      <c r="AH28" s="12" t="inlineStr">
+        <is>
+          <t>unauthenticated call(s) forwarding only msg.value to a fixed destination ([('transferTokens(address)', 370, '0xd0e49dec126d0ac848389843917c5204aa2be5c2'), ('0x29cd3d04', 370, '0xd0e49dec126d0ac848389843917c5204aa2be5c2'), ('executeCall(address,bytes)', 370, '0xd0e49dec126d0ac848389843917c5204aa2be5c2')]) — a caller can only donate their own ETH, so this is not by itself a path to the account's assets</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
@@ -4385,6 +5963,63 @@
       <c r="W29" s="9" t="inlineStr"/>
       <c r="X29" s="8" t="inlineStr"/>
       <c r="Y29" s="8" t="inlineStr"/>
+      <c r="Z29" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA29" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB29" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: sweep(address[]): CALL at pc=1673 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC29" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD29" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE29" s="12" t="inlineStr">
+        <is>
+          <t>3324-byte runtime on optimism exposing 5 dispatched function(s): 0x3f7e82d6, multicall(address[],uint256[],bytes[]), sweep(address[]), execute(address,uint256,bytes), receiver()
+Concern(s) found: sweep(address[]): CALL at pc=1673 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; multicall(address[],uint256[],bytes[]): msg.sender must equal the hardcoded address 0x6a92a3127334f1ed2aa0349e2221d87f5d512183. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; execute(address,uint256,bytes): msg.sender must equal the hardcoded address 0x6a92a3127334f1ed2aa0349e2221d87f5d512183. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×2, CALL×7, CALLER×3, CREATE×1, SSTORE×1, STATICCALL×2</t>
+        </is>
+      </c>
+      <c r="AF29" s="12" t="inlineStr">
+        <is>
+          <t>• 0x3f7e82d6: an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• multicall(address[],uint256[],bytes[]): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x6a92a3127334f1ed2aa0349e2221d87f5d512183 [analysis incomplete for this function]
+• sweep(address[]): an unauthenticated path to a sensitive operation exists
+• execute(address,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x6a92a3127334f1ed2aa0349e2221d87f5d512183 [analysis incomplete for this function]
+• receiver(): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG29" s="12" t="inlineStr">
+        <is>
+          <t>chain=optimism
+runtime size=3324 bytes
+verified source=False
+other chains with identical bytecode: ["optimism"]
+addresses embedded in the code: [{"bytecode_offset": 578, "address": "0xd8792d39bddb4622cbadd62004a067e72206ca98"}, {"bytecode_offset": 1755, "address": "0x115490cc8c08199bdc9dd85c990819985a5b1959"}, {"bytecode_offset": 2674, "address": "0x6a92a3127334f1ed2aa0349e2221d87f5d512183"}]</t>
+        </is>
+      </c>
+      <c r="AH29" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [2977, 3061]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x3f7e82d6, execute(address,uint256,bytes), multicall(address[],uint256[],bytes[]); unrestricted CREATE/CREATE2 at [('0x3f7e82d6', 550)] — a capability whose concrete risk depends on what the created contract is given authority over, which bytecode alone does not establish; unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: 0x3f7e82d6 pc=656 -&gt; 0xd8792d39bddb4622cbadd62004a067e72206ca98 (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -4512,6 +6147,60 @@
       <c r="W30" s="6" t="inlineStr"/>
       <c r="X30" s="8" t="inlineStr"/>
       <c r="Y30" s="8" t="inlineStr"/>
+      <c r="Z30" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA30" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB30" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x3cc85aee: msg.sender must equal the hardcoded address 0xdead652ebf95cf995c99638adbb8f1cfd01a6a00. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as PARTIALLY_CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC30" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed PARTIALLY_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD30" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The reachability the rule asserts is reproduced (an external call is reachable from receive()/fallback()), but every such path passes an authorization branch. The rule is correct about capability and silent about authorization, which is its documented limitation — it has no guard predicate. This is capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
+      <c r="AE30" s="12" t="inlineStr">
+        <is>
+          <t>5163-byte runtime on optimism exposing 4 dispatched function(s): 0x3cc85aee, noop(), 0x773d5602, owner() Embedded strings mention: Executor, not authorized.
+Concern(s) found: 0x3cc85aee: msg.sender must equal the hardcoded address 0xdead652ebf95cf995c99638adbb8f1cfd01a6a00. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x3cc85aee: msg.sender must equal the hardcoded address 0xdead652ebf95cf995c99638adbb8f1cfd01a6a00. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×2, CALL×4, CALLER×5</t>
+        </is>
+      </c>
+      <c r="AF30" s="12" t="inlineStr">
+        <is>
+          <t>• 0x3cc85aee: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xdead652ebf95cf995c99638adbb8f1cfd01a6a00; hardcoded_address_check against 0xdead652ebf95cf995c99638adbb8f1cfd01a6a00
+• noop(): no sensitive operation reachable
+• 0x773d5602: no sensitive operation reachable
+• owner(): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG30" s="12" t="inlineStr">
+        <is>
+          <t>chain=optimism
+runtime size=5163 bytes
+verified source=False
+other chains with identical bytecode: ["optimism"]</t>
+        </is>
+      </c>
+      <c r="AH30" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
@@ -4639,6 +6328,65 @@
       <c r="W31" s="9" t="inlineStr"/>
       <c r="X31" s="8" t="inlineStr"/>
       <c r="Y31" s="8" t="inlineStr"/>
+      <c r="Z31" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA31" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB31" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x64559ce7: CALL at pc=1455 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC31" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD31" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE31" s="12" t="inlineStr">
+        <is>
+          <t>5916-byte runtime on ethereum exposing 7 dispatched function(s): 0x503324bc, 0x64559ce7, 0x6709617a, 0x786d161d, 0x8f038e4a, 0xa540582f, 0xca56ebfb
+Concern(s) found: 0x64559ce7: CALL at pc=1455 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0x6709617a: CALL at pc=1812 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0xca56ebfb: CALL at pc=3319 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0x503324bc: CALL at pc=929 to 0x0bfb5ba84adb386083f3b782b2d926f8154f06c4 with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; 0x786d161d: tx.origin must equal the hardcoded address 0x0bfb5ba84adb386083f3b782b2d926f8154f06c4. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x8f038e4a: tx.origin must equal the hardcoded address 0x0bfb5ba84adb386083f3b782b2d926f8154f06c4. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0xa540582f: tx.origin must equal the hardcoded address 0x0bfb5ba84adb386083f3b782b2d926f8154f06c4. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×3, CALL×10, CALLER×1, ORIGIN×3, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF31" s="12" t="inlineStr">
+        <is>
+          <t>• 0x503324bc: an unauthenticated path to a sensitive operation exists
+• 0x64559ce7: an unauthenticated path to a sensitive operation exists
+• 0x6709617a: an unauthenticated path to a sensitive operation exists
+• 0x786d161d: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0bfb5ba84adb386083f3b782b2d926f8154f06c4
+• 0x8f038e4a: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0bfb5ba84adb386083f3b782b2d926f8154f06c4
+• 0xa540582f: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0bfb5ba84adb386083f3b782b2d926f8154f06c4
+• 0xca56ebfb: an unauthenticated path to a sensitive operation exists
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG31" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=5916 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 134, "address": "0x0bfb5ba84adb386083f3b782b2d926f8154f06c4"}]</t>
+        </is>
+      </c>
+      <c r="AH31" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [5904]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -4766,6 +6514,68 @@
       <c r="W32" s="6" t="inlineStr"/>
       <c r="X32" s="8" t="inlineStr"/>
       <c r="Y32" s="8" t="inlineStr"/>
+      <c r="Z32" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA32" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB32" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: rescue(): CALL at pc=961 to unresolved with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time The source static analyzer's verdict was assessed as PARTIALLY_CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC32" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed PARTIALLY_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD32" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The reachability the rule asserts is reproduced (an external call is reachable from receive()/fallback()), but every such path passes an authorization branch. The rule is correct about capability and silent about authorization, which is its documented limitation — it has no guard predicate. This is capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
+      <c r="AE32" s="12" t="inlineStr">
+        <is>
+          <t>6202-byte runtime on ethereum exposing 10 dispatched function(s): 0x0ce66fc4, rescue(), 0x45407d71, 0x5330ff81, rescue(uint256), revoke(address), 0x793d70f6, owner(), 0xb67b62b9, 0xcd7e8be1
+Concern(s) found: rescue(): CALL at pc=961 to unresolved with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; 0x45407d71: CALL at pc=961 to unresolved with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; rescue(uint256): CALL at pc=961 to unresolved with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time
+Instruction census (whole contract): ADDRESS×3, CALL×8, ORIGIN×3, STATICCALL×2</t>
+        </is>
+      </c>
+      <c r="AF32" s="12" t="inlineStr">
+        <is>
+          <t>• 0x0ce66fc4: no sensitive operation reachable
+• rescue(): an unauthenticated path to a sensitive operation exists
+• 0x45407d71: an unauthenticated path to a sensitive operation exists
+• 0x5330ff81: no sensitive operation reachable
+• rescue(uint256): an unauthenticated path to a sensitive operation exists
+• revoke(address): an unauthenticated path to a sensitive operation exists
+• 0x793d70f6: no sensitive operation reachable
+• owner(): no sensitive operation reachable
+• 0xb67b62b9: no sensitive operation reachable
+• 0xcd7e8be1: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 4 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG32" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=6202 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 2561, "address": "0xc02aaa39b223fe8d0a0e5c4f27ead9083c756cc2"}, {"bytecode_offset": 2585, "address": "0xe592427a0aece92de3edee1f18e0157c05861564"}]</t>
+        </is>
+      </c>
+      <c r="AH32" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [2445, 2711, 2983, 3365]}) — capability here is a lower bound; unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: rescue() pc=1685 -&gt; 0xf0bae7189bf0ebbaa76b5a6b372c9db837e455c4 (value=0, data=memory); rescue() pc=2257 -&gt; 0xc3f822e94c321dd3ee53ca46b78098ea79b7ec8d (value=0, data=memory); rescue(uint256) pc=1685 -&gt; 0xf0bae7189bf0ebbaa76b5a6b372c9db837e455c4 (value=0, data=memory); rescue(uint256) pc=2257 -&gt; 0xc3f822e94c321dd3ee53ca46b78098ea79b7ec8d (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
@@ -4893,6 +6703,59 @@
       <c r="W33" s="9" t="inlineStr"/>
       <c r="X33" s="8" t="inlineStr"/>
       <c r="Y33" s="8" t="inlineStr"/>
+      <c r="Z33" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA33" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB33" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x3cc85aee: msg.sender must equal the hardcoded address 0xdead652ebf95cf995c99638adbb8f1cfd01a6a00. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as PARTIALLY_CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC33" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed PARTIALLY_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD33" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The reachability the rule asserts is reproduced (an external call is reachable from receive()/fallback()), but every such path passes an authorization branch. The rule is correct about capability and silent about authorization, which is its documented limitation — it has no guard predicate. This is capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
+      <c r="AE33" s="12" t="inlineStr">
+        <is>
+          <t>4321-byte runtime on bnb exposing 3 dispatched function(s): 0x3cc85aee, 0x773d5602, owner() Embedded strings mention: Executor.
+Concern(s) found: 0x3cc85aee: msg.sender must equal the hardcoded address 0xdead652ebf95cf995c99638adbb8f1cfd01a6a00. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x3cc85aee: msg.sender must equal the hardcoded address 0xdead652ebf95cf995c99638adbb8f1cfd01a6a00. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×2, CALL×4, CALLER×5</t>
+        </is>
+      </c>
+      <c r="AF33" s="12" t="inlineStr">
+        <is>
+          <t>• 0x3cc85aee: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xdead652ebf95cf995c99638adbb8f1cfd01a6a00; hardcoded_address_check against 0xdead652ebf95cf995c99638adbb8f1cfd01a6a00 [analysis incomplete for this function]
+• 0x773d5602: no sensitive operation reachable
+• owner(): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG33" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=4321 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]</t>
+        </is>
+      </c>
+      <c r="AH33" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x3cc85aee</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -5020,6 +6883,62 @@
       <c r="W34" s="6" t="inlineStr"/>
       <c r="X34" s="8" t="inlineStr"/>
       <c r="Y34" s="8" t="inlineStr"/>
+      <c r="Z34" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA34" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB34" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x1bd13a99: CALL at pc=359 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC34" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD34" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE34" s="12" t="inlineStr">
+        <is>
+          <t>2403-byte runtime on arbitrum exposing 3 dispatched function(s): 0x1bd13a99, owner(), 0xc1d3ab60
+Concern(s) found: 0x1bd13a99: CALL at pc=359 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 3}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx3 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×3</t>
+        </is>
+      </c>
+      <c r="AF34" s="12" t="inlineStr">
+        <is>
+          <t>• 0x1bd13a99: an unauthenticated path to a sensitive operation exists
+• owner(): no sensitive operation reachable
+• 0xc1d3ab60: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG34" s="12" t="inlineStr">
+        <is>
+          <t>chain=arbitrum
+runtime size=2403 bytes
+verified source=False
+other chains with identical bytecode: ["arbitrum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 1, "n_writes": 0}]
+addresses embedded in the code: [{"bytecode_offset": 62, "address": "0xb8d0d79eada4e2432fc71682d70732273f5ac186"}]</t>
+        </is>
+      </c>
+      <c r="AH34" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [821]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
@@ -5147,6 +7066,61 @@
       <c r="W35" s="9" t="inlineStr"/>
       <c r="X35" s="8" t="inlineStr"/>
       <c r="Y35" s="8" t="inlineStr"/>
+      <c r="Z35" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA35" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB35" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: initialize(address): SSTORE to slot 0x0 at pc=583 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC35" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD35" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE35" s="12" t="inlineStr">
+        <is>
+          <t>1042-byte runtime on base exposing 2 dispatched function(s): destination(), initialize(address)
+Concern(s) found: initialize(address): SSTORE to slot 0x0 at pc=583 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls
+Instruction census (whole contract): CALL×1, CALLCODE×1, CALLER×1, SSTORE×1</t>
+        </is>
+      </c>
+      <c r="AF35" s="12" t="inlineStr">
+        <is>
+          <t>• destination(): no sensitive operation reachable
+• initialize(address): an unauthenticated path to a sensitive operation exists
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG35" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=1042 bytes
+verified source=True
+other chains with identical bytecode: ["base", "bnb", "ethereum", "gnosis", "optimism"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 1, "n_writes": 1}]
+addresses embedded in the code: [{"bytecode_offset": 1009, "address": "0x69bb9c7db3a5b404a21dc91bdf63e891ef7e9320"}]</t>
+        </is>
+      </c>
+      <c r="AH35" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALLCODE': [1002]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -5274,6 +7248,60 @@
       <c r="W36" s="6" t="inlineStr"/>
       <c r="X36" s="8" t="inlineStr"/>
       <c r="Y36" s="8" t="inlineStr"/>
+      <c r="Z36" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA36" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB36" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: every dispatched function analysed to completion with no reachable sensitive operation. The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC36" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD36" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE36" s="12" t="inlineStr">
+        <is>
+          <t>1524-byte runtime on bnb exposing 4 dispatched function(s): 0x5a04aa5f, initialized(address), 0xda8120d8, receiver()
+Instruction census (whole contract): CALL×1, CALLER×4, SSTORE×2</t>
+        </is>
+      </c>
+      <c r="AF36" s="12" t="inlineStr">
+        <is>
+          <t>• 0x5a04aa5f: no sensitive operation reachable
+• initialized(address): no sensitive operation reachable
+• 0xda8120d8: an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• receiver(): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG36" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=1524 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "mapping(address =&gt; bool)", "n_reads": 2, "n_writes": 1}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "mapping(address =&gt; bool)", "n_reads": 1, "n_</t>
+        </is>
+      </c>
+      <c r="AH36" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
@@ -5401,6 +7429,64 @@
       <c r="W37" s="9" t="inlineStr"/>
       <c r="X37" s="8" t="inlineStr"/>
       <c r="Y37" s="8" t="inlineStr"/>
+      <c r="Z37" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA37" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB37" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [2136]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC37" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD37" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE37" s="12" t="inlineStr">
+        <is>
+          <t>6259-byte runtime on arbitrum exposing 6 dispatched function(s): 0x353e6aec, recipient(), getOwner(), changeOwner(address), nonce(), 0xb0b49641 Embedded strings mention: Signed Message, not owner.
+Protection(s) found: self-call restriction (msg.sender == address(this)) on 0x353e6aec — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent; signature-derived authorization branch (ecrecover) on 0xb0b49641; msg.sender compared against a stored authority on changeOwner(address)
+Instruction census (whole contract): ADDRESS×2, CALL×2, CALLER×4, SSTORE×2, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF37" s="12" t="inlineStr">
+        <is>
+          <t>• 0x353e6aec: every path to a sensitive operation passes an authorization check — check found: self_call_check; storage_condition
+• recipient(): no sensitive operation reachable
+• getOwner(): no sensitive operation reachable
+• changeOwner(address): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check
+• nonce(): no sensitive operation reachable
+• 0xb0b49641: every path to a sensitive operation passes an authorization check — check found: signature_authorization; storage_condition [analysis incomplete for this function]
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG37" s="12" t="inlineStr">
+        <is>
+          <t>chain=arbitrum
+runtime size=6259 bytes
+verified source=False
+other chains with identical bytecode: ["arbitrum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 2, "n_writes": 1}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "uint256", "n_reads": 1, "n_writes": 2}]</t>
+        </is>
+      </c>
+      <c r="AH37" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [2136]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0xb0b49641</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -5528,6 +7614,60 @@
       <c r="W38" s="6" t="inlineStr"/>
       <c r="X38" s="8" t="inlineStr"/>
       <c r="Y38" s="8" t="inlineStr"/>
+      <c r="Z38" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA38" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB38" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: withdrawNative(address): CALL at pc=773 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC38" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD38" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE38" s="12" t="inlineStr">
+        <is>
+          <t>2259-byte runtime on base exposing 2 dispatched function(s): withdrawNative(address), withdrawToken(address,address)
+Concern(s) found: withdrawNative(address): CALL at pc=773 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call
+Instruction census (whole contract): ADDRESS×1, CALL×3, CALLER×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF38" s="12" t="inlineStr">
+        <is>
+          <t>• withdrawNative(address): an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• withdrawToken(address,address): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG38" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=2259 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 2, "n_writes": 0}]</t>
+        </is>
+      </c>
+      <c r="AH38" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [1413]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
@@ -5655,6 +7795,60 @@
       <c r="W39" s="9" t="inlineStr"/>
       <c r="X39" s="8" t="inlineStr"/>
       <c r="Y39" s="8" t="inlineStr"/>
+      <c r="Z39" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA39" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB39" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: withdrawAnyToken(address): msg.sender must equal the hardcoded address 0x7e537bae7ca6540e234349d477494099c03c9999. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC39" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD39" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE39" s="12" t="inlineStr">
+        <is>
+          <t>1342-byte runtime on ethereum exposing 1 dispatched function(s): withdrawAnyToken(address)
+Concern(s) found: withdrawAnyToken(address): msg.sender must equal the hardcoded address 0x7e537bae7ca6540e234349d477494099c03c9999. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×5, CALL×2, CALLER×9, ORIGIN×2, SELFDESTRUCT×1, SSTORE×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF39" s="12" t="inlineStr">
+        <is>
+          <t>• withdrawAnyToken(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x7e537bae7ca6540e234349d477494099c03c9999
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG39" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=1342 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "mapping(address =&gt; uint8)", "n_reads": 0, "n_writes": 0}]
+addresses embedded in the code: [{"bytecode_offset": 227, "address": "0x7e537bae7ca6540e234349d477494099c03c9999"}]</t>
+        </is>
+      </c>
+      <c r="AH39" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'SELFDESTRUCT': [1314]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -5782,6 +7976,60 @@
       <c r="W40" s="6" t="inlineStr"/>
       <c r="X40" s="8" t="inlineStr"/>
       <c r="Y40" s="8" t="inlineStr"/>
+      <c r="Z40" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA40" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB40" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: withdrawAnyToken(address): msg.sender must equal the hardcoded address 0x3e577385fe768238d525b04cb25fae7c0e700000. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as PARTIALLY_CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC40" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed PARTIALLY_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD40" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The reachability the rule asserts is reproduced (an external call is reachable from receive()/fallback()), but every such path passes an authorization branch. The rule is correct about capability and silent about authorization, which is its documented limitation — it has no guard predicate. This is capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
+      <c r="AE40" s="12" t="inlineStr">
+        <is>
+          <t>1475-byte runtime on bnb exposing 2 dispatched function(s): withdrawAnyToken(address), 0xa9f5cd83
+Concern(s) found: withdrawAnyToken(address): msg.sender must equal the hardcoded address 0x3e577385fe768238d525b04cb25fae7c0e700000. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0xa9f5cd83: msg.sender must equal the hardcoded address 0x3e577385fe768238d525b04cb25fae7c0e700000. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×5, CALL×2, CALLER×8, ORIGIN×2, SSTORE×2, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF40" s="12" t="inlineStr">
+        <is>
+          <t>• withdrawAnyToken(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x3e577385fe768238d525b04cb25fae7c0e700000
+• 0xa9f5cd83: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x3e577385fe768238d525b04cb25fae7c0e700000</t>
+        </is>
+      </c>
+      <c r="AG40" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=1475 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "mapping(address =&gt; uint8)", "n_reads": 0, "n_writes": 1}]
+addresses embedded in the code: [{"bytecode_offset": 238, "address": "0x3e577385fe768238d525b04cb25fae7c0e700000"}]</t>
+        </is>
+      </c>
+      <c r="AH40" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
@@ -5909,6 +8157,113 @@
       <c r="W41" s="9" t="inlineStr"/>
       <c r="X41" s="8" t="inlineStr"/>
       <c r="Y41" s="8" t="inlineStr"/>
+      <c r="Z41" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA41" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB41" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: delegateToImplementation(bytes): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC41" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD41" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): fallback()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE41" s="12" t="inlineStr">
+        <is>
+          <t>7544-byte runtime on base exposing 54 dispatched function(s): name(), delegateToImplementation(bytes), approve(address,uint256), repayBorrow(uint256), reserveFactorMantissa(), borrowBalanceCurrent(address), totalSupply(), exchangeRateStored(), sweepToken(address), transferFrom(address,address,uint256)
+Concern(s) found: delegateToImplementation(bytes): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; approve(address,uint256): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; repayBorrow(uint256): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; borrowBalanceCurrent(address): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; sweepToken(address): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; transferFrom(address,address,uint256): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; repayBorrowBehalf(address,uint256): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; balanceOfUnderlying(address): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; _addReserves(uint256): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; _setComptroller(address): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; _reduceReserves(uint256): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; totalBorrowsCurrent(): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; _setProtocolSeizeShare(uint256): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; redeemUnderlying(uint256): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; mint(uint256): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; accrueInterest(): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; transfer(address,uint256): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; seize(address,address,uint256): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; _setPendingAdmin(address): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; exchangeRateCurrent(): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; borrow(uint256): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; mintWithPermit(uint256,uint256,uint8,bytes32,bytes32): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; redeem(uint256): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; _acceptAdmin(): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; _setInterestRateModel(address): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; liquidateBorrow(address,uint256,address): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; _setReserveFactor(uint256): DELEGATECALL at pc=6250 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage
+Protection(s) found: msg.sender compared against a stored authority on _setImplementation(address,bool,bytes)
+Instruction census (whole contract): ADDRESS×1, CALL×1, CALLER×1, CREATE2×1, DELEGATECALL×2, SSTORE×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF41" s="12" t="inlineStr">
+        <is>
+          <t>• name(): no sensitive operation reachable — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• delegateToImplementation(bytes): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• approve(address,uint256): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• repayBorrow(uint256): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• reserveFactorMantissa(): no sensitive operation reachable
+• borrowBalanceCurrent(address): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• totalSupply(): no sensitive operation reachable
+• exchangeRateStored(): no sensitive operation reachable [analysis incomplete for this function]
+• sweepToken(address): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• transferFrom(address,address,uint256): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• repayBorrowBehalf(address,uint256): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• pendingAdmin(): no sensitive operation reachable
+• decimals(): no sensitive operation reachable
+• balanceOfUnderlying(address): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• getCash(): no sensitive operation reachable [analysis incomplete for this function]
+• _addReserves(uint256): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• delegateToViewImplementation(bytes): no sensitive operation reachable [analysis incomplete for this function]
+• _setComptroller(address): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• totalBorrows(): no sensitive operation reachable
+• _setImplementation(address,bool,bytes): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_condition [analysis incomplete for this function]
+• implementation(): no sensitive operation reachable
+• comptroller(): no sensitive operation reachable
+• _reduceReserves(uint256): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• protocolSeizeShareMantissa(): no sensitive operation reachable
+• 0x699cd5e2: no sensitive operation reachable
+• underlying(): no sensitive operation reachable
+• balanceOf(address): no sensitive operation reachable [analysis incomplete for this function]
+• totalBorrowsCurrent(): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• _setProtocolSeizeShare(uint256): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• redeemUnderlying(uint256): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• totalReserves(): no sensitive operation reachable
+• symbol(): no sensitive operation reachable — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• borrowBalanceStored(address): no sensitive operation reachable [analysis incomplete for this function]
+• mint(uint256): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• accrueInterest(): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• transfer(address,uint256): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• borrowIndex(): no sensitive operation reachable
+• seize(address,address,uint256): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• _setPendingAdmin(address): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• exchangeRateCurrent(): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• getAccountSnapshot(address): no sensitive operation reachable [analysis incomplete for this function]
+• borrow(uint256): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• borrowRatePerTimestamp(): no sensitive operation reachable [analysis incomplete for this function]
+• accrualBlockTimestamp(): no sensitive operation reachable
+• mintWithPermit(uint256,uint256,uint8,bytes32,bytes32): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• supplyRatePerTimestamp(): no sensitive operation reachable [analysis incomplete for this function]
+• redeem(uint256): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• allowance(address,address): no sensitive operation reachable [analysis incomplete for this function]
+• _acceptAdmin(): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• _setInterestRateModel(address): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• interestRateModel(): no sensitive operation reachable
+• liquidateBorrow(address,uint256,address): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• admin(): no sensitive operation reachable
+• _setReserveFactor(uint256): an unauthenticated path to a sensitive operation exists — check found: storage_condition [analysis incomplete for this function]
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG41" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=7544 bytes
+verified source=True
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "string", "n_reads": 1, "n_writes": 0}, {"slot": "0000000000000000000000000000000000000000000000000000000000000002", "offset": 0, "type": "string", "n_reads": 1, "n_writes": 0}, {"slot": "0000000000000</t>
+        </is>
+      </c>
+      <c r="AH41" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [7502], 'CREATE2': [7527]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: _acceptAdmin(), _addReserves(uint256), _reduceReserves(uint256), _setComptroller(address), _setImplementation(address,bool,bytes), _setInterestRateModel(address), _setPendingAdmin(address), _setProtocolSeizeShare(uint256)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -6036,6 +8391,60 @@
       <c r="W42" s="6" t="inlineStr"/>
       <c r="X42" s="8" t="inlineStr"/>
       <c r="Y42" s="8" t="inlineStr"/>
+      <c r="Z42" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA42" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB42" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: burn(): CALL at pc=452 to 0xe576417d2a27afe942513a076ab0ad5f8f36242e with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC42" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD42" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE42" s="12" t="inlineStr">
+        <is>
+          <t>1857-byte runtime on ethereum exposing 3 dispatched function(s): 0x1d073a7a, burn(), 0xf3f869c3
+Concern(s) found: burn(): CALL at pc=452 to 0xe576417d2a27afe942513a076ab0ad5f8f36242e with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; burn(): CALL at pc=525 to unresolved with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; 0xf3f869c3: tx.origin must equal the hardcoded address 0xe576417d2a27afe942513a076ab0ad5f8f36242e. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×5, CALLER×1, ORIGIN×1</t>
+        </is>
+      </c>
+      <c r="AF42" s="12" t="inlineStr">
+        <is>
+          <t>• 0x1d073a7a: no sensitive operation reachable
+• burn(): an unauthenticated path to a sensitive operation exists
+• 0xf3f869c3: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xe576417d2a27afe942513a076ab0ad5f8f36242e</t>
+        </is>
+      </c>
+      <c r="AG42" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=1857 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 61, "address": "0xe576417d2a27afe942513a076ab0ad5f8f36242e"}]</t>
+        </is>
+      </c>
+      <c r="AH42" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
@@ -6163,6 +8572,59 @@
       <c r="W43" s="9" t="inlineStr"/>
       <c r="X43" s="8" t="inlineStr"/>
       <c r="Y43" s="8" t="inlineStr"/>
+      <c r="Z43" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA43" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB43" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: destroyMe(): tx.origin must equal the hardcoded address 0x7638a17d0dde05a2616b8b765600af6a0adad750. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC43" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD43" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE43" s="12" t="inlineStr">
+        <is>
+          <t>2900-byte runtime on arbitrum exposing 2 dispatched function(s): 0x0a7c8ed6, destroyMe() Embedded strings mention: Multicall, not owner.
+Concern(s) found: destroyMe(): tx.origin must equal the hardcoded address 0x7638a17d0dde05a2616b8b765600af6a0adad750. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×3, CALLER×1, ORIGIN×2, SELFDESTRUCT×2, SSTORE×1</t>
+        </is>
+      </c>
+      <c r="AF43" s="12" t="inlineStr">
+        <is>
+          <t>• 0x0a7c8ed6: no sensitive operation reachable — check found: hardcoded_address_check against 0x7638a17d0dde05a2616b8b765600af6a0adad750 [analysis incomplete for this function]
+• destroyMe(): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x7638a17d0dde05a2616b8b765600af6a0adad750
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG43" s="12" t="inlineStr">
+        <is>
+          <t>chain=arbitrum
+runtime size=2900 bytes
+verified source=False
+other chains with identical bytecode: ["arbitrum"]</t>
+        </is>
+      </c>
+      <c r="AH43" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [731], 'SELFDESTRUCT': [2857]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x0a7c8ed6</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -6290,6 +8752,64 @@
       <c r="W44" s="6" t="inlineStr"/>
       <c r="X44" s="8" t="inlineStr"/>
       <c r="Y44" s="8" t="inlineStr"/>
+      <c r="Z44" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA44" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB44" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: transferAllToken(address,address): tx.origin must equal the hardcoded address 0x72785d42874e965086829ea789a703fe1a5238df. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC44" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD44" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE44" s="12" t="inlineStr">
+        <is>
+          <t>2193-byte runtime on arbitrum exposing 7 dispatched function(s): transferAllToken(address,address), getCurrentBlockTimestamp(), aggregate3Value((address,bool,uint256,bytes)[]), 0x35447e72, getBlockNumber(), getEthBalance(address), getCurrentBlockCoinbase() Embedded strings mention: Multicall.
+Concern(s) found: transferAllToken(address,address): tx.origin must equal the hardcoded address 0x72785d42874e965086829ea789a703fe1a5238df. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; aggregate3Value((address,bool,uint256,bytes)[]): msg.sender must equal the hardcoded address 0x72785d42874e965086829ea789a703fe1a5238df. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x35447e72: tx.origin must equal the hardcoded address 0x72785d42874e965086829ea789a703fe1a5238df. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×1, CALL×3, CALLER×1, ORIGIN×2, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF44" s="12" t="inlineStr">
+        <is>
+          <t>• transferAllToken(address,address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x72785d42874e965086829ea789a703fe1a5238df
+• getCurrentBlockTimestamp(): no sensitive operation reachable
+• aggregate3Value((address,bool,uint256,bytes)[]): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x72785d42874e965086829ea789a703fe1a5238df [analysis incomplete for this function]
+• 0x35447e72: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x72785d42874e965086829ea789a703fe1a5238df
+• getBlockNumber(): no sensitive operation reachable
+• getEthBalance(address): no sensitive operation reachable
+• getCurrentBlockCoinbase(): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG44" s="12" t="inlineStr">
+        <is>
+          <t>chain=arbitrum
+runtime size=2193 bytes
+verified source=False
+other chains with identical bytecode: ["arbitrum", "base", "bnb", "ethereum", "optimism", "polygon"]
+addresses embedded in the code: [{"bytecode_offset": 352, "address": "0x72785d42874e965086829ea789a703fe1a5238df"}]</t>
+        </is>
+      </c>
+      <c r="AH44" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: aggregate3Value((address,bool,uint256,bytes)[])</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
@@ -6417,6 +8937,61 @@
       <c r="W45" s="9" t="inlineStr"/>
       <c r="X45" s="8" t="inlineStr"/>
       <c r="Y45" s="8" t="inlineStr"/>
+      <c r="Z45" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA45" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB45" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: transferTokens(address): CALL at pc=1679 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC45" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD45" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE45" s="12" t="inlineStr">
+        <is>
+          <t>3597-byte runtime on bnb exposing 5 dispatched function(s): transferTokens(address), 0x29cd3d04, 0x2c7bddf4, 0xab7e4c70, executeCall(address,bytes)
+Concern(s) found: transferTokens(address): CALL at pc=1679 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0xab7e4c70: CALL at pc=1037 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; executeCall(address,bytes): CALL at pc=1852 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0x2c7bddf4: CALL at pc=704 to 0xd0e49dec126d0ac848389843917c5204aa2be5c2 with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time
+Instruction census (whole contract): ADDRESS×1, CALL×5, CALLER×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF45" s="12" t="inlineStr">
+        <is>
+          <t>• transferTokens(address): an unauthenticated path to a sensitive operation exists
+• 0x29cd3d04: an unauthenticated path to a sensitive operation exists
+• 0x2c7bddf4: an unauthenticated path to a sensitive operation exists
+• 0xab7e4c70: an unauthenticated path to a sensitive operation exists
+• executeCall(address,bytes): an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG45" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=3597 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]</t>
+        </is>
+      </c>
+      <c r="AH45" s="12" t="inlineStr">
+        <is>
+          <t>unauthenticated call(s) forwarding only msg.value to a fixed destination ([('0x29cd3d04', 391, '0xd0e49dec126d0ac848389843917c5204aa2be5c2'), ('0xab7e4c70', 391, '0xd0e49dec126d0ac848389843917c5204aa2be5c2'), ('executeCall(address,bytes)', 391, '0xd0e49dec126d0ac848389843917c5204aa2be5c2')]) — a caller can only donate their own ETH, so this is not by itself a path to the account's assets</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -6544,6 +9119,60 @@
       <c r="W46" s="6" t="inlineStr"/>
       <c r="X46" s="8" t="inlineStr"/>
       <c r="Y46" s="8" t="inlineStr"/>
+      <c r="Z46" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA46" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB46" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x17f2408f: CALL at pc=1053 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC46" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD46" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE46" s="12" t="inlineStr">
+        <is>
+          <t>1841-byte runtime on bnb exposing 3 dispatched function(s): 0x17f2408f, withdrawETH(), withdrawERC20(address)
+Concern(s) found: 0x17f2408f: CALL at pc=1053 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; withdrawERC20(address): CALL at pc=1053 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0x17f2408f: CALL at pc=232 to 0x222d1f38252726c9d49c8b963b6dcb808e8dcbfd with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; withdrawETH(): CALL at pc=232 to 0x222d1f38252726c9d49c8b963b6dcb808e8dcbfd with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time
+Instruction census (whole contract): ADDRESS×2, CALL×2, CALLER×1, STATICCALL×2</t>
+        </is>
+      </c>
+      <c r="AF46" s="12" t="inlineStr">
+        <is>
+          <t>• 0x17f2408f: an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• withdrawETH(): an unauthenticated path to a sensitive operation exists
+• withdrawERC20(address): an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]</t>
+        </is>
+      </c>
+      <c r="AG46" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=1841 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+addresses embedded in the code: [{"bytecode_offset": 296, "address": "0xeeeeeeeeeeeeeeeeeeeeeeeeeeeeeeeeeeeeeeee"}]</t>
+        </is>
+      </c>
+      <c r="AH46" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x17f2408f, withdrawERC20(address)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
@@ -6671,6 +9300,64 @@
       <c r="W47" s="9" t="inlineStr"/>
       <c r="X47" s="8" t="inlineStr"/>
       <c r="Y47" s="8" t="inlineStr"/>
+      <c r="Z47" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA47" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB47" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: setDestination(address): tx.origin must equal the hardcoded address 0x59987dc305076a6043504916ef9d655583f7e0a0. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC47" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD47" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE47" s="12" t="inlineStr">
+        <is>
+          <t>2497-byte runtime on ethereum exposing 6 dispatched function(s): setDestination(address), 0x2c1315e4, execute(address[],uint256[],bytes[]), 0xaee6ac73, destination(), 0xee179dbd
+Concern(s) found: setDestination(address): tx.origin must equal the hardcoded address 0x59987dc305076a6043504916ef9d655583f7e0a0. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x2c1315e4: tx.origin must equal the hardcoded address 0x59987dc305076a6043504916ef9d655583f7e0a0. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; execute(address[],uint256[],bytes[]): tx.origin must equal the hardcoded address 0x59987dc305076a6043504916ef9d655583f7e0a0. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0xaee6ac73: tx.origin must equal the hardcoded address 0x59987dc305076a6043504916ef9d655583f7e0a0. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0xee179dbd: tx.origin must equal the hardcoded address 0x59987dc305076a6043504916ef9d655583f7e0a0. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×2, CALL×5, CALLER×1, ORIGIN×5, SSTORE×1, STATICCALL×2</t>
+        </is>
+      </c>
+      <c r="AF47" s="12" t="inlineStr">
+        <is>
+          <t>• setDestination(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x59987dc305076a6043504916ef9d655583f7e0a0
+• 0x2c1315e4: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x59987dc305076a6043504916ef9d655583f7e0a0; storage_condition
+• execute(address[],uint256[],bytes[]): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x59987dc305076a6043504916ef9d655583f7e0a0
+• 0xaee6ac73: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x59987dc305076a6043504916ef9d655583f7e0a0
+• destination(): no sensitive operation reachable
+• 0xee179dbd: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x59987dc305076a6043504916ef9d655583f7e0a0</t>
+        </is>
+      </c>
+      <c r="AG47" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=2497 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 2, "n_writes": 1}]
+addresses embedded in the code: [{"bytecode_offset": 394, "address": "0x59987dc305076a6043504916ef9d655583f7e0a0"}]</t>
+        </is>
+      </c>
+      <c r="AH47" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: 0x2c1315e4 (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); 0x2c1315e4 (storage_condition (e.g. initialized flag, paused flag, or an authority slot))</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -6798,6 +9485,60 @@
       <c r="W48" s="6" t="inlineStr"/>
       <c r="X48" s="8" t="inlineStr"/>
       <c r="Y48" s="8" t="inlineStr"/>
+      <c r="Z48" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA48" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB48" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x04f3a55d: msg.sender must equal the hardcoded address 0xe342b094d684e6d17ba127ae6eadf613de736554. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC48" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD48" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE48" s="12" t="inlineStr">
+        <is>
+          <t>3497-byte runtime on bnb exposing 3 dispatched function(s): 0x04f3a55d, 0x773d5602, owner() Embedded strings mention: Executor, not authorized.
+Concern(s) found: 0x04f3a55d: msg.sender must equal the hardcoded address 0xe342b094d684e6d17ba127ae6eadf613de736554. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x04f3a55d: msg.sender must equal the hardcoded address 0xe342b094d684e6d17ba127ae6eadf613de736554. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×5, CALLER×3</t>
+        </is>
+      </c>
+      <c r="AF48" s="12" t="inlineStr">
+        <is>
+          <t>• 0x04f3a55d: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xe342b094d684e6d17ba127ae6eadf613de736554; hardcoded_address_check against 0xe342b094d684e6d17ba127ae6eadf613de736554
+• 0x773d5602: no sensitive operation reachable
+• owner(): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG48" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=3497 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]</t>
+        </is>
+      </c>
+      <c r="AH48" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [3482]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
@@ -6925,6 +9666,62 @@
       <c r="W49" s="9" t="inlineStr"/>
       <c r="X49" s="8" t="inlineStr"/>
       <c r="Y49" s="8" t="inlineStr"/>
+      <c r="Z49" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA49" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB49" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: executeBatch(address[],bytes[]): msg.sender must equal the hardcoded address 0x8b4ea4f8a25ed1b7b18044bb1a2bec9425603572. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC49" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD49" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 2 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE49" s="12" t="inlineStr">
+        <is>
+          <t>6430-byte runtime on base exposing 4 dispatched function(s): executeBatch(address[],bytes[]), execute(address,bytes), flushToken(address), withdrawETH()
+Concern(s) found: executeBatch(address[],bytes[]): msg.sender must equal the hardcoded address 0x8b4ea4f8a25ed1b7b18044bb1a2bec9425603572. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; execute(address,bytes): msg.sender must equal the hardcoded address 0x8b4ea4f8a25ed1b7b18044bb1a2bec9425603572. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; flushToken(address): msg.sender must equal the hardcoded address 0x8b4ea4f8a25ed1b7b18044bb1a2bec9425603572. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; withdrawETH(): msg.sender must equal the hardcoded address 0x8b4ea4f8a25ed1b7b18044bb1a2bec9425603572. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×2, CALL×11, CALLER×6, ORIGIN×1, STATICCALL×2</t>
+        </is>
+      </c>
+      <c r="AF49" s="12" t="inlineStr">
+        <is>
+          <t>• executeBatch(address[],bytes[]): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x8b4ea4f8a25ed1b7b18044bb1a2bec9425603572
+• execute(address,bytes): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x8b4ea4f8a25ed1b7b18044bb1a2bec9425603572
+• flushToken(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x8b4ea4f8a25ed1b7b18044bb1a2bec9425603572
+• withdrawETH(): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x8b4ea4f8a25ed1b7b18044bb1a2bec9425603572
+• COVERAGE GAP: the analysis never reached 5 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG49" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=6430 bytes
+verified source=False
+other chains with identical bytecode: ["base", "optimism"]
+addresses embedded in the code: [{"bytecode_offset": 82, "address": "0x8b4ea4f8a25ed1b7b18044bb1a2bec9425603572"}]</t>
+        </is>
+      </c>
+      <c r="AH49" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [438, 749, 1356, 1431]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -7052,6 +9849,59 @@
       <c r="W50" s="6" t="inlineStr"/>
       <c r="X50" s="8" t="inlineStr"/>
       <c r="Y50" s="8" t="inlineStr"/>
+      <c r="Z50" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA50" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB50" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x896b3555: CALL at pc=182 to 0x0b48bbd77b222b45db1f5669bc26708681e4cbca with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC50" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD50" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE50" s="12" t="inlineStr">
+        <is>
+          <t>2320-byte runtime on bnb exposing 2 dispatched function(s): 0x896b3555, execute((bytes,address,uint256)[])
+Concern(s) found: 0x896b3555: CALL at pc=182 to 0x0b48bbd77b222b45db1f5669bc26708681e4cbca with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; execute((bytes,address,uint256)[]): CALL at pc=182 to 0x0b48bbd77b222b45db1f5669bc26708681e4cbca with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 3, 'CREATE': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx3, CREATEx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×3, CREATE×1</t>
+        </is>
+      </c>
+      <c r="AF50" s="12" t="inlineStr">
+        <is>
+          <t>• 0x896b3555: an unauthenticated path to a sensitive operation exists
+• execute((bytes,address,uint256)[]): an unauthenticated path to a sensitive operation exists
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG50" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=2320 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]</t>
+        </is>
+      </c>
+      <c r="AH50" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [2282], 'CREATE': [2287]}) — capability here is a lower bound; unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: execute((bytes,address,uint256)[]) pc=407 -&gt; unresolved (value=memory, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
@@ -7179,6 +10029,61 @@
       <c r="W51" s="9" t="inlineStr"/>
       <c r="X51" s="8" t="inlineStr"/>
       <c r="Y51" s="8" t="inlineStr"/>
+      <c r="Z51" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA51" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB51" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x0f83369d: msg.sender must equal the hardcoded address 0xda43dcc01abded0c734b72ab295b4acee654e92d. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC51" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD51" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE51" s="12" t="inlineStr">
+        <is>
+          <t>1667-byte runtime on bnb exposing 3 dispatched function(s): 0x0f83369d, getBalance(), target()
+Concern(s) found: 0x0f83369d: msg.sender must equal the hardcoded address 0xda43dcc01abded0c734b72ab295b4acee654e92d. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×3, CALLER×1, SSTORE×1</t>
+        </is>
+      </c>
+      <c r="AF51" s="12" t="inlineStr">
+        <is>
+          <t>• 0x0f83369d: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xda43dcc01abded0c734b72ab295b4acee654e92d; storage_condition
+• getBalance(): no sensitive operation reachable
+• target(): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG51" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=1667 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 2, "n_writes": 1}]
+addresses embedded in the code: [{"bytecode_offset": 388, "address": "0xda43dcc01abded0c734b72ab295b4acee654e92d"}]</t>
+        </is>
+      </c>
+      <c r="AH51" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: 0x0f83369d (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); 0x0f83369d (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); 0x0f83369d (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); 0x0f83369d (storage_condition (e.g. initialized flag, paused flag, or an authority slot))</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -7306,6 +10211,68 @@
       <c r="W52" s="6" t="inlineStr"/>
       <c r="X52" s="8" t="inlineStr"/>
       <c r="Y52" s="8" t="inlineStr"/>
+      <c r="Z52" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA52" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB52" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x48f8c24f: SSTORE to slot 0x1 at pc=1324 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC52" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD52" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE52" s="12" t="inlineStr">
+        <is>
+          <t>4284-byte runtime on ethereum exposing 10 dispatched function(s): execute(bytes), keys(uint256), 0x10d1bfe5, 0x48f8c24f, 0x490d9a01, 0x5fce1927, 0x641cdfe2, multiSend(bytes), 0x972ce4bc, nonce()
+Concern(s) found: 0x48f8c24f: SSTORE to slot 0x1 at pc=1324 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x490d9a01: SSTORE to slot 0x0 at pc=2842 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x641cdfe2: SSTORE to slot 0x1 at pc=1324 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x972ce4bc: SSTORE to slot 0x1 at pc=1324 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls
+Protection(s) found: self-call restriction (msg.sender == address(this)) on 0x5fce1927, execute(bytes) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent; signature-derived authorization branch (ecrecover) on 0x48f8c24f, 0x641cdfe2
+Instruction census (whole contract): ADDRESS×5, CALL×1, CALLER×3, SSTORE×8, STATICCALL×6</t>
+        </is>
+      </c>
+      <c r="AF52" s="12" t="inlineStr">
+        <is>
+          <t>• execute(bytes): every path to a sensitive operation passes an authorization check — check found: self_call_check
+• keys(uint256): no sensitive operation reachable — check found: storage_condition; storage_condition
+• 0x10d1bfe5: no sensitive operation reachable
+• 0x48f8c24f: an unauthenticated path to a sensitive operation exists — check found: storage_condition; signature_authorization
+• 0x490d9a01: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• 0x5fce1927: every path to a sensitive operation passes an authorization check — check found: storage_condition; self_call_check
+• 0x641cdfe2: an unauthenticated path to a sensitive operation exists — check found: storage_condition; signature_authorization
+• multiSend(bytes): an unauthenticated path to a sensitive operation exists
+• 0x972ce4bc: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• nonce(): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG52" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=4284 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "uint32", "n_reads": 7, "n_writes": 2}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "uint256", "n_reads": 1, "n_writes": 4}, {"slot": "290decd9548b</t>
+        </is>
+      </c>
+      <c r="AH52" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x972ce4bc; unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: multiSend(bytes) pc=3047 -&gt; unresolved (value=memory, data=memory); 0x972ce4bc pc=3047 -&gt; unresolved (value=memory, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
@@ -7433,6 +10400,88 @@
       <c r="W53" s="9" t="inlineStr"/>
       <c r="X53" s="8" t="inlineStr"/>
       <c r="Y53" s="8" t="inlineStr"/>
+      <c r="Z53" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA53" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB53" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: executeFromExecutor(bytes32,bytes): msg.sender must equal the hardcoded address 0xdb9b1e94b5b69df7e401ddbede43491141047db3. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC53" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD53" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE53" s="12" t="inlineStr">
+        <is>
+          <t>11185-byte runtime on arbitrum exposing 29 dispatched function(s): supportsInterface(bytes4), 0x06394d67, onERC721Received(address,address,uint256,bytes), isValidSignature(bytes32,bytes), validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256), 0x2b3afd99, getNonce(uint192), 0x3ed01015, 0x445140b8, 0x49934047. Bytecode matches the documented project MetaMask_EIP7702StatelessDeleGator (VERIFIED_LEGITIMATE_CONTROL, provenance HIGH).
+Concern(s) found: executeFromExecutor(bytes32,bytes): msg.sender must equal the hardcoded address 0xdb9b1e94b5b69df7e401ddbede43491141047db3. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Protection(s) found: signature-derived authorization branch (ecrecover) on isValidSignature(bytes32,bytes), validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256); caller restricted to a recognized ERC-4337 EntryPoint on 0x3ed01015, 0x49934047, execute((address,uint256,bytes)), execute(bytes32,bytes), redeemDelegations(bytes[],bytes32[],bytes[]), validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256)
+Instruction census (whole contract): ADDRESS×21, CALL×6, CALLER×17, ORIGIN×1, STATICCALL×4</t>
+        </is>
+      </c>
+      <c r="AF53" s="12" t="inlineStr">
+        <is>
+          <t>• supportsInterface(bytes4): no sensitive operation reachable
+• 0x06394d67: no sensitive operation reachable
+• onERC721Received(address,address,uint256,bytes): no sensitive operation reachable
+• isValidSignature(bytes32,bytes): no sensitive operation reachable — check found: signature_authorization
+• validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032; signature_authorization
+• 0x2b3afd99: no sensitive operation reachable
+• getNonce(uint192): no sensitive operation reachable
+• 0x3ed01015: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032; hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032
+• 0x445140b8: no sensitive operation reachable
+• 0x49934047: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032; hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032
+• addDeposit(): an unauthenticated path to a sensitive operation exists
+• execute((address,uint256,bytes)): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032; hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032
+• withdrawDeposit(address,uint256): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032; hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032
+• getDomainHash(): no sensitive operation reachable
+• eip712Domain(): no sensitive operation reachable [analysis incomplete for this function]
+• NAME(): no sensitive operation reachable [analysis incomplete for this function]
+• DOMAIN_VERSION(): no sensitive operation reachable [analysis incomplete for this function]
+• entryPoint(): no sensitive operation reachable
+• onERC1155BatchReceived(address,address,uint256[],uint256[],bytes): no sensitive operation reachable
+• getDeposit(): no sensitive operation reachable
+• redeemDelegations(bytes[],bytes32[],bytes[]): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032; hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032 [analysis incomplete for this function]
+• supportsExecutionMode(bytes32): no sensitive operation reachable
+• getNonce(): no sensitive operation reachable
+• executeFromExecutor(bytes32,bytes): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xdb9b1e94b5b69df7e401ddbede43491141047db3 [analysis incomplete for this function]
+• execute(bytes32,bytes): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032; hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032 [analysis incomplete for this function]
+• delegationManager(): no sensitive operation reachable
+• 0xed8101b5: no sensitive operation reachable
+• onERC1155Received(address,address,uint256,uint256,bytes): no sensitive operation reachable
+• VERSION(): no sensitive operation reachable [analysis incomplete for this function]</t>
+        </is>
+      </c>
+      <c r="AG53" s="12" t="inlineStr">
+        <is>
+          <t>chain=arbitrum
+runtime size=11185 bytes
+verified source=True
+other chains with identical bytecode: ["arbitrum"]
+documented project: MetaMask_EIP7702StatelessDeleGator (VERIFIED_LEGITIMATE_CONTROL, provenance HIGH); docs: https://github.com/MetaMask/delegation-framework/blob/main/documents/Deployments.md
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "string", "n_reads": 1, "n_writes": 0}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "string", "n_reads": 1, "n_writes": 0}]</t>
+        </is>
+      </c>
+      <c r="AH53" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: DOMAIN_VERSION(), NAME(), VERSION(), eip712Domain(), execute(bytes32,bytes), executeFromExecutor(bytes32,bytes), redeemDelegations(bytes[],bytes32[],bytes[]); unauthenticated call(s) forwarding only msg.value to a fixed destination ([('addDeposit()', 2549, '0x0000000071727de22e5e9d8baf0edac6f37da032')]) — a caller can only donate their own ETH, so this is not by itself a path to the account's assets</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -7560,6 +10609,63 @@
       <c r="W54" s="6" t="inlineStr"/>
       <c r="X54" s="8" t="inlineStr"/>
       <c r="Y54" s="8" t="inlineStr"/>
+      <c r="Z54" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA54" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB54" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [1364, 2076]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC54" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD54" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE54" s="12" t="inlineStr">
+        <is>
+          <t>5249-byte runtime on base exposing 6 dispatched function(s): supportsInterface(bytes4), isValidSignature(bytes32,bytes), validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256), 0x19c0f409, 0x9265bb9d, ENTRY_POINT()
+Protection(s) found: signature-derived authorization branch (ecrecover) on isValidSignature(bytes32,bytes), validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256); caller restricted to a recognized ERC-4337 EntryPoint on validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256)
+Instruction census (whole contract): ADDRESS×1, CALL×3, CALLER×2, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF54" s="12" t="inlineStr">
+        <is>
+          <t>• supportsInterface(bytes4): no sensitive operation reachable
+• isValidSignature(bytes32,bytes): no sensitive operation reachable — check found: signature_authorization
+• validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x4337084d9e255ff0702461cf8895ce9e3b5ff108; signature_authorization
+• 0x19c0f409: no sensitive operation reachable
+• 0x9265bb9d: no sensitive operation reachable
+• ENTRY_POINT(): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG54" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=5249 bytes
+verified source=False
+other chains with identical bytecode: ["base"]</t>
+        </is>
+      </c>
+      <c r="AH54" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [1364, 2076]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
@@ -7687,6 +10793,78 @@
       <c r="W55" s="9" t="inlineStr"/>
       <c r="X55" s="8" t="inlineStr"/>
       <c r="Y55" s="8" t="inlineStr"/>
+      <c r="Z55" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA55" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB55" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: approve(address,uint256) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); increaseAllowance(address,uint256) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); increaseAllowance(address,uint256) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); burn(uint256) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)) The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC55" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD55" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE55" s="12" t="inlineStr">
+        <is>
+          <t>4413-byte runtime on bnb exposing 20 dispatched function(s): name(), approve(address,uint256), totalSupply(), transferFrom(address,address,uint256), decimals(), _decimals(), increaseAllowance(address,uint256), burn(uint256), balanceOf(address), renounceOwnership() Embedded strings mention: Ownable, Safe.
+Protection(s) found: msg.sender compared against a stored authority on mint(uint256), renounceOwnership(), transferOwnership(address)
+Instruction census (whole contract): ADDRESS×5, CALLER×1, ORIGIN×4, SSTORE×9</t>
+        </is>
+      </c>
+      <c r="AF55" s="12" t="inlineStr">
+        <is>
+          <t>• name(): no sensitive operation reachable — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• approve(address,uint256): every path to a sensitive operation passes an authorization check — check found: caller_check
+• totalSupply(): no sensitive operation reachable
+• transferFrom(address,address,uint256): an unauthenticated path to a sensitive operation exists — check found: caller_check; storage_condition [analysis incomplete for this function]
+• decimals(): no sensitive operation reachable
+• _decimals(): no sensitive operation reachable
+• increaseAllowance(address,uint256): every path to a sensitive operation passes an authorization check — check found: caller_check; storage_condition
+• burn(uint256): every path to a sensitive operation passes an authorization check — check found: storage_condition; caller_check [analysis incomplete for this function]
+• balanceOf(address): no sensitive operation reachable
+• renounceOwnership(): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check
+• getOwner(): no sensitive operation reachable
+• owner(): no sensitive operation reachable
+• symbol(): no sensitive operation reachable — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• mint(uint256): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_condition
+• decreaseAllowance(address,uint256): every path to a sensitive operation passes an authorization check — check found: caller_check; storage_condition [analysis incomplete for this function]
+• transfer(address,uint256): every path to a sensitive operation passes an authorization check — check found: caller_check; storage_condition [analysis incomplete for this function]
+• _symbol(): no sensitive operation reachable — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• _name(): no sensitive operation reachable — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• allowance(address,address): no sensitive operation reachable
+• transferOwnership(address): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check</t>
+        </is>
+      </c>
+      <c r="AG55" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=4413 bytes
+verified source=True
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 5, "n_writes": 2}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "mapping(address =&gt; uint256)", "n_reads": 5, "n_writes": 4}, {
+addresses embedded in the code: [{"bytecode_offset": 4179, "address": "0x2062616c616e636542455032303a207472616e73"}, {"bytecode_offset": 4236, "address": "0x656420616c6c6f77616e63652062656c6f77207a"}]</t>
+        </is>
+      </c>
+      <c r="AH55" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: approve(address,uint256) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); increaseAllowance(address,uint256) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); increaseAllowance(address,uint256) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); burn(uint256) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: _name(), _symbol(), burn(uint256), decreaseAllowance(address,uint256), name(), symbol(), transfer(address,uint256), transferFrom(address,address,uint256)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -7814,6 +10992,58 @@
       <c r="W56" s="6" t="inlineStr"/>
       <c r="X56" s="8" t="inlineStr"/>
       <c r="Y56" s="8" t="inlineStr"/>
+      <c r="Z56" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA56" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB56" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: sendNative(address,uint256): CALL at pc=250 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC56" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD56" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE56" s="12" t="inlineStr">
+        <is>
+          <t>1267-byte runtime on base exposing 1 dispatched function(s): sendNative(address,uint256)
+Concern(s) found: sendNative(address,uint256): CALL at pc=250 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'ADDRESS': 1, 'CALL': 1, 'DELEGATECALL': 1, 'CREATE': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx1, DELEGATECALLx1, CREATEx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): ADDRESS×1, CALL×1, CREATE×1, DELEGATECALL×1</t>
+        </is>
+      </c>
+      <c r="AF56" s="12" t="inlineStr">
+        <is>
+          <t>• sendNative(address,uint256): an unauthenticated path to a sensitive operation exists
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG56" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=1267 bytes
+verified source=True
+other chains with identical bytecode: ["base"]</t>
+        </is>
+      </c>
+      <c r="AH56" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'DELEGATECALL': [1224], 'CREATE': [1229]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
@@ -7941,6 +11171,68 @@
       <c r="W57" s="9" t="inlineStr"/>
       <c r="X57" s="8" t="inlineStr"/>
       <c r="Y57" s="8" t="inlineStr"/>
+      <c r="Z57" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA57" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB57" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: msg.sender compared against a stored authority on renounceOwnership(), transferOwnership(address) The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC57" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD57" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE57" s="12" t="inlineStr">
+        <is>
+          <t>3179-byte runtime on ethereum exposing 11 dispatched function(s): getCurrentBlockTimestamp(), aggregate((address,bytes)[]), getLastBlockHash(), getEthBalance(address), renounceOwnership(), getCurrentBlockDifficulty(), getCurrentBlockGasLimit(), owner(), getCurrentBlockCoinbase(), getBlockHash(uint256)
+Protection(s) found: msg.sender compared against a stored authority on renounceOwnership(), transferOwnership(address)
+Instruction census (whole contract): CALL×1, CALLER×2, SSTORE×1</t>
+        </is>
+      </c>
+      <c r="AF57" s="12" t="inlineStr">
+        <is>
+          <t>• getCurrentBlockTimestamp(): no sensitive operation reachable
+• aggregate((address,bytes)[]): an unauthenticated path to a sensitive operation exists
+• getLastBlockHash(): no sensitive operation reachable
+• getEthBalance(address): no sensitive operation reachable
+• renounceOwnership(): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check
+• getCurrentBlockDifficulty(): no sensitive operation reachable
+• getCurrentBlockGasLimit(): no sensitive operation reachable
+• owner(): no sensitive operation reachable
+• getCurrentBlockCoinbase(): no sensitive operation reachable
+• getBlockHash(uint256): no sensitive operation reachable
+• transferOwnership(address): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check</t>
+        </is>
+      </c>
+      <c r="AG57" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=3179 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 3, "n_writes": 2}]</t>
+        </is>
+      </c>
+      <c r="AH57" s="12" t="inlineStr">
+        <is>
+          <t>unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: aggregate((address,bytes)[]) pc=752 -&gt; unresolved (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -8068,6 +11360,90 @@
       <c r="W58" s="6" t="inlineStr"/>
       <c r="X58" s="8" t="inlineStr"/>
       <c r="Y58" s="8" t="inlineStr"/>
+      <c r="Z58" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA58" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB58" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: routeClaim(bytes[],bytes[]): DELEGATECALL at pc=9845 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC58" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD58" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE58" s="12" t="inlineStr">
+        <is>
+          <t>10210-byte runtime on optimism exposing 31 dispatched function(s): supportsInterface(bytes4), 0x08763f55, 0x0c6c9f35, routeClaim(bytes[],bytes[]), setAtomicFillSigner(address), initialized(), getRoleAdmin(bytes32), grantRole(bytes32,address), DOMAIN_SEPARATOR(), renounceRole(bytes32,address) Embedded strings mention: Router, Signed Message.
+Concern(s) found: routeClaim(bytes[],bytes[]): DELEGATECALL at pc=9845 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; 0x45197d6b: DELEGATECALL at pc=9512 to ['calldata'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; routeClaim(bytes,bytes): DELEGATECALL at pc=9845 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; 0xb51d6fdf: DELEGATECALL at pc=9512 to ['calldata'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; 0xdf2c9057: DELEGATECALL at pc=9845 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage
+Protection(s) found: self-call restriction (msg.sender == address(this)) on initialize(address) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent; signature-derived authorization branch (ecrecover) on 0xdf2c9057
+Instruction census (whole contract): ADDRESS×8, CALL×4, CALLER×17, DELEGATECALL×2, SSTORE×16, STATICCALL×3</t>
+        </is>
+      </c>
+      <c r="AF58" s="12" t="inlineStr">
+        <is>
+          <t>• supportsInterface(bytes4): no sensitive operation reachable
+• 0x08763f55: no sensitive operation reachable
+• 0x0c6c9f35: an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• routeClaim(bytes[],bytes[]): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• setAtomicFillSigner(address): an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• initialized(): no sensitive operation reachable
+• getRoleAdmin(bytes32): no sensitive operation reachable
+• grantRole(bytes32,address): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• DOMAIN_SEPARATOR(): no sensitive operation reachable
+• renounceRole(bytes32,address): every path to a sensitive operation passes an authorization check — check found: calldata_comparison; storage_condition
+• 0x45197d6b: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• initialize(address,address): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• 0x4a4d200e: an unauthenticated path to a sensitive operation exists
+• routeClaim(bytes,bytes): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• pause(): an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• eip712Domain(): no sensitive operation reachable [analysis incomplete for this function]
+• hasRole(bytes32,address): no sensitive operation reachable
+• 0x925230b0: no sensitive operation reachable
+• 0x9481639f: no sensitive operation reachable
+• 0x9f360648: no sensitive operation reachable
+• DEFAULT_ADMIN_ROLE(): no sensitive operation reachable
+• 0xb51d6fdf: an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• 0xb72ff04f: no sensitive operation reachable
+• initialize(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xd1dcdd8e6fe04c338ac3f76f7d7105becab74f77; self_call_check
+• 0xcfbf97b6: no sensitive operation reachable
+• 0xcfd4bf49: no sensitive operation reachable
+• 0xd40ba9dc: no sensitive operation reachable — check found: storage_condition
+• revokeRole(bytes32,address): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• 0xdf2c9057: an unauthenticated path to a sensitive operation exists — check found: storage_condition; signature_authorization [analysis incomplete for this function]
+• HELPER(): no sensitive operation reachable
+• 0xf7101677: an unauthenticated path to a sensitive operation exists — check found: storage_condition</t>
+        </is>
+      </c>
+      <c r="AG58" s="12" t="inlineStr">
+        <is>
+          <t>chain=optimism
+runtime size=10210 bytes
+verified source=False
+other chains with identical bytecode: ["optimism"]
+on-chain storage read during evidence collection: [{"slot": "1ec626b893ca4a4a01eaf39ec7e7bd14742f8b05d0ff7a16b9587dccde396f2c", "offset": 0, "type": "mapping(address =&gt; uint8)", "n_reads": 4, "n_writes": 2}, {"slot": "32082cf48e80a36a6bd2e8ae64f9fbe0be581fd2c37c677bd828491c7122bcf0", "offset": 0, "type": "uint8", "n_reads": 1, "n_writes": 1}, {"slo
+addresses embedded in the code: [{"bytecode_offset": 2473, "address": "0xd1dcdd8e6fe04c338ac3f76f7d7105becab74f77"}]</t>
+        </is>
+      </c>
+      <c r="AH58" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: renounceRole(bytes32,address) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0xdf2c9057, eip712Domain(), routeClaim(bytes[],bytes[]); unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: routeClaim(bytes[],bytes[]) pc=7128 -&gt; 0x27691cb6b2e1de2887d04f827fdff2fe681d92d6 (value=0, data=memory); routeClaim(bytes[],bytes[]) pc=7266 -&gt; 0xd03b5038b442341b54a3188eb4800a01e5d02f19 (value=0, data=memory); routeClaim(bytes,bytes) pc=7128 -&gt; 0x27691cb6b2e1de2887d04f827fdff2fe681d92d6 (value=0, data=memory); routeClaim(bytes,bytes) pc=7266 -&gt; 0xd03b5038b442341b54a3188eb4800a01e5d02f19 (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
@@ -8195,6 +11571,63 @@
       <c r="W59" s="9" t="inlineStr"/>
       <c r="X59" s="8" t="inlineStr"/>
       <c r="Y59" s="8" t="inlineStr"/>
+      <c r="Z59" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA59" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB59" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: createProxyWithCallback(address,bytes,uint256,address): CALL at pc=1734 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC59" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD59" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE59" s="12" t="inlineStr">
+        <is>
+          <t>3054-byte runtime on arbitrum exposing 5 dispatched function(s): createProxyWithNonce(address,bytes,uint256), getChainId(), proxyCreationCode(), createProxyWithCallback(address,bytes,uint256,address), createChainSpecificProxyWithNonce(address,bytes,uint256)
+Concern(s) found: createProxyWithCallback(address,bytes,uint256,address): CALL at pc=1734 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 2, 'CREATE2': 1, 'SSTORE': 1, 'DELEGATECALL': 1, 'STATICCALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx2, DELEGATECALLx1, CREATE2x1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×2, CREATE2×1, DELEGATECALL×1, SSTORE×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF59" s="12" t="inlineStr">
+        <is>
+          <t>• createProxyWithNonce(address,bytes,uint256): an unauthenticated path to a sensitive operation exists
+• getChainId(): no sensitive operation reachable
+• proxyCreationCode(): no sensitive operation reachable [analysis incomplete for this function]
+• createProxyWithCallback(address,bytes,uint256,address): an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• createChainSpecificProxyWithNonce(address,bytes,uint256): an unauthenticated path to a sensitive operation exists
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG59" s="12" t="inlineStr">
+        <is>
+          <t>chain=arbitrum
+runtime size=3054 bytes
+verified source=True
+other chains with identical bytecode: ["arbitrum", "base"]
+addresses embedded in the code: [{"bytecode_offset": 2975, "address": "0x696e676c65746f6e20616464726573732070726f"}]</t>
+        </is>
+      </c>
+      <c r="AH59" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'DELEGATECALL': [2890]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: createProxyWithCallback(address,bytes,uint256,address), proxyCreationCode(); unrestricted CREATE/CREATE2 at [('createProxyWithNonce(address,bytes,uint256)', 2271), ('createProxyWithCallback(address,bytes,uint256,address)', 2271), ('createChainSpecificProxyWithNonce(address,bytes,uint256)', 2271)] — a capability whose concrete risk depends on what the created contract is given authority over, which bytecode alone does not establish; unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: createProxyWithNonce(address,bytes,uint256) pc=2462 -&gt; unresolved (value=0, data=memory); createProxyWithCallback(address,bytes,uint256,address) pc=2462 -&gt; unresolved (value=0, data=memory); createChainSpecificProxyWithNonce(address,bytes,uint256) pc=2462 -&gt; unresolved (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -8322,6 +11755,65 @@
       <c r="W60" s="6" t="inlineStr"/>
       <c r="X60" s="8" t="inlineStr"/>
       <c r="Y60" s="8" t="inlineStr"/>
+      <c r="Z60" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA60" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB60" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [2351]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC60" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD60" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE60" s="12" t="inlineStr">
+        <is>
+          <t>7152-byte runtime on ethereum exposing 7 dispatched function(s): get_block_hash_257335279069929(uint256), supportsInterface(bytes4), 0x2e9d9f47, 0x7c2987ea, 0xab2f4358, 0xf4a8cdfc, uniswapV3SwapCallback(int256,int256,bytes)
+Protection(s) found: self-call restriction (msg.sender == address(this)) on 0x2e9d9f47, 0x7c2987ea, 0xf4a8cdfc, get_block_hash_257335279069929(uint256), uniswapV3SwapCallback(int256,int256,bytes) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent
+Instruction census (whole contract): ADDRESS×7, CALL×4, CALLER×8, ORIGIN×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF60" s="12" t="inlineStr">
+        <is>
+          <t>• get_block_hash_257335279069929(uint256): every path to a sensitive operation passes an authorization check — check found: self_call_check [analysis incomplete for this function]
+• supportsInterface(bytes4): no sensitive operation reachable
+• 0x2e9d9f47: no sensitive operation reachable — check found: self_call_check
+• 0x7c2987ea: every path to a sensitive operation passes an authorization check — check found: self_call_check
+• 0xab2f4358: no sensitive operation reachable
+• 0xf4a8cdfc: no sensitive operation reachable — check found: self_call_check
+• uniswapV3SwapCallback(int256,int256,bytes): every path to a sensitive operation passes an authorization check — check found: self_call_check; caller_check
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG60" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=7152 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 2031, "address": "0x1f98431c8ad98523631ae4a59f267346ea31f984"}]</t>
+        </is>
+      </c>
+      <c r="AH60" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [2351]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: get_block_hash_257335279069929(uint256)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
@@ -8449,6 +11941,59 @@
       <c r="W61" s="9" t="inlineStr"/>
       <c r="X61" s="8" t="inlineStr"/>
       <c r="Y61" s="8" t="inlineStr"/>
+      <c r="Z61" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA61" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB61" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: multicall((address,bytes,uint256)[]): SSTORE to slot 0x0 at pc=198 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC61" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD61" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE61" s="12" t="inlineStr">
+        <is>
+          <t>1365-byte runtime on base exposing 1 dispatched function(s): multicall((address,bytes,uint256)[])
+Concern(s) found: multicall((address,bytes,uint256)[]): SSTORE to slot 0x0 at pc=198 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls
+Protection(s) found: self-call restriction (msg.sender == address(this)) on multicall((address,bytes,uint256)[]) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent
+Instruction census (whole contract): ADDRESS×1, CALL×1, CALLER×2, SSTORE×2</t>
+        </is>
+      </c>
+      <c r="AF61" s="12" t="inlineStr">
+        <is>
+          <t>• multicall((address,bytes,uint256)[]): an unauthenticated path to a sensitive operation exists — check found: storage_condition; self_call_check [analysis incomplete for this function]</t>
+        </is>
+      </c>
+      <c r="AG61" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=1365 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "uint8", "n_reads": 1, "n_writes": 1}]</t>
+        </is>
+      </c>
+      <c r="AH61" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: multicall((address,bytes,uint256)[])</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -8576,6 +12121,59 @@
       <c r="W62" s="6" t="inlineStr"/>
       <c r="X62" s="8" t="inlineStr"/>
       <c r="Y62" s="8" t="inlineStr"/>
+      <c r="Z62" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA62" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB62" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: collectERC20(address,uint256): msg.sender must equal the hardcoded address 0xbd1eec68f8af17f40391fb8e3a259e174aa25f98. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC62" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD62" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE62" s="12" t="inlineStr">
+        <is>
+          <t>1707-byte runtime on arbitrum exposing 3 dispatched function(s): collectERC20(address,uint256), tokenReceived(address,uint256,bytes), collectETH(uint256)
+Concern(s) found: collectERC20(address,uint256): msg.sender must equal the hardcoded address 0xbd1eec68f8af17f40391fb8e3a259e174aa25f98. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; collectETH(uint256): msg.sender must equal the hardcoded address 0xbd1eec68f8af17f40391fb8e3a259e174aa25f98. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×2, CALLER×3</t>
+        </is>
+      </c>
+      <c r="AF62" s="12" t="inlineStr">
+        <is>
+          <t>• collectERC20(address,uint256): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xbd1eec68f8af17f40391fb8e3a259e174aa25f98
+• tokenReceived(address,uint256,bytes): no sensitive operation reachable
+• collectETH(uint256): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xbd1eec68f8af17f40391fb8e3a259e174aa25f98</t>
+        </is>
+      </c>
+      <c r="AG62" s="12" t="inlineStr">
+        <is>
+          <t>chain=arbitrum
+runtime size=1707 bytes
+verified source=False
+other chains with identical bytecode: ["arbitrum"]</t>
+        </is>
+      </c>
+      <c r="AH62" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
@@ -8703,6 +12301,57 @@
       <c r="W63" s="9" t="inlineStr"/>
       <c r="X63" s="8" t="inlineStr"/>
       <c r="Y63" s="8" t="inlineStr"/>
+      <c r="Z63" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA63" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB63" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [481]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC63" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD63" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE63" s="12" t="inlineStr">
+        <is>
+          <t>2262-byte runtime on ethereum exposing 1 dispatched function(s): 0xe5f454c8
+Instruction census (whole contract): CALL×1, CALLER×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF63" s="12" t="inlineStr">
+        <is>
+          <t>• 0xe5f454c8: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG63" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=2262 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH63" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [481]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
@@ -8830,6 +12479,69 @@
       <c r="W64" s="6" t="inlineStr"/>
       <c r="X64" s="8" t="inlineStr"/>
       <c r="Y64" s="8" t="inlineStr"/>
+      <c r="Z64" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA64" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB64" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x0c0bf4c1: CALL at pc=544 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC64" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD64" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE64" s="12" t="inlineStr">
+        <is>
+          <t>6087-byte runtime on base exposing 10 dispatched function(s): 0x0c0bf4c1, addVault(address), 0x52312364, vaults(uint256), factoryAddress(), getVaultsCount(), _factory(), removeVault(uint256), transferOwnership(address), getVaultData()
+Concern(s) found: 0x0c0bf4c1: CALL at pc=544 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call
+Protection(s) found: msg.sender compared against a stored authority on addVault(address), removeVault(uint256), transferOwnership(address)
+Instruction census (whole contract): CALL×3, CALLER×3, ORIGIN×3, SSTORE×7, STATICCALL×11</t>
+        </is>
+      </c>
+      <c r="AF64" s="12" t="inlineStr">
+        <is>
+          <t>• 0x0c0bf4c1: an unauthenticated path to a sensitive operation exists
+• addVault(address): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• 0x52312364: no sensitive operation reachable
+• vaults(uint256): no sensitive operation reachable — check found: storage_condition
+• factoryAddress(): no sensitive operation reachable
+• getVaultsCount(): no sensitive operation reachable
+• _factory(): no sensitive operation reachable
+• removeVault(uint256): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• transferOwnership(address): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• getVaultData(): no sensitive operation reachable — check found: storage_condition; storage_condition
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG64" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=6087 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 1, "n_writes": 0}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "address[]", "n_reads": 3, "n_writes": 2}, {"slot": "000000000</t>
+        </is>
+      </c>
+      <c r="AH64" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [973, 1068]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
@@ -8957,6 +12669,57 @@
       <c r="W65" s="9" t="inlineStr"/>
       <c r="X65" s="8" t="inlineStr"/>
       <c r="Y65" s="8" t="inlineStr"/>
+      <c r="Z65" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA65" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB65" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: callTarget(address,bytes): CALL at pc=115 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC65" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD65" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE65" s="12" t="inlineStr">
+        <is>
+          <t>788-byte runtime on bnb exposing 1 dispatched function(s): callTarget(address,bytes)
+Concern(s) found: callTarget(address,bytes): CALL at pc=115 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×1</t>
+        </is>
+      </c>
+      <c r="AF65" s="12" t="inlineStr">
+        <is>
+          <t>• callTarget(address,bytes): an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG65" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=788 bytes
+verified source=True
+other chains with identical bytecode: ["bnb"]</t>
+        </is>
+      </c>
+      <c r="AH65" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -9084,6 +12847,78 @@
       <c r="W66" s="6" t="inlineStr"/>
       <c r="X66" s="8" t="inlineStr"/>
       <c r="Y66" s="8" t="inlineStr"/>
+      <c r="Z66" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA66" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB66" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x0a5491b4: msg.sender must equal the hardcoded address 0x0bb9ad9357565a592668e6c41463b05a17c68a09. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC66" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD66" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE66" s="12" t="inlineStr">
+        <is>
+          <t>14003-byte runtime on bnb exposing 19 dispatched function(s): 0x0a5491b4, token0(), 0x116210c6, poolAddress(), 0x241e4344, 0x2d803566, 0x2e24f896, withdraw(), lastTick(), 0x5b5dc217 Embedded strings mention: Not owner, not owner.
+Concern(s) found: 0x0a5491b4: msg.sender must equal the hardcoded address 0x0bb9ad9357565a592668e6c41463b05a17c68a09. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x241e4344: msg.sender must equal the hardcoded address 0x0bb9ad9357565a592668e6c41463b05a17c68a09. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; withdraw(): msg.sender must equal the hardcoded address 0x0bb9ad9357565a592668e6c41463b05a17c68a09. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; withdrawToken(address): msg.sender must equal the hardcoded address 0x0bb9ad9357565a592668e6c41463b05a17c68a09. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; setPoolAddress(address): msg.sender must equal the hardcoded address 0x0bb9ad9357565a592668e6c41463b05a17c68a09. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x2e24f896: SSTORE to slot 0x2 at pc=7408 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x2e24f896: SSTORE to slot 0x2 at pc=7442 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x2e24f896: SSTORE to slot 0x2 at pc=7554 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x5b5dc217: SSTORE to slot 0x3 at pc=3932 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x5b5dc217: SSTORE to slot 0x2 at pc=7408 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x5b5dc217: SSTORE to slot 0x2 at pc=7442 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x5b5dc217: SSTORE to slot 0x2 at pc=7554 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls
+Protection(s) found: callback entry point(s) restricted to a fixed protocol address: pancakeV3MintCallback(uint256,uint256,bytes) — pancakeV3MintCallback(uint256,uint256,bytes) is a callback-shaped entry point restricted to the fixed address 0x0bb9ad9357565a592668e6c41463b05a17c68a09; a callback is invoked by a protocol during an operation the account itself started, so this reads as the protocol's prescribed restriction rather than standing third-party access. The identity of 0x0bb9ad9357565a592668e6c41463b05a17c68a09 was not independently confirmed.; msg.sender compared against a stored authority on pancakeV3MintCallback(uint256,uint256,bytes)
+Instruction census (whole contract): ADDRESS×9, CALL×11, CALLER×6, ORIGIN×1, SSTORE×11, STATICCALL×13</t>
+        </is>
+      </c>
+      <c r="AF66" s="12" t="inlineStr">
+        <is>
+          <t>• 0x0a5491b4: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0bb9ad9357565a592668e6c41463b05a17c68a09; storage_condition
+• token0(): no sensitive operation reachable
+• 0x116210c6: no sensitive operation reachable
+• poolAddress(): no sensitive operation reachable
+• 0x241e4344: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0bb9ad9357565a592668e6c41463b05a17c68a09
+• 0x2d803566: no sensitive operation reachable
+• 0x2e24f896: an unauthenticated path to a sensitive operation exists — check found: hardcoded_address_check against 0x0bb9ad9357565a592668e6c41463b05a17c68a09; storage_condition [analysis incomplete for this function]
+• withdraw(): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0bb9ad9357565a592668e6c41463b05a17c68a09
+• lastTick(): no sensitive operation reachable
+• 0x5b5dc217: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• 0x69dd9807: no sensitive operation reachable — check found: storage_condition
+• 0x85eda707: no sensitive operation reachable
+• withdrawToken(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0bb9ad9357565a592668e6c41463b05a17c68a09
+• isStop(): no sensitive operation reachable
+• pancakeV3MintCallback(uint256,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; hardcoded_address_check against 0x0bb9ad9357565a592668e6c41463b05a17c68a09
+• 0xc1ea76d7: no sensitive operation reachable [analysis incomplete for this function]
+• tickSpacing(): no sensitive operation reachable
+• token1(): no sensitive operation reachable
+• setPoolAddress(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0bb9ad9357565a592668e6c41463b05a17c68a09; storage_condition
+• COVERAGE GAP: the analysis never reached 4 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG66" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=14003 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 7, "n_writes": 1}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "address", "n_reads": 5, "n_writes": 1}, {"slot": "00000000000</t>
+        </is>
+      </c>
+      <c r="AH66" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: 0x0a5491b4 (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); 0x0a5491b4 (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); 0x0a5491b4 (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); 0x0a5491b4 (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [3112, 5750, 7100, 7320]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x2e24f896, 0x5b5dc217, 0xc1ea76d7; unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: 0x2e24f896 pc=2905 -&gt; stored(sload) (value=0, data=memory); 0x2e24f896 pc=7753 -&gt; stored(sload) (value=0, data=memory); 0x5b5dc217 pc=7753 -&gt; stored(sload) (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
@@ -9211,6 +13046,69 @@
       <c r="W67" s="9" t="inlineStr"/>
       <c r="X67" s="8" t="inlineStr"/>
       <c r="Y67" s="8" t="inlineStr"/>
+      <c r="Z67" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA67" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB67" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x0a5491b4: msg.sender must equal the hardcoded address 0x0bb9ad9357565a592668e6c41463b05a17c68a09. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC67" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD67" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE67" s="12" t="inlineStr">
+        <is>
+          <t>7064-byte runtime on bnb exposing 11 dispatched function(s): 0x0a5491b4, token0(), poolAddress(), 0x2e24f896, 0x5b5dc217, 0x69dd9807, positionInfo(), pancakeV3MintCallback(uint256,uint256,bytes), 0xcab2e64e, token1()
+Concern(s) found: 0x0a5491b4: msg.sender must equal the hardcoded address 0x0bb9ad9357565a592668e6c41463b05a17c68a09. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0xcab2e64e: msg.sender must equal the hardcoded address 0x0bb9ad9357565a592668e6c41463b05a17c68a09. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; setPoolAddress(address): msg.sender must equal the hardcoded address 0x0bb9ad9357565a592668e6c41463b05a17c68a09. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x2e24f896: SSTORE to slot 0x3 at pc=3452 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x2e24f896: SSTORE to slot 0x3 at pc=3489 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x2e24f896: SSTORE to slot 0x3 at pc=3532 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x2e24f896: SSTORE to slot 0x3 at pc=3579 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x2e24f896: SSTORE to slot 0x3 at pc=3619 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x5b5dc217: SSTORE to slot 0x3 at pc=3452 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x5b5dc217: SSTORE to slot 0x3 at pc=3489 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x5b5dc217: SSTORE to slot 0x3 at pc=3532 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x5b5dc217: SSTORE to slot 0x3 at pc=3579 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x5b5dc217: SSTORE to slot 0x3 at pc=3619 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls
+Protection(s) found: msg.sender compared against a stored authority on pancakeV3MintCallback(uint256,uint256,bytes)
+Instruction census (whole contract): ADDRESS×9, CALL×5, CALLER×4, SSTORE×13, STATICCALL×10</t>
+        </is>
+      </c>
+      <c r="AF67" s="12" t="inlineStr">
+        <is>
+          <t>• 0x0a5491b4: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0bb9ad9357565a592668e6c41463b05a17c68a09; storage_condition
+• token0(): no sensitive operation reachable
+• poolAddress(): no sensitive operation reachable
+• 0x2e24f896: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• 0x5b5dc217: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• 0x69dd9807: no sensitive operation reachable — check found: storage_condition; storage_condition
+• positionInfo(): no sensitive operation reachable
+• pancakeV3MintCallback(uint256,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_condition
+• 0xcab2e64e: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0bb9ad9357565a592668e6c41463b05a17c68a09
+• token1(): no sensitive operation reachable
+• setPoolAddress(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0bb9ad9357565a592668e6c41463b05a17c68a09</t>
+        </is>
+      </c>
+      <c r="AG67" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=7064 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 6, "n_writes": 2}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "address", "n_reads": 5, "n_writes": 2}, {"slot": "00000000000</t>
+        </is>
+      </c>
+      <c r="AH67" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: 0x0a5491b4 (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); 0x0a5491b4 (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); 0x0a5491b4 (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x2e24f896, 0x5b5dc217; unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: 0x2e24f896 pc=3757 -&gt; stored(sload) (value=0, data=memory); 0x2e24f896 pc=3840 -&gt; stored(sload) (value=0, data=memory); 0x2e24f896 pc=4415 -&gt; stored(sload) (value=0, data=memory); 0x5b5dc217 pc=4415 -&gt; stored(sload) (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -9338,6 +13236,62 @@
       <c r="W68" s="6" t="inlineStr"/>
       <c r="X68" s="8" t="inlineStr"/>
       <c r="Y68" s="8" t="inlineStr"/>
+      <c r="Z68" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA68" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB68" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: transferTokenTo(address,address,uint256) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); execute(address,bytes) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); 0x71e07d9b (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); 0x914d910a (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined) The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC68" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD68" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE68" s="12" t="inlineStr">
+        <is>
+          <t>3910-byte runtime on ethereum exposing 6 dispatched function(s): transferTokenTo(address,address,uint256), execute(address,bytes), contains(address[],address), 0x71e07d9b, 0x914d910a, 0xa225bd4c
+Instruction census (whole contract): ADDRESS×3, CALL×6, CALLER×6, STATICCALL×4</t>
+        </is>
+      </c>
+      <c r="AF68" s="12" t="inlineStr">
+        <is>
+          <t>• transferTokenTo(address,address,uint256): every path to a sensitive operation passes an authorization check — check found: caller_check [analysis incomplete for this function]
+• execute(address,bytes): every path to a sensitive operation passes an authorization check — check found: caller_check [analysis incomplete for this function]
+• contains(address[],address): no sensitive operation reachable [analysis incomplete for this function]
+• 0x71e07d9b: every path to a sensitive operation passes an authorization check — check found: caller_check [analysis incomplete for this function]
+• 0x914d910a: every path to a sensitive operation passes an authorization check — check found: caller_check [analysis incomplete for this function]
+• 0xa225bd4c: every path to a sensitive operation passes an authorization check — check found: caller_check [analysis incomplete for this function]</t>
+        </is>
+      </c>
+      <c r="AG68" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=3910 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 291, "address": "0x9a46823a51dc134eec255ff63481543675b97e91"}, {"bytecode_offset": 362, "address": "0xd060d168fa75ce8ecda305873627bb9b78cd56cd"}]</t>
+        </is>
+      </c>
+      <c r="AH68" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: transferTokenTo(address,address,uint256) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); execute(address,bytes) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); 0x71e07d9b (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); 0x914d910a (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x71e07d9b, 0x914d910a, 0xa225bd4c, contains(address[],address), execute(address,bytes), transferTokenTo(address,address,uint256)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
@@ -9465,6 +13419,67 @@
       <c r="W69" s="9" t="inlineStr"/>
       <c r="X69" s="8" t="inlineStr"/>
       <c r="Y69" s="8" t="inlineStr"/>
+      <c r="Z69" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA69" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB69" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: increaseAllowance(address,uint256) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); decreaseAllowance(address,uint256) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); transfer(address,uint256) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); transfer(address,uint256) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)) The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC69" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD69" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE69" s="12" t="inlineStr">
+        <is>
+          <t>5025-byte runtime on base exposing 11 dispatched function(s): name(), approve(address,uint256), totalSupply(), transferFrom(address,address,uint256), decimals(), increaseAllowance(address,uint256), balanceOf(address), symbol(), decreaseAllowance(address,uint256), transfer(address,uint256)
+Instruction census (whole contract): CALLER×2, SSTORE×3</t>
+        </is>
+      </c>
+      <c r="AF69" s="12" t="inlineStr">
+        <is>
+          <t>• name(): no sensitive operation reachable — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• approve(address,uint256): every path to a sensitive operation passes an authorization check — check found: zero_address_check against 0x0000000000000000000000000000000000000000
+• totalSupply(): no sensitive operation reachable
+• transferFrom(address,address,uint256): no sensitive operation reachable
+• decimals(): no sensitive operation reachable
+• increaseAllowance(address,uint256): every path to a sensitive operation passes an authorization check — check found: zero_address_check against 0x0000000000000000000000000000000000000000; storage_condition
+• balanceOf(address): no sensitive operation reachable
+• symbol(): no sensitive operation reachable — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• decreaseAllowance(address,uint256): every path to a sensitive operation passes an authorization check — check found: storage_condition; zero_address_check against 0x0000000000000000000000000000000000000000
+• transfer(address,uint256): every path to a sensitive operation passes an authorization check — check found: zero_address_check against 0x0000000000000000000000000000000000000000; storage_condition
+• allowance(address,address): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG69" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=5025 bytes
+verified source=True
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "mapping(address =&gt; uint256)", "n_reads": 3, "n_writes": 2}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "mapping(address =&gt; mapping(address =&gt; uin</t>
+        </is>
+      </c>
+      <c r="AH69" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: increaseAllowance(address,uint256) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); decreaseAllowance(address,uint256) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); transfer(address,uint256) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); transfer(address,uint256) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: name(), symbol()</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -9592,6 +13607,75 @@
       <c r="W70" s="6" t="inlineStr"/>
       <c r="X70" s="8" t="inlineStr"/>
       <c r="Y70" s="8" t="inlineStr"/>
+      <c r="Z70" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA70" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB70" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x1a6c11dc: CALL at pc=8263 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC70" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD70" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE70" s="12" t="inlineStr">
+        <is>
+          <t>11133-byte runtime on base exposing 18 dispatched function(s): supportsInterface(bytes4), 0x1a6c11dc, 0x299ed167, 0x2ab11a7a, 0x5817ebe4, 0x67ba0b80, 0x762d0698, 0x7b6eb5f4, 0x853c3f38, 0x8d32bb2d
+Concern(s) found: 0x1a6c11dc: CALL at pc=8263 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0x1a6c11dc: CALL at pc=8380 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0x8d32bb2d: CALL at pc=8263 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0x8d32bb2d: CALL at pc=8380 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0xb58dedbf: CALL at pc=8263 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0xb58dedbf: CALL at pc=8380 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0x67ba0b80: msg.sender must equal the hardcoded address 0xb3fcb766efa166492522e4861c9f84a147b09eaf. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×1, CALL×9, CALLER×3, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF70" s="12" t="inlineStr">
+        <is>
+          <t>• supportsInterface(bytes4): no sensitive operation reachable
+• 0x1a6c11dc: an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• 0x299ed167: no sensitive operation reachable [analysis incomplete for this function]
+• 0x2ab11a7a: no sensitive operation reachable [analysis incomplete for this function]
+• 0x5817ebe4: no sensitive operation reachable
+• 0x67ba0b80: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xb3fcb766efa166492522e4861c9f84a147b09eaf [analysis incomplete for this function]
+• 0x762d0698: no sensitive operation reachable [analysis incomplete for this function]
+• 0x7b6eb5f4: no sensitive operation reachable
+• 0x853c3f38: no sensitive operation reachable
+• 0x8d32bb2d: an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• ARBITER(): no sensitive operation reachable
+• 0x98e4439a: no sensitive operation reachable
+• 0xb1bb5bc1: no sensitive operation reachable
+• 0xb58dedbf: an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• 0xc6308ff7: no sensitive operation reachable
+• 0xc6445e16: no sensitive operation reachable [analysis incomplete for this function]
+• 0xc85d92c2: no sensitive operation reachable
+• 0xd5e961d6: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG70" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=11133 bytes
+verified source=False
+other chains with identical bytecode: ["base"]</t>
+        </is>
+      </c>
+      <c r="AH70" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [10274]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x1a6c11dc, 0x299ed167, 0x2ab11a7a, 0x67ba0b80, 0x762d0698, 0x8d32bb2d, 0xb58dedbf, 0xc6445e16; unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: 0x1a6c11dc pc=8018 -&gt; 0xfcf17ec1b84f1031a3fc9dca992b82fc927113a9 (value=0, data=memory); 0x8d32bb2d pc=1669 -&gt; 0x000000000022d473030f116ddee9f6b43ac78ba3 (value=0, data=memory); 0x8d32bb2d pc=8018 -&gt; 0xfcf17ec1b84f1031a3fc9dca992b82fc927113a9 (value=0, data=memory); 0xb58dedbf pc=8018 -&gt; 0xfcf17ec1b84f1031a3fc9dca992b82fc927113a9 (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
@@ -9719,6 +13803,78 @@
       <c r="W71" s="9" t="inlineStr"/>
       <c r="X71" s="8" t="inlineStr"/>
       <c r="Y71" s="8" t="inlineStr"/>
+      <c r="Z71" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA71" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB71" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: withdrawETH(address,uint256): CALL at pc=1416 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC71" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD71" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE71" s="12" t="inlineStr">
+        <is>
+          <t>5940-byte runtime on base exposing 18 dispatched function(s): supportsInterface(bytes4), EXECUTOR_ROLE(), getRoleAdmin(bytes32), grantRole(bytes32,address), renounceRole(bytes32,address), unpause(), 0x45ef041f, withdrawETH(address,uint256), paused(), rescueERC721(address,address,uint256) Embedded strings mention: Executor, not authorized.
+Concern(s) found: withdrawETH(address,uint256): CALL at pc=1416 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; rescueERC721(address,address,uint256): CALL at pc=1198 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; rescueERC20(address,address,uint256): CALL at pc=561 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; unpause(): SSTORE to slot 0x1 at pc=2956 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x45ef041f: SSTORE to slot 0x2 at pc=5837 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; pause(): SSTORE to slot 0x1 at pc=908 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; batchTransactions(uint256[],address[],bytes[]): SSTORE to slot 0x2 at pc=4133 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; batchTransactions(uint256[],address[],bytes[]): SSTORE to slot 0x2 at pc=5837 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls
+Protection(s) found: signature-derived authorization branch (ecrecover) on 0x45ef041f
+Instruction census (whole contract): ADDRESS×3, CALL×4, CALLER×13, SSTORE×9, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF71" s="12" t="inlineStr">
+        <is>
+          <t>• supportsInterface(bytes4): no sensitive operation reachable
+• EXECUTOR_ROLE(): no sensitive operation reachable
+• getRoleAdmin(bytes32): no sensitive operation reachable
+• grantRole(bytes32,address): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• renounceRole(bytes32,address): every path to a sensitive operation passes an authorization check — check found: calldata_comparison; storage_condition
+• unpause(): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• 0x45ef041f: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• withdrawETH(address,uint256): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• paused(): no sensitive operation reachable
+• rescueERC721(address,address,uint256): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• nonces(address): no sensitive operation reachable
+• grantExecutorRole(address): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• pause(): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• hasRole(bytes32,address): no sensitive operation reachable
+• DEFAULT_ADMIN_ROLE(): no sensitive operation reachable
+• rescueERC20(address,address,uint256): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• batchTransactions(uint256[],address[],bytes[]): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• revokeRole(bytes32,address): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG71" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=5940 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "mapping(uint256 =&gt; mapping(address =&gt; bool))", "n_reads": 6, "n_writes": 3}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "bool", "n_reads": 7, "n_
+addresses embedded in the code: [{"bytecode_offset": 1503, "address": "0x496e73756666696369656e742062616c616e6365"}]</t>
+        </is>
+      </c>
+      <c r="AH71" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: renounceRole(bytes32,address) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [4288]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x45ef041f, batchTransactions(uint256[],address[],bytes[])</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -9846,6 +14002,90 @@
       <c r="W72" s="6" t="inlineStr"/>
       <c r="X72" s="8" t="inlineStr"/>
       <c r="Y72" s="8" t="inlineStr"/>
+      <c r="Z72" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA72" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB72" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: routeClaim(bytes[],bytes[]): DELEGATECALL at pc=9845 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC72" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD72" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE72" s="12" t="inlineStr">
+        <is>
+          <t>10210-byte runtime on base exposing 31 dispatched function(s): supportsInterface(bytes4), 0x08763f55, 0x0c6c9f35, routeClaim(bytes[],bytes[]), setAtomicFillSigner(address), initialized(), getRoleAdmin(bytes32), grantRole(bytes32,address), DOMAIN_SEPARATOR(), renounceRole(bytes32,address) Embedded strings mention: Router, Signed Message.
+Concern(s) found: routeClaim(bytes[],bytes[]): DELEGATECALL at pc=9845 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; 0x45197d6b: DELEGATECALL at pc=9512 to ['calldata'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; routeClaim(bytes,bytes): DELEGATECALL at pc=9845 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; 0xb51d6fdf: DELEGATECALL at pc=9512 to ['calldata'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; 0xdf2c9057: DELEGATECALL at pc=9845 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage
+Protection(s) found: self-call restriction (msg.sender == address(this)) on initialize(address) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent; signature-derived authorization branch (ecrecover) on 0xdf2c9057
+Instruction census (whole contract): ADDRESS×8, CALL×4, CALLER×17, DELEGATECALL×2, SSTORE×16, STATICCALL×3</t>
+        </is>
+      </c>
+      <c r="AF72" s="12" t="inlineStr">
+        <is>
+          <t>• supportsInterface(bytes4): no sensitive operation reachable
+• 0x08763f55: no sensitive operation reachable
+• 0x0c6c9f35: an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• routeClaim(bytes[],bytes[]): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• setAtomicFillSigner(address): an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• initialized(): no sensitive operation reachable
+• getRoleAdmin(bytes32): no sensitive operation reachable
+• grantRole(bytes32,address): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• DOMAIN_SEPARATOR(): no sensitive operation reachable
+• renounceRole(bytes32,address): every path to a sensitive operation passes an authorization check — check found: calldata_comparison; storage_condition
+• 0x45197d6b: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• initialize(address,address): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• 0x4a4d200e: an unauthenticated path to a sensitive operation exists
+• routeClaim(bytes,bytes): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• pause(): an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• eip712Domain(): no sensitive operation reachable [analysis incomplete for this function]
+• hasRole(bytes32,address): no sensitive operation reachable
+• 0x925230b0: no sensitive operation reachable
+• 0x9481639f: no sensitive operation reachable
+• 0x9f360648: no sensitive operation reachable
+• DEFAULT_ADMIN_ROLE(): no sensitive operation reachable
+• 0xb51d6fdf: an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• 0xb72ff04f: no sensitive operation reachable
+• initialize(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xd1dcdd8e6fe04c338ac3f76f7d7105becab74f77; self_call_check
+• 0xcfbf97b6: no sensitive operation reachable
+• 0xcfd4bf49: no sensitive operation reachable
+• 0xd40ba9dc: no sensitive operation reachable — check found: storage_condition
+• revokeRole(bytes32,address): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• 0xdf2c9057: an unauthenticated path to a sensitive operation exists — check found: storage_condition; signature_authorization [analysis incomplete for this function]
+• HELPER(): no sensitive operation reachable
+• 0xf7101677: an unauthenticated path to a sensitive operation exists — check found: storage_condition</t>
+        </is>
+      </c>
+      <c r="AG72" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=10210 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "1ec626b893ca4a4a01eaf39ec7e7bd14742f8b05d0ff7a16b9587dccde396f2c", "offset": 0, "type": "mapping(address =&gt; uint8)", "n_reads": 4, "n_writes": 2}, {"slot": "32082cf48e80a36a6bd2e8ae64f9fbe0be581fd2c37c677bd828491c7122bcf0", "offset": 0, "type": "uint8", "n_reads": 1, "n_writes": 1}, {"slo
+addresses embedded in the code: [{"bytecode_offset": 2473, "address": "0xd1dcdd8e6fe04c338ac3f76f7d7105becab74f77"}]</t>
+        </is>
+      </c>
+      <c r="AH72" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: renounceRole(bytes32,address) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0xdf2c9057, eip712Domain(), routeClaim(bytes[],bytes[]); unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: routeClaim(bytes[],bytes[]) pc=7128 -&gt; 0x4be2637f7149b95719311ed0141e08371d02687a (value=0, data=memory); routeClaim(bytes[],bytes[]) pc=7266 -&gt; 0xb4029eb5ba35415edc537b9ed11bc2cd4ac11315 (value=0, data=memory); routeClaim(bytes,bytes) pc=7128 -&gt; 0x4be2637f7149b95719311ed0141e08371d02687a (value=0, data=memory); routeClaim(bytes,bytes) pc=7266 -&gt; 0xb4029eb5ba35415edc537b9ed11bc2cd4ac11315 (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
@@ -9973,6 +14213,58 @@
       <c r="W73" s="9" t="inlineStr"/>
       <c r="X73" s="8" t="inlineStr"/>
       <c r="Y73" s="8" t="inlineStr"/>
+      <c r="Z73" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA73" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB73" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: execute((bytes,address,uint256)[]): tx.origin must equal the hardcoded address 0x4ccd02690d32e2512fc99dfd837972597e522c2b. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC73" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD73" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE73" s="12" t="inlineStr">
+        <is>
+          <t>988-byte runtime on polygon exposing 1 dispatched function(s): execute((bytes,address,uint256)[])
+Concern(s) found: execute((bytes,address,uint256)[]): tx.origin must equal the hardcoded address 0x4ccd02690d32e2512fc99dfd837972597e522c2b. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×1, CALLER×1, ORIGIN×1</t>
+        </is>
+      </c>
+      <c r="AF73" s="12" t="inlineStr">
+        <is>
+          <t>• execute((bytes,address,uint256)[]): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x4ccd02690d32e2512fc99dfd837972597e522c2b</t>
+        </is>
+      </c>
+      <c r="AG73" s="12" t="inlineStr">
+        <is>
+          <t>chain=polygon
+runtime size=988 bytes
+verified source=False
+other chains with identical bytecode: ["polygon"]
+addresses embedded in the code: [{"bytecode_offset": 65, "address": "0x4ccd02690d32e2512fc99dfd837972597e522c2b"}]</t>
+        </is>
+      </c>
+      <c r="AH73" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
@@ -10100,6 +14392,58 @@
       <c r="W74" s="6" t="inlineStr"/>
       <c r="X74" s="8" t="inlineStr"/>
       <c r="Y74" s="8" t="inlineStr"/>
+      <c r="Z74" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA74" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB74" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: msg.sender compared against a stored authority on 0x64e4251e The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC74" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD74" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE74" s="12" t="inlineStr">
+        <is>
+          <t>1352-byte runtime on optimism exposing 1 dispatched function(s): 0x64e4251e
+Protection(s) found: msg.sender compared against a stored authority on 0x64e4251e
+Instruction census (whole contract): CALL×2, CALLER×2, ORIGIN×2, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF74" s="12" t="inlineStr">
+        <is>
+          <t>• 0x64e4251e: every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_condition</t>
+        </is>
+      </c>
+      <c r="AG74" s="12" t="inlineStr">
+        <is>
+          <t>chain=optimism
+runtime size=1352 bytes
+verified source=False
+other chains with identical bytecode: ["optimism"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 1, "n_writes": 0}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "address", "n_reads": 1, "n_writes": 0}, {"slot": "00000000000</t>
+        </is>
+      </c>
+      <c r="AH74" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
@@ -10227,6 +14571,58 @@
       <c r="W75" s="9" t="inlineStr"/>
       <c r="X75" s="8" t="inlineStr"/>
       <c r="Y75" s="8" t="inlineStr"/>
+      <c r="Z75" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA75" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB75" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [507]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC75" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD75" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE75" s="12" t="inlineStr">
+        <is>
+          <t>2914-byte runtime on base exposing 2 dispatched function(s): 0x4053ac31, initialize()
+Instruction census (whole contract): ADDRESS×1, CALL×1, CALLER×4</t>
+        </is>
+      </c>
+      <c r="AF75" s="12" t="inlineStr">
+        <is>
+          <t>• 0x4053ac31: no sensitive operation reachable
+• initialize(): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG75" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=2914 bytes
+verified source=False
+other chains with identical bytecode: ["base"]</t>
+        </is>
+      </c>
+      <c r="AH75" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [507]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
@@ -10354,6 +14750,57 @@
       <c r="W76" s="6" t="inlineStr"/>
       <c r="X76" s="8" t="inlineStr"/>
       <c r="Y76" s="8" t="inlineStr"/>
+      <c r="Z76" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA76" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB76" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'SELFDESTRUCT': [856]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONTRADICTED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC76" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONTRADICTED</t>
+        </is>
+      </c>
+      <c r="AD76" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: The source analyzer did not flag this contract, yet an external call is reachable from the receive()/fallback() path without passing any caller authorization branch. `unflagged` is a weak signal by construction — the negatives in this dataset are rule-silent, never benignity-verified — so this is a plausible source-rule miss rather than a contradiction of a positive finding.</t>
+        </is>
+      </c>
+      <c r="AE76" s="12" t="inlineStr">
+        <is>
+          <t>871-byte runtime on ethereum exposing 1 dispatched function(s): recipient()
+Instruction census (whole contract): CALL×2, CALLER×1, SELFDESTRUCT×1, SSTORE×1</t>
+        </is>
+      </c>
+      <c r="AF76" s="12" t="inlineStr">
+        <is>
+          <t>• recipient(): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG76" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=871 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH76" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'SELFDESTRUCT': [856]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
@@ -10481,6 +14928,67 @@
       <c r="W77" s="9" t="inlineStr"/>
       <c r="X77" s="8" t="inlineStr"/>
       <c r="Y77" s="8" t="inlineStr"/>
+      <c r="Z77" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA77" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB77" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: sendNative(address,uint256): CALL at pc=881 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC77" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD77" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE77" s="12" t="inlineStr">
+        <is>
+          <t>4026-byte runtime on bnb exposing 10 dispatched function(s): name(), approve(address,uint256), totalSupply(), transferFrom(address,address,uint256), decimals(), sendNative(address,uint256), balanceOf(address), symbol(), 0xd01a4e61, allowance(address,address) Embedded strings mention: Executor.
+Concern(s) found: sendNative(address,uint256): CALL at pc=881 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0xd01a4e61: CALL at pc=1299 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call
+Instruction census (whole contract): CALL×3, CALLCODE×1, CALLER×1</t>
+        </is>
+      </c>
+      <c r="AF77" s="12" t="inlineStr">
+        <is>
+          <t>• name(): no sensitive operation reachable
+• approve(address,uint256): no sensitive operation reachable
+• totalSupply(): no sensitive operation reachable
+• transferFrom(address,address,uint256): no sensitive operation reachable
+• decimals(): no sensitive operation reachable
+• sendNative(address,uint256): an unauthenticated path to a sensitive operation exists
+• balanceOf(address): no sensitive operation reachable
+• symbol(): no sensitive operation reachable
+• 0xd01a4e61: an unauthenticated path to a sensitive operation exists
+• allowance(address,address): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG77" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=4026 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]</t>
+        </is>
+      </c>
+      <c r="AH77" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [3993], 'CALLCODE': [4002]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
@@ -10608,6 +15116,69 @@
       <c r="W78" s="6" t="inlineStr"/>
       <c r="X78" s="8" t="inlineStr"/>
       <c r="Y78" s="8" t="inlineStr"/>
+      <c r="Z78" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA78" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB78" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x62a29564: msg.sender must equal the hardcoded address 0x0e1730aab680245971603f9edeaa0c85ebeaaaaa. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC78" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD78" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE78" s="12" t="inlineStr">
+        <is>
+          <t>3301-byte runtime on arbitrum exposing 10 dispatched function(s): 0x137bdcf2, 0x3257384d, 0x369c1082, 0x62a29564, 0x729650a6, nonces(address), nonce(), 0xb4902387, 0xee5d6a12, 0xf9e1dea5 Embedded strings mention: Signed Message.
+Concern(s) found: 0x62a29564: msg.sender must equal the hardcoded address 0x0e1730aab680245971603f9edeaa0c85ebeaaaaa. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Protection(s) found: signature-derived authorization branch (ecrecover) on 0x369c1082, 0x729650a6
+Instruction census (whole contract): ADDRESS×6, CALL×1, CALLER×10, SSTORE×5, STATICCALL×2</t>
+        </is>
+      </c>
+      <c r="AF78" s="12" t="inlineStr">
+        <is>
+          <t>• 0x137bdcf2: no sensitive operation reachable
+• 0x3257384d: no sensitive operation reachable
+• 0x369c1082: no sensitive operation reachable — check found: signature_authorization
+• 0x62a29564: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0e1730aab680245971603f9edeaa0c85ebeaaaaa; storage_condition
+• 0x729650a6: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0e1730aab680245971603f9edeaa0c85ebeaaaaa; storage_condition
+• nonces(address): no sensitive operation reachable
+• nonce(): no sensitive operation reachable
+• 0xb4902387: no sensitive operation reachable
+• 0xee5d6a12: no sensitive operation reachable — check found: storage_condition
+• 0xf9e1dea5: no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG78" s="12" t="inlineStr">
+        <is>
+          <t>chain=arbitrum
+runtime size=3301 bytes
+verified source=False
+other chains with identical bytecode: ["arbitrum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "mapping(address =&gt; uint256)", "n_reads": 5, "n_writes": 2}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "mapping(address =&gt; uint256)", "n_reads": 
+addresses embedded in the code: [{"bytecode_offset": 178, "address": "0x0e1730aab680245971603f9edeaa0c85ebeaaaaa"}, {"bytecode_offset": 1393, "address": "0x2ab730baba3437b934bd32b21039b837b739b7b9"}, {"bytecode_offset": 2625, "address": "0x070b98555b40122cb8b01fcf6f550642f5f55555"}]</t>
+        </is>
+      </c>
+      <c r="AH78" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: 0x62a29564 (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); 0x62a29564 (storage_condition (e.g. initialized flag, paused flag, or an authority slot))</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
@@ -10735,6 +15306,58 @@
       <c r="W79" s="9" t="inlineStr"/>
       <c r="X79" s="8" t="inlineStr"/>
       <c r="Y79" s="8" t="inlineStr"/>
+      <c r="Z79" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA79" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB79" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: every dispatched function analysed to completion with no reachable sensitive operation. The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC79" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD79" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE79" s="12" t="inlineStr">
+        <is>
+          <t>549-byte runtime on gnosis exposing 2 dispatched function(s): deploy(), bootstrap()
+Instruction census (whole contract): CALL×1, CALLER×1, CREATE2×1</t>
+        </is>
+      </c>
+      <c r="AF79" s="12" t="inlineStr">
+        <is>
+          <t>• deploy(): an unauthenticated path to a sensitive operation exists
+• bootstrap(): an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG79" s="12" t="inlineStr">
+        <is>
+          <t>chain=gnosis
+runtime size=549 bytes
+verified source=False
+other chains with identical bytecode: ["gnosis"]
+addresses embedded in the code: [{"bytecode_offset": 136, "address": "0xc0de945918f144dcdf063469823a4c51152df05d"}, {"bytecode_offset": 307, "address": "0x962560a0333190d57009a0aaab7bfa088f58461c"}]</t>
+        </is>
+      </c>
+      <c r="AH79" s="12" t="inlineStr">
+        <is>
+          <t>unrestricted CREATE/CREATE2 at [('bootstrap()', 173)] — a capability whose concrete risk depends on what the created contract is given authority over, which bytecode alone does not establish; unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: deploy() pc=435 -&gt; 0x962560a0333190d57009a0aaab7bfa088f58461c (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
@@ -10862,6 +15485,94 @@
       <c r="W80" s="6" t="inlineStr"/>
       <c r="X80" s="8" t="inlineStr"/>
       <c r="Y80" s="8" t="inlineStr"/>
+      <c r="Z80" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA80" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB80" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x0f4d4caf: CALL at pc=12186 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC80" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD80" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE80" s="12" t="inlineStr">
+        <is>
+          <t>16136-byte runtime on optimism exposing 34 dispatched function(s): 0x0ba65e8d, 0x0bb28465, 0x0f4d4caf, 0x115ff7ee, isValidSignature(bytes32,bytes), 0x1ad4e175, 0x20320171, 0x20a4753b, 0x253c0c9d, 0x4149bc28 Embedded strings mention: Signed Message.
+Concern(s) found: 0x0f4d4caf: CALL at pc=12186 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call
+Protection(s) found: signature-derived authorization branch (ecrecover) on 0x437d55db, 0x6bb0bfe2, 0x71e72d80, 0x92da94a8, 0xd9828e82, 0xfd810579
+Instruction census (whole contract): ADDRESS×26, CALL×14, CALLER×7, CREATE2×1, SSTORE×55, STATICCALL×13</t>
+        </is>
+      </c>
+      <c r="AF80" s="12" t="inlineStr">
+        <is>
+          <t>• 0x0ba65e8d: no sensitive operation reachable
+• 0x0bb28465: an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• 0x0f4d4caf: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• 0x115ff7ee: no sensitive operation reachable — check found: storage_condition; storage_condition
+• isValidSignature(bytes32,bytes): no sensitive operation reachable
+• 0x1ad4e175: no sensitive operation reachable
+• 0x20320171: no sensitive operation reachable
+• 0x20a4753b: no sensitive operation reachable
+• 0x253c0c9d: no sensitive operation reachable — check found: storage_condition; storage_condition
+• 0x4149bc28: no sensitive operation reachable
+• 0x437d55db: every path to a sensitive operation passes an authorization check — check found: storage_condition; signature_authorization
+• cancelLimitOrder(bytes32,bytes): every path to a sensitive operation passes an authorization check — check found: storage_condition; storage_condition
+• 0x4fb655aa: no sensitive operation reachable
+• 0x53f20a4f: no sensitive operation reachable
+• 0x589f075c: no sensitive operation reachable
+• executedOrders(uint256): no sensitive operation reachable
+• 0x6bb0bfe2: every path to a sensitive operation passes an authorization check — check found: storage_condition; signature_authorization [analysis incomplete for this function]
+• 0x71e72d80: every path to a sensitive operation passes an authorization check — check found: signature_authorization
+• 0x78f197ad: no sensitive operation reachable
+• 0x7f545269: no sensitive operation reachable
+• 0x7f94dd33: no sensitive operation reachable
+• 0x8501bfb5: no sensitive operation reachable
+• 0x92da94a8: every path to a sensitive operation passes an authorization check — check found: signature_authorization
+• 0x964566ec: no sensitive operation reachable
+• 0x9cf54c00: no sensitive operation reachable
+• 0xa98127a0: no sensitive operation reachable
+• 0xaae94f99: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• 0xaf87aaec: an unauthenticated path to a sensitive operation exists
+• nonce(): no sensitive operation reachable
+• 0xba72066b: no sensitive operation reachable
+• 0xd29ca57c: no sensitive operation reachable
+• 0xd9828e82: every path to a sensitive operation passes an authorization check — check found: signature_authorization
+• 0xfd810579: every path to a sensitive operation passes an authorization check — check found: storage_condition; storage_condition
+• 0xfdfb3220: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG80" s="12" t="inlineStr">
+        <is>
+          <t>chain=optimism
+runtime size=16136 bytes
+verified source=False
+other chains with identical bytecode: ["optimism"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "uint256", "n_reads": 2, "n_writes": 1}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "mapping(uint256 =&gt; bool)", "n_reads": 2, "n_writes": 1}, {"sl
+addresses embedded in the code: [{"bytecode_offset": 14596, "address": "0x13dc99195c881b9bdd081c9959da5cdd195c9959"}]</t>
+        </is>
+      </c>
+      <c r="AH80" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CREATE2': [16114]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x0f4d4caf, 0x6bb0bfe2; unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: 0x0f4d4caf pc=12132 -&gt; unresolved (value=0, data=memory); 0xaae94f99 pc=3557 -&gt; 0x2339f78e2ec15c47cf042f2460c532c0d7ff1cce (value=0, data=memory); 0xaae94f99 pc=3626 -&gt; unresolved (value=0, data=memory); 0xaf87aaec pc=2362 -&gt; unresolved (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
@@ -10989,6 +15700,62 @@
       <c r="W81" s="9" t="inlineStr"/>
       <c r="X81" s="8" t="inlineStr"/>
       <c r="Y81" s="8" t="inlineStr"/>
+      <c r="Z81" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA81" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB81" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: transferTokenTo(address,address,uint256) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); execute(address,bytes) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); 0x71e07d9b (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); 0x914d910a (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined) The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC81" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD81" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE81" s="12" t="inlineStr">
+        <is>
+          <t>3924-byte runtime on ethereum exposing 6 dispatched function(s): transferTokenTo(address,address,uint256), execute(address,bytes), contains(address[],address), 0x71e07d9b, 0x914d910a, 0xa225bd4c
+Instruction census (whole contract): ADDRESS×3, CALL×7, CALLER×7, ORIGIN×1, SSTORE×1, STATICCALL×3</t>
+        </is>
+      </c>
+      <c r="AF81" s="12" t="inlineStr">
+        <is>
+          <t>• transferTokenTo(address,address,uint256): every path to a sensitive operation passes an authorization check — check found: caller_check [analysis incomplete for this function]
+• execute(address,bytes): every path to a sensitive operation passes an authorization check — check found: caller_check [analysis incomplete for this function]
+• contains(address[],address): no sensitive operation reachable [analysis incomplete for this function]
+• 0x71e07d9b: every path to a sensitive operation passes an authorization check — check found: caller_check [analysis incomplete for this function]
+• 0x914d910a: every path to a sensitive operation passes an authorization check — check found: caller_check [analysis incomplete for this function]
+• 0xa225bd4c: every path to a sensitive operation passes an authorization check — check found: caller_check [analysis incomplete for this function]</t>
+        </is>
+      </c>
+      <c r="AG81" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=3924 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 291, "address": "0x9a46823a51dc134eec255ff63481543675b97e91"}, {"bytecode_offset": 362, "address": "0xd060d168fa75ce8ecda305873627bb9b78cd56cd"}]</t>
+        </is>
+      </c>
+      <c r="AH81" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: transferTokenTo(address,address,uint256) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); execute(address,bytes) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); 0x71e07d9b (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); 0x914d910a (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x71e07d9b, 0x914d910a, 0xa225bd4c, contains(address[],address), execute(address,bytes), transferTokenTo(address,address,uint256)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
@@ -11116,6 +15883,59 @@
       <c r="W82" s="6" t="inlineStr"/>
       <c r="X82" s="8" t="inlineStr"/>
       <c r="Y82" s="8" t="inlineStr"/>
+      <c r="Z82" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA82" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB82" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [309]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC82" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD82" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE82" s="12" t="inlineStr">
+        <is>
+          <t>1012-byte runtime on ethereum exposing 2 dispatched function(s): 0xc48724cf, token()
+Instruction census (whole contract): ADDRESS×1, CALL×1, CALLER×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF82" s="12" t="inlineStr">
+        <is>
+          <t>• 0xc48724cf: no sensitive operation reachable
+• token(): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG82" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=1012 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 1, "n_writes": 0}]</t>
+        </is>
+      </c>
+      <c r="AH82" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [309]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
@@ -11243,6 +16063,61 @@
       <c r="W83" s="9" t="inlineStr"/>
       <c r="X83" s="8" t="inlineStr"/>
       <c r="Y83" s="8" t="inlineStr"/>
+      <c r="Z83" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA83" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB83" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0xbc49482d: SSTORE to slot 0x0 at pc=297 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC83" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD83" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE83" s="12" t="inlineStr">
+        <is>
+          <t>3495-byte runtime on bnb exposing 2 dispatched function(s): DPPFlashLoanCall(address,uint256,uint256,bytes), 0xbc49482d
+Concern(s) found: 0xbc49482d: SSTORE to slot 0x0 at pc=297 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0xbc49482d: SSTORE to slot 0x1 at pc=310 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0xbc49482d: SSTORE to slot 0x2 at pc=315 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0xbc49482d: SSTORE to slot 0x3 at pc=333 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls
+Instruction census (whole contract): ADDRESS×4, CALL×11, CALLER×1, SELFDESTRUCT×1, SSTORE×4, STATICCALL×4</t>
+        </is>
+      </c>
+      <c r="AF83" s="12" t="inlineStr">
+        <is>
+          <t>• DPPFlashLoanCall(address,uint256,uint256,bytes): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• 0xbc49482d: an unauthenticated path to a sensitive operation exists
+• COVERAGE GAP: the analysis never reached 4 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG83" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=3495 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 1, "n_writes": 1}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "address", "n_reads": 1, "n_writes": 1}, {"slot": "00000000000
+addresses embedded in the code: [{"bytecode_offset": 153, "address": "0x55d398326f99059ff775485246999027b3197955"}, {"bytecode_offset": 334, "address": "0x6098a5638d8d7e9ed2f952d35b2b67c34ec6b476"}, {"bytecode_offset": 1459, "address": "0x10ed43c718714eb63d5aa57b78b54704e256024e"}]</t>
+        </is>
+      </c>
+      <c r="AH83" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [196, 1963, 2050], 'SELFDESTRUCT': [3461]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: DPPFlashLoanCall(address,uint256,uint256,bytes); unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: DPPFlashLoanCall(address,uint256,uint256,bytes) pc=621 -&gt; stored(sload) (value=0, data=memory); DPPFlashLoanCall(address,uint256,uint256,bytes) pc=711 -&gt; stored(sload) (value=0, data=memory); DPPFlashLoanCall(address,uint256,uint256,bytes) pc=847 -&gt; 0x55d398326f99059ff775485246999027b3197955 (value=0, data=memory); DPPFlashLoanCall(address,uint256,uint256,bytes) pc=1074 -&gt; stored(sload) (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
@@ -11370,6 +16245,59 @@
       <c r="W84" s="6" t="inlineStr"/>
       <c r="X84" s="8" t="inlineStr"/>
       <c r="Y84" s="8" t="inlineStr"/>
+      <c r="Z84" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA84" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB84" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 2, 'CREATE2': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx2, CREATE2x1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored. The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC84" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD84" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE84" s="12" t="inlineStr">
+        <is>
+          <t>1178-byte runtime on ethereum exposing 2 dispatched function(s): transferNFT(address,address,address,uint256), transferERC1155(address,address,address,uint256,uint256,bytes)
+Concern(s) found: the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 2, 'CREATE2': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx2, CREATE2x1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×2, CREATE2×1</t>
+        </is>
+      </c>
+      <c r="AF84" s="12" t="inlineStr">
+        <is>
+          <t>• transferNFT(address,address,address,uint256): no sensitive operation reachable
+• transferERC1155(address,address,address,uint256,uint256,bytes): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 3 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG84" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=1178 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH84" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [199, 317], 'CREATE2': [1138]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="9" t="inlineStr">
@@ -11497,6 +16425,63 @@
       <c r="W85" s="9" t="inlineStr"/>
       <c r="X85" s="8" t="inlineStr"/>
       <c r="Y85" s="8" t="inlineStr"/>
+      <c r="Z85" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA85" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB85" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: withdrawAllERC20(address): CALL at pc=845 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC85" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD85" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE85" s="12" t="inlineStr">
+        <is>
+          <t>2577-byte runtime on base exposing 5 dispatched function(s): 0x548d268e, 0x720ebbd9, withdrawAllERC20(address), RECEIVER(), withdrawETH()
+Concern(s) found: withdrawAllERC20(address): CALL at pc=845 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; withdrawETH(): CALL at pc=992 to 0xb6db24cf73c54def808d4ceb04d444a1d5e93aae with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time
+Instruction census (whole contract): ADDRESS×1, CALL×4, CALLER×2, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF85" s="12" t="inlineStr">
+        <is>
+          <t>• 0x548d268e: no sensitive operation reachable
+• 0x720ebbd9: no sensitive operation reachable
+• withdrawAllERC20(address): an unauthenticated path to a sensitive operation exists
+• RECEIVER(): no sensitive operation reachable
+• withdrawETH(): an unauthenticated path to a sensitive operation exists
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG85" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=2577 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+addresses embedded in the code: [{"bytecode_offset": 782, "address": "0xb6db24cf73c54def808d4ceb04d444a1d5e93aae"}]</t>
+        </is>
+      </c>
+      <c r="AH85" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [369, 524]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
@@ -11624,6 +16609,72 @@
       <c r="W86" s="6" t="inlineStr"/>
       <c r="X86" s="8" t="inlineStr"/>
       <c r="Y86" s="8" t="inlineStr"/>
+      <c r="Z86" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA86" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB86" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: withdrawEther(uint256): tx.origin must equal the hardcoded address 0x2853f51f7b300cc1a4b88c4df7198c7aac1f89a9. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC86" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD86" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE86" s="12" t="inlineStr">
+        <is>
+          <t>12531-byte runtime on bnb exposing 12 dispatched function(s): setAuth(address,bool), uniswapV2Call(address,uint256,uint256,bytes), pancakeV3SwapCallback(int256,int256,bytes), withdrawEther(uint256), getReserves(address), setAllAuth(address[],bool), getAmountOut(uint256,uint256,uint256,uint256), getAuth(address), pancakeCall(address,uint256,uint256,bytes), withdrawToken(address,uint256)
+Concern(s) found: withdrawEther(uint256): tx.origin must equal the hardcoded address 0x2853f51f7b300cc1a4b88c4df7198c7aac1f89a9. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Protection(s) found: msg.sender compared against a stored authority on setAllAuth(address[],bool), setAuth(address,bool)
+Instruction census (whole contract): ADDRESS×7, CALL×8, CALLER×6, ORIGIN×3, SSTORE×2, STATICCALL×2</t>
+        </is>
+      </c>
+      <c r="AF86" s="12" t="inlineStr">
+        <is>
+          <t>• setAuth(address,bool): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check
+• uniswapV2Call(address,uint256,uint256,bytes): no sensitive operation reachable
+• pancakeV3SwapCallback(int256,int256,bytes): no sensitive operation reachable — check found: storage_condition
+• withdrawEther(uint256): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x2853f51f7b300cc1a4b88c4df7198c7aac1f89a9
+• getReserves(address): no sensitive operation reachable [analysis incomplete for this function]
+• setAllAuth(address[],bool): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check
+• getAmountOut(uint256,uint256,uint256,uint256): no sensitive operation reachable
+• getAuth(address): no sensitive operation reachable
+• pancakeCall(address,uint256,uint256,bytes): no sensitive operation reachable
+• withdrawToken(address,uint256): no sensitive operation reachable — check found: hardcoded_address_check against 0x2853f51f7b300cc1a4b88c4df7198c7aac1f89a9 [analysis incomplete for this function]
+• 0xe3b4fde5: no sensitive operation reachable
+• uniswapV3SwapCallback(int256,int256,bytes): no sensitive operation reachable — check found: storage_condition
+• COVERAGE GAP: the analysis never reached 7 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG86" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=12531 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "mapping(address =&gt; bool)", "n_reads": 3, "n_writes": 2}, {"slot": "0000000000000000000000000000000000000000000000000000000000000002", "offset": 0, "type": "address", "n_reads": 2, "n_writes": 0}]
+addresses embedded in the code: [{"bytecode_offset": 992, "address": "0x2853f51f7b300cc1a4b88c4df7198c7aac1f89a9"}, {"bytecode_offset": 6017, "address": "0xfffd8963efd1fc6a506488495d951d5263988d25"}]</t>
+        </is>
+      </c>
+      <c r="AH86" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [3775, 4626, 4906, 5550]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: getReserves(address), withdrawToken(address,uint256)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
@@ -11751,6 +16802,66 @@
       <c r="W87" s="9" t="inlineStr"/>
       <c r="X87" s="8" t="inlineStr"/>
       <c r="Y87" s="8" t="inlineStr"/>
+      <c r="Z87" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA87" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB87" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates:  The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC87" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD87" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE87" s="12" t="inlineStr">
+        <is>
+          <t>5868-byte runtime on bnb exposing 7 dispatched function(s): withdrawETH(address), renounceOwnership(), initialize(), owner(), withdrawERC20(address,address), main(), transferOwnership(address)
+Protection(s) found: msg.sender compared against a stored authority on renounceOwnership(), transferOwnership(address), withdrawETH(address)
+Instruction census (whole contract): ADDRESS×8, CALL×5, CALLER×3, ORIGIN×1, SSTORE×4, STATICCALL×6</t>
+        </is>
+      </c>
+      <c r="AF87" s="12" t="inlineStr">
+        <is>
+          <t>• withdrawETH(address): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check
+• renounceOwnership(): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check
+• initialize(): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• owner(): no sensitive operation reachable
+• withdrawERC20(address,address): no sensitive operation reachable
+• main(): no sensitive operation reachable
+• transferOwnership(address): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check
+• COVERAGE GAP: the analysis never reached 4 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG87" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=5868 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "9016d09d72d40fdae2fd8ceac6b6234c7706214fd39c1cd1e609a0528c199300", "offset": 0, "type": "address", "n_reads": 6, "n_writes": 3}, {"slot": "f0c57e16840df040f15088dc2f81fe391c3923bec73e23a9662efc9c229c6a00", "offset": 0, "type": "uint64", "n_reads": 1, "n_writes": 1}, {"slot": "f0c57e16840d
+addresses embedded in the code: [{"bytecode_offset": 1400, "address": "0x55d398326f99059ff775485246999027b3197955"}, {"bytecode_offset": 1558, "address": "0x45d675ff71fc8a08d27f631e99af2aced1d48903"}, {"bytecode_offset": 1725, "address": "0xf0788db035f1aebf5e653f0692e72c0d34f9860c"}]</t>
+        </is>
+      </c>
+      <c r="AH87" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [1088, 2235, 2399, 2660]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
@@ -11878,6 +16989,80 @@
       <c r="W88" s="6" t="inlineStr"/>
       <c r="X88" s="8" t="inlineStr"/>
       <c r="Y88" s="8" t="inlineStr"/>
+      <c r="Z88" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA88" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB88" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: addWhitelistedSender(address): msg.sender must equal the hardcoded address 0xc56a0bd4cf93032c2487bdf254e4a3d69fa7c4ba. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC88" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD88" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE88" s="12" t="inlineStr">
+        <is>
+          <t>9804-byte runtime on ethereum exposing 20 dispatched function(s): 0x0985efd4, OWNER(), getValidator(), getBalance(), DOMAIN_TYPEHASH(), whitelistedSenders(address), getNonce(address), 0x2dffc938, DOMAIN_SEPARATOR(), isWhitelisted(address)
+Concern(s) found: addWhitelistedSender(address): msg.sender must equal the hardcoded address 0xc56a0bd4cf93032c2487bdf254e4a3d69fa7c4ba. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; removeWhitelistedSender(address): msg.sender must equal the hardcoded address 0xc56a0bd4cf93032c2487bdf254e4a3d69fa7c4ba. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; emergencyWithdraw(address,uint256): msg.sender must equal the hardcoded address 0xc56a0bd4cf93032c2487bdf254e4a3d69fa7c4ba. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; initializeWhitelist(address[]): msg.sender must equal the hardcoded address 0xc56a0bd4cf93032c2487bdf254e4a3d69fa7c4ba. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Protection(s) found: signature-derived authorization branch (ecrecover) on 0x0985efd4, 0xca503a67
+Instruction census (whole contract): CALL×5, CALLER×10, SSTORE×20, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF88" s="12" t="inlineStr">
+        <is>
+          <t>• 0x0985efd4: every path to a sensitive operation passes an authorization check — check found: signature_authorization [analysis incomplete for this function]
+• OWNER(): no sensitive operation reachable
+• getValidator(): no sensitive operation reachable
+• getBalance(): no sensitive operation reachable
+• DOMAIN_TYPEHASH(): no sensitive operation reachable
+• whitelistedSenders(address): no sensitive operation reachable
+• getNonce(address): no sensitive operation reachable
+• 0x2dffc938: no sensitive operation reachable
+• DOMAIN_SEPARATOR(): no sensitive operation reachable
+• isWhitelisted(address): no sensitive operation reachable
+• addWhitelistedSender(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xc56a0bd4cf93032c2487bdf254e4a3d69fa7c4ba; storage_condition
+• getWhitelistedAddresses(): no sensitive operation reachable — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• removeWhitelistedSender(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xc56a0bd4cf93032c2487bdf254e4a3d69fa7c4ba; storage_condition [analysis incomplete for this function]
+• nonces(address): no sensitive operation reachable
+• emergencyWithdraw(address,uint256): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xc56a0bd4cf93032c2487bdf254e4a3d69fa7c4ba
+• 0xb1bc8bd6: no sensitive operation reachable
+• whitelistedAddresses(uint256): no sensitive operation reachable — check found: storage_condition
+• 0xca503a67: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xc56a0bd4cf93032c2487bdf254e4a3d69fa7c4ba; caller_check [analysis incomplete for this function]
+• getDomainSeparator(): no sensitive operation reachable
+• initializeWhitelist(address[]): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xc56a0bd4cf93032c2487bdf254e4a3d69fa7c4ba; storage_condition [analysis incomplete for this function]
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG88" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=9804 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "mapping(address =&gt; bool)", "n_reads": 5, "n_writes": 2}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "address[]", "n_reads": 4, "n_writes": 1}, {"
+addresses embedded in the code: [{"bytecode_offset": 2910, "address": "0x496e73756666696369656e742062616c616e6365"}, {"bytecode_offset": 3026, "address": "0x7462d43e300fb964b6a38175381d56a07c860faa"}, {"bytecode_offset": 3049, "address": "0xf140165a173e5093e87a870b4be95449f0d54cec"}, {"bytecode_offset": 3075, "address": "0xf241a5c</t>
+        </is>
+      </c>
+      <c r="AH88" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: addWhitelistedSender(address) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); removeWhitelistedSender(address) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); removeWhitelistedSender(address) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); removeWhitelistedSender(address) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [6203]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x0985efd4, 0xca503a67, getWhitelistedAddresses(), initializeWhitelist(address[]), removeWhitelistedSender(address)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
@@ -12005,6 +17190,65 @@
       <c r="W89" s="9" t="inlineStr"/>
       <c r="X89" s="8" t="inlineStr"/>
       <c r="Y89" s="8" t="inlineStr"/>
+      <c r="Z89" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA89" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB89" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored. The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC89" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD89" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE89" s="12" t="inlineStr">
+        <is>
+          <t>2235-byte runtime on bnb exposing 8 dispatched function(s): getCurrentBlockTimestamp(), aggregate((address,bytes)[]), getLastBlockHash(), getEthBalance(address), getCurrentBlockDifficulty(), getCurrentBlockGasLimit(), getCurrentBlockCoinbase(), getBlockHash(uint256)
+Concern(s) found: the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×1</t>
+        </is>
+      </c>
+      <c r="AF89" s="12" t="inlineStr">
+        <is>
+          <t>• getCurrentBlockTimestamp(): no sensitive operation reachable
+• aggregate((address,bytes)[]): no sensitive operation reachable [analysis incomplete for this function]
+• getLastBlockHash(): no sensitive operation reachable
+• getEthBalance(address): no sensitive operation reachable
+• getCurrentBlockDifficulty(): no sensitive operation reachable
+• getCurrentBlockGasLimit(): no sensitive operation reachable
+• getCurrentBlockCoinbase(): no sensitive operation reachable
+• getBlockHash(uint256): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG89" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=2235 bytes
+verified source=True
+other chains with identical bytecode: ["bnb"]</t>
+        </is>
+      </c>
+      <c r="AH89" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [623]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: aggregate((address,bytes)[])</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
@@ -12132,6 +17376,57 @@
       <c r="W90" s="6" t="inlineStr"/>
       <c r="X90" s="8" t="inlineStr"/>
       <c r="Y90" s="8" t="inlineStr"/>
+      <c r="Z90" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA90" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB90" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: every dispatched function analysed to completion with no reachable sensitive operation. The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC90" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD90" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE90" s="12" t="inlineStr">
+        <is>
+          <t>476-byte runtime on base exposing 2 dispatched function(s): ping(), initialize()
+Instruction census (whole contract): CALLER×1</t>
+        </is>
+      </c>
+      <c r="AF90" s="12" t="inlineStr">
+        <is>
+          <t>• ping(): no sensitive operation reachable
+• initialize(): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG90" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=476 bytes
+verified source=False
+other chains with identical bytecode: ["base"]</t>
+        </is>
+      </c>
+      <c r="AH90" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
@@ -12259,6 +17554,58 @@
       <c r="W91" s="9" t="inlineStr"/>
       <c r="X91" s="8" t="inlineStr"/>
       <c r="Y91" s="8" t="inlineStr"/>
+      <c r="Z91" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA91" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB91" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: set(): tx.origin must equal the hardcoded address 0xa5142abaabafe8535f0b54779cc0e441976d464e. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC91" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD91" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE91" s="12" t="inlineStr">
+        <is>
+          <t>568-byte runtime on bnb exposing 1 dispatched function(s): set()
+Concern(s) found: set(): tx.origin must equal the hardcoded address 0xa5142abaabafe8535f0b54779cc0e441976d464e. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×1, ORIGIN×2</t>
+        </is>
+      </c>
+      <c r="AF91" s="12" t="inlineStr">
+        <is>
+          <t>• set(): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xa5142abaabafe8535f0b54779cc0e441976d464e; tx_origin_check</t>
+        </is>
+      </c>
+      <c r="AG91" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=568 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+addresses embedded in the code: [{"bytecode_offset": 119, "address": "0xa5142abaabafe8535f0b54779cc0e441976d464e"}]</t>
+        </is>
+      </c>
+      <c r="AH91" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: set() (tx_origin_check (tx.origin compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
@@ -12386,6 +17733,57 @@
       <c r="W92" s="6" t="inlineStr"/>
       <c r="X92" s="8" t="inlineStr"/>
       <c r="Y92" s="8" t="inlineStr"/>
+      <c r="Z92" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA92" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB92" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored. The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC92" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD92" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE92" s="12" t="inlineStr">
+        <is>
+          <t>1588-byte runtime on base exposing 1 dispatched function(s): execute((address,bytes,uint256)[])
+Concern(s) found: the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×1</t>
+        </is>
+      </c>
+      <c r="AF92" s="12" t="inlineStr">
+        <is>
+          <t>• execute((address,bytes,uint256)[]): an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG92" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=1588 bytes
+verified source=False
+other chains with identical bytecode: ["base", "ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH92" s="12" t="inlineStr">
+        <is>
+          <t>unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: execute((address,bytes,uint256)[]) pc=224 -&gt; unresolved (value=memory, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
@@ -12513,6 +17911,59 @@
       <c r="W93" s="9" t="inlineStr"/>
       <c r="X93" s="8" t="inlineStr"/>
       <c r="Y93" s="8" t="inlineStr"/>
+      <c r="Z93" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA93" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB93" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x2bd5dea8: msg.sender must equal the hardcoded address 0x6969698f9369abf880d1b1a6fe0e64de0f61528b. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC93" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD93" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE93" s="12" t="inlineStr">
+        <is>
+          <t>3229-byte runtime on bnb exposing 2 dispatched function(s): 0x2bd5dea8, 0xe9524386
+Concern(s) found: 0x2bd5dea8: msg.sender must equal the hardcoded address 0x6969698f9369abf880d1b1a6fe0e64de0f61528b. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0xe9524386: msg.sender must equal the hardcoded address 0x6969698f9369abf880d1b1a6fe0e64de0f61528b. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×2, CALLER×3</t>
+        </is>
+      </c>
+      <c r="AF93" s="12" t="inlineStr">
+        <is>
+          <t>• 0x2bd5dea8: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x6969698f9369abf880d1b1a6fe0e64de0f61528b
+• 0xe9524386: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x6969698f9369abf880d1b1a6fe0e64de0f61528b</t>
+        </is>
+      </c>
+      <c r="AG93" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=3229 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+addresses embedded in the code: [{"bytecode_offset": 248, "address": "0x6969698f9369abf880d1b1a6fe0e64de0f61528b"}]</t>
+        </is>
+      </c>
+      <c r="AH93" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
@@ -12640,6 +18091,60 @@
       <c r="W94" s="6" t="inlineStr"/>
       <c r="X94" s="8" t="inlineStr"/>
       <c r="Y94" s="8" t="inlineStr"/>
+      <c r="Z94" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA94" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB94" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x5ee9acc7: CALL at pc=442 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC94" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD94" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE94" s="12" t="inlineStr">
+        <is>
+          <t>3426-byte runtime on arbitrum exposing 3 dispatched function(s): 0x5ee9acc7, multicall(address[],bytes[]), owner()
+Concern(s) found: 0x5ee9acc7: CALL at pc=442 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; multicall(address[],bytes[]): CALL at pc=794 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call
+Instruction census (whole contract): CALL×2, CALLER×1</t>
+        </is>
+      </c>
+      <c r="AF94" s="12" t="inlineStr">
+        <is>
+          <t>• 0x5ee9acc7: an unauthenticated path to a sensitive operation exists
+• multicall(address[],bytes[]): an unauthenticated path to a sensitive operation exists
+• owner(): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG94" s="12" t="inlineStr">
+        <is>
+          <t>chain=arbitrum
+runtime size=3426 bytes
+verified source=False
+other chains with identical bytecode: ["arbitrum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 1, "n_writes": 0}]</t>
+        </is>
+      </c>
+      <c r="AH94" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
@@ -12767,6 +18272,67 @@
       <c r="W95" s="9" t="inlineStr"/>
       <c r="X95" s="8" t="inlineStr"/>
       <c r="Y95" s="8" t="inlineStr"/>
+      <c r="Z95" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA95" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB95" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [6344, 6641, 6938, 7235]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC95" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD95" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE95" s="12" t="inlineStr">
+        <is>
+          <t>9945-byte runtime on base exposing 9 dispatched function(s): 0x5b4e1153, 0x6672818d, 0x6a879419, 0x6c71e859, 0x8cca10d5, owner(), 0xa3bdee3b, 0xc6513a60, 0xf82e8c00 Embedded strings mention: Not owner.
+Protection(s) found: msg.sender compared against a stored authority on 0xf82e8c00
+Instruction census (whole contract): CALL×5, CALLER×3, STATICCALL×33</t>
+        </is>
+      </c>
+      <c r="AF95" s="12" t="inlineStr">
+        <is>
+          <t>• 0x5b4e1153: no sensitive operation reachable
+• 0x6672818d: no sensitive operation reachable
+• 0x6a879419: no sensitive operation reachable
+• 0x6c71e859: no sensitive operation reachable — check found: storage_condition; storage_condition
+• 0x8cca10d5: no sensitive operation reachable
+• owner(): no sensitive operation reachable
+• 0xa3bdee3b: no sensitive operation reachable — check found: storage_condition; storage_condition
+• 0xc6513a60: no sensitive operation reachable
+• 0xf82e8c00: every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check
+• COVERAGE GAP: the analysis never reached 4 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG95" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=9945 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 1, "n_writes": 0}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "address", "n_reads": 1, "n_writes": 0}, {"slot": "00000000000</t>
+        </is>
+      </c>
+      <c r="AH95" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [6344, 6641, 6938, 7235]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
@@ -12894,6 +18460,83 @@
       <c r="W96" s="6" t="inlineStr"/>
       <c r="X96" s="8" t="inlineStr"/>
       <c r="Y96" s="8" t="inlineStr"/>
+      <c r="Z96" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA96" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB96" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: initialize(bytes): CALL at pc=13838 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC96" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD96" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE96" s="12" t="inlineStr">
+        <is>
+          <t>15335-byte runtime on optimism exposing 24 dispatched function(s): 0x0ee9bf14, isModuleInstalled(uint256,address,bytes), isValidSignature(bytes32,bytes), validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256), recover(address,bytes), 0x3eb1765a, initialize(bytes), upgradeToAndCall(address,bytes), proxiableUUID(), installModule(uint256,address,bytes)
+Concern(s) found: initialize(bytes): CALL at pc=13838 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; executeFromExecutor(bytes32,bytes): CALL at pc=13838 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; recover(address,bytes): msg.sender must equal the hardcoded address 0x1059e069a8fbec96b38a80eb745f14d6336bd752. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x3eb1765a: msg.sender must equal the hardcoded address 0x1059e069a8fbec96b38a80eb745f14d6336bd752. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Protection(s) found: self-call restriction (msg.sender == address(this)) on execute(bytes32,bytes), installModule(uint256,address,bytes), uninstallModule(uint256,address,bytes), upgradeToAndCall(address,bytes) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent; caller restricted to a recognized ERC-4337 EntryPoint on execute(bytes32,bytes), installModule(uint256,address,bytes), uninstallModule(uint256,address,bytes), upgradeToAndCall(address,bytes), validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256)
+Instruction census (whole contract): ADDRESS×8, CALL×10, CALLER×14, DELEGATECALL×1, ORIGIN×1, SSTORE×27, STATICCALL×10</t>
+        </is>
+      </c>
+      <c r="AF96" s="12" t="inlineStr">
+        <is>
+          <t>• 0x0ee9bf14: no sensitive operation reachable
+• isModuleInstalled(uint256,address,bytes): no sensitive operation reachable — check found: storage_condition
+• isValidSignature(bytes32,bytes): no sensitive operation reachable [analysis incomplete for this function]
+• validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032
+• recover(address,bytes): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x1059e069a8fbec96b38a80eb745f14d6336bd752; storage_condition
+• 0x3eb1765a: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x1059e069a8fbec96b38a80eb745f14d6336bd752
+• initialize(bytes): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• upgradeToAndCall(address,bytes): every path to a sensitive operation passes an authorization check — check found: storage_condition; hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032
+• proxiableUUID(): no sensitive operation reachable
+• installModule(uint256,address,bytes): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032; self_call_check
+• executors(address): no sensitive operation reachable
+• 0x9bdafcb3: no sensitive operation reachable
+• accountId(): no sensitive operation reachable [analysis incomplete for this function]
+• 0xa09f1f85: no sensitive operation reachable
+• uninstallModule(uint256,address,bytes): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032; self_call_check
+• UPGRADE_INTERFACE_VERSION(): no sensitive operation reachable [analysis incomplete for this function]
+• 0xd2c1934f: no sensitive operation reachable
+• executeFromExecutor(bytes32,bytes): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• CONFIG(): no sensitive operation reachable
+• 0xe18ff63f: no sensitive operation reachable
+• ENTRYPOINT(): no sensitive operation reachable
+• execute(bytes32,bytes): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032; self_call_check [analysis incomplete for this function]
+• 0xeed2f252: no sensitive operation reachable
+• supportsModule(uint256): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG96" s="12" t="inlineStr">
+        <is>
+          <t>chain=optimism
+runtime size=15335 bytes
+verified source=False
+other chains with identical bytecode: ["optimism"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "uint256", "n_reads": 3, "n_writes": 1}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "mapping(bytes =&gt; mapping(uint256 =&gt; bool))", "n_reads": 4, "n
+addresses embedded in the code: [{"bytecode_offset": 495, "address": "0x1059e069a8fbec96b38a80eb745f14d6336bd752"}, {"bytecode_offset": 7605, "address": "0x76192fdcbf93594ef55c0098865e84ca02905811"}]</t>
+        </is>
+      </c>
+      <c r="AH96" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: recover(address,bytes) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); recover(address,bytes) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); recover(address,bytes) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); recover(address,bytes) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: UPGRADE_INTERFACE_VERSION(), accountId(), execute(bytes32,bytes), executeFromExecutor(bytes32,bytes), initialize(bytes), isValidSignature(bytes32,bytes); unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: initialize(bytes) pc=9082 -&gt; 0x22cbe69de5f40f8387cb9f41ce7c25d299896800 (value=0, data=memory); executeFromExecutor(bytes32,bytes) pc=9082 -&gt; stored(sload) (value=0, data=memory); executeFromExecutor(bytes32,bytes) pc=13674 -&gt; stored(sload) (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
@@ -13021,6 +18664,60 @@
       <c r="W97" s="9" t="inlineStr"/>
       <c r="X97" s="8" t="inlineStr"/>
       <c r="Y97" s="8" t="inlineStr"/>
+      <c r="Z97" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA97" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB97" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x040113fc: tx.origin must equal the hardcoded address 0xe0f886106fdb30e0069fb6c02b67400fc4f9ae1d. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC97" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD97" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE97" s="12" t="inlineStr">
+        <is>
+          <t>3286-byte runtime on polygon exposing 4 dispatched function(s): 0x040113fc, onERC721Received(address,address,uint256,bytes), onERC1155BatchReceived(address,address,uint256[],uint256[],bytes), onERC1155Received(address,address,uint256,uint256,bytes) Embedded strings mention: Not owner.
+Concern(s) found: 0x040113fc: tx.origin must equal the hardcoded address 0xe0f886106fdb30e0069fb6c02b67400fc4f9ae1d. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×2, ORIGIN×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF97" s="12" t="inlineStr">
+        <is>
+          <t>• 0x040113fc: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xe0f886106fdb30e0069fb6c02b67400fc4f9ae1d
+• onERC721Received(address,address,uint256,bytes): no sensitive operation reachable
+• onERC1155BatchReceived(address,address,uint256[],uint256[],bytes): no sensitive operation reachable
+• onERC1155Received(address,address,uint256,uint256,bytes): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG97" s="12" t="inlineStr">
+        <is>
+          <t>chain=polygon
+runtime size=3286 bytes
+verified source=False
+other chains with identical bytecode: ["polygon"]</t>
+        </is>
+      </c>
+      <c r="AH97" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
@@ -13148,6 +18845,61 @@
       <c r="W98" s="6" t="inlineStr"/>
       <c r="X98" s="8" t="inlineStr"/>
       <c r="Y98" s="8" t="inlineStr"/>
+      <c r="Z98" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA98" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB98" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: self-call restriction (msg.sender == address(this)) on deploy(uint256,bytes32,bytes), execute(address,uint256,bytes), multicall(bytes[]), setWhitelist(address,bool) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC98" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD98" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE98" s="12" t="inlineStr">
+        <is>
+          <t>2232-byte runtime on bnb exposing 4 dispatched function(s): setWhitelist(address,bool), deploy(uint256,bytes32,bytes), multicall(bytes[]), execute(address,uint256,bytes)
+Protection(s) found: self-call restriction (msg.sender == address(this)) on deploy(uint256,bytes32,bytes), execute(address,uint256,bytes), multicall(bytes[]), setWhitelist(address,bool) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent
+Instruction census (whole contract): ADDRESS×5, CALL×2, CALLER×8, CREATE2×1, SSTORE×1</t>
+        </is>
+      </c>
+      <c r="AF98" s="12" t="inlineStr">
+        <is>
+          <t>• setWhitelist(address,bool): every path to a sensitive operation passes an authorization check — check found: self_call_check; self_call_check
+• deploy(uint256,bytes32,bytes): every path to a sensitive operation passes an authorization check — check found: self_call_check; self_call_check
+• multicall(bytes[]): every path to a sensitive operation passes an authorization check — check found: self_call_check; self_call_check
+• execute(address,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: self_call_check; self_call_check</t>
+        </is>
+      </c>
+      <c r="AG98" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=2232 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "mapping(address =&gt; bool)", "n_reads": 4, "n_writes": 1}]</t>
+        </is>
+      </c>
+      <c r="AH98" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
@@ -13275,6 +19027,59 @@
       <c r="W99" s="9" t="inlineStr"/>
       <c r="X99" s="8" t="inlineStr"/>
       <c r="Y99" s="8" t="inlineStr"/>
+      <c r="Z99" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA99" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB99" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [828]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC99" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD99" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE99" s="12" t="inlineStr">
+        <is>
+          <t>2672-byte runtime on arbitrum exposing 2 dispatched function(s): 0x2ced0188, 0x53d4e0d5
+Protection(s) found: signature-derived authorization branch (ecrecover) on 0x53d4e0d5
+Instruction census (whole contract): ADDRESS×1, CALL×1, SSTORE×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF99" s="12" t="inlineStr">
+        <is>
+          <t>• 0x2ced0188: no sensitive operation reachable
+• 0x53d4e0d5: no sensitive operation reachable — check found: storage_condition; signature_authorization [analysis incomplete for this function]
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG99" s="12" t="inlineStr">
+        <is>
+          <t>chain=arbitrum
+runtime size=2672 bytes
+verified source=False
+other chains with identical bytecode: ["arbitrum", "base"]</t>
+        </is>
+      </c>
+      <c r="AH99" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [828]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x53d4e0d5</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
@@ -13382,6 +19187,58 @@
       <c r="W100" s="6" t="inlineStr"/>
       <c r="X100" s="8" t="inlineStr"/>
       <c r="Y100" s="8" t="inlineStr"/>
+      <c r="Z100" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA100" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB100" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CREATE2': [319]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC100" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD100" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE100" s="12" t="inlineStr">
+        <is>
+          <t>357-byte runtime on ethereum exposing 0 dispatched function(s): &lt;no dispatcher recovered; analysed from pc=0&gt;
+Instruction census (whole contract): CALLER×1, CREATE2×1, ORIGIN×1</t>
+        </is>
+      </c>
+      <c r="AF100" s="12" t="inlineStr">
+        <is>
+          <t>• &lt;no dispatcher recovered; analysed from pc=0&gt;: no sensitive operation reachable — check found: hardcoded_address_check against 0xc13ced137e90bc695cb77288962280516a2f9b8b
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG100" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=357 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 10, "address": "0xc13ced137e90bc695cb77288962280516a2f9b8b"}]</t>
+        </is>
+      </c>
+      <c r="AH100" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CREATE2': [319]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
@@ -13509,6 +19366,64 @@
       <c r="W101" s="9" t="inlineStr"/>
       <c r="X101" s="8" t="inlineStr"/>
       <c r="Y101" s="8" t="inlineStr"/>
+      <c r="Z101" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA101" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB101" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x2f6b312b: msg.sender must equal the hardcoded address 0x00806daa2cfe49715ea05243ff259deb195760fc. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC101" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD101" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE101" s="12" t="inlineStr">
+        <is>
+          <t>3172-byte runtime on ethereum exposing 6 dispatched function(s): settle(address[],uint256[],(uint256,uint256,address,uint256,uint256,uint32,bytes32,uint256,uint256,uint256,bytes)[],(address,uint256,bytes)[][3]), 0x2f6b312b, 0x5197a0d3, 0x752be0d6, 0x7f6e9d4b, admin() Embedded strings mention: Unauthorized.
+Concern(s) found: 0x2f6b312b: msg.sender must equal the hardcoded address 0x00806daa2cfe49715ea05243ff259deb195760fc. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x5197a0d3: msg.sender must equal the hardcoded address 0x00806daa2cfe49715ea05243ff259deb195760fc. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×2, CALLER×3, SSTORE×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF101" s="12" t="inlineStr">
+        <is>
+          <t>• settle(address[],uint256[],(uint256,uint256,address,uint256,uint256,uint32,bytes32,uint256,uint256,uint256,bytes)[],(address,uint256,bytes)[][3]): no sensitive operation reachable — check found: storage_condition [analysis incomplete for this function]
+• 0x2f6b312b: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x00806daa2cfe49715ea05243ff259deb195760fc
+• 0x5197a0d3: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x00806daa2cfe49715ea05243ff259deb195760fc
+• 0x752be0d6: no sensitive operation reachable
+• 0x7f6e9d4b: no sensitive operation reachable
+• admin(): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG101" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=3172 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "mapping(address =&gt; bool)", "n_reads": 2, "n_writes": 1}]</t>
+        </is>
+      </c>
+      <c r="AH101" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [621]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: settle(address[],uint256[],(uint256,uint256,address,uint256,uint256,uint32,bytes32,uint256,uint256,uint256,bytes)[],(address,uint256,bytes)[][3])</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
@@ -13636,6 +19551,59 @@
       <c r="W102" s="6" t="inlineStr"/>
       <c r="X102" s="8" t="inlineStr"/>
       <c r="Y102" s="8" t="inlineStr"/>
+      <c r="Z102" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA102" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB102" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: signature-derived authorization branch (ecrecover) on execute((address,uint256,bytes)[],bytes) The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC102" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD102" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE102" s="12" t="inlineStr">
+        <is>
+          <t>4163-byte runtime on base exposing 2 dispatched function(s): execute((address,uint256,bytes)[],bytes), nonce() Embedded strings mention: Signed Message.
+Protection(s) found: signature-derived authorization branch (ecrecover) on execute((address,uint256,bytes)[],bytes)
+Instruction census (whole contract): ADDRESS×1, CALL×1, CALLER×1, SSTORE×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF102" s="12" t="inlineStr">
+        <is>
+          <t>• execute((address,uint256,bytes)[],bytes): every path to a sensitive operation passes an authorization check — check found: signature_authorization; storage_condition [analysis incomplete for this function]
+• nonce(): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG102" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=4163 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "uint256", "n_reads": 1, "n_writes": 1}]</t>
+        </is>
+      </c>
+      <c r="AH102" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: execute((address,uint256,bytes)[],bytes)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
@@ -13763,6 +19731,58 @@
       <c r="W103" s="9" t="inlineStr"/>
       <c r="X103" s="8" t="inlineStr"/>
       <c r="Y103" s="8" t="inlineStr"/>
+      <c r="Z103" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA103" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB103" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored. The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC103" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD103" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE103" s="12" t="inlineStr">
+        <is>
+          <t>274-byte runtime on base exposing 1 dispatched function(s): transfer(address,uint256)
+Concern(s) found: the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×1</t>
+        </is>
+      </c>
+      <c r="AF103" s="12" t="inlineStr">
+        <is>
+          <t>• transfer(address,uint256): an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG103" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=274 bytes
+verified source=False
+other chains with identical bytecode: ["base", "bnb"]
+addresses embedded in the code: [{"bytecode_offset": 0, "address": "0xb9d00655cae73b4d0905d199150c82d3b124da7c"}]</t>
+        </is>
+      </c>
+      <c r="AH103" s="12" t="inlineStr">
+        <is>
+          <t>unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: transfer(address,uint256) pc=257 -&gt; unresolved (value=0, data=-). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
@@ -13870,6 +19890,58 @@
       <c r="W104" s="6" t="inlineStr"/>
       <c r="X104" s="8" t="inlineStr"/>
       <c r="Y104" s="8" t="inlineStr"/>
+      <c r="Z104" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA104" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB104" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored. The source static analyzer's verdict was assessed as CONTRADICTED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC104" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONTRADICTED</t>
+        </is>
+      </c>
+      <c r="AD104" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: The source analyzer did not flag this contract, yet an external call is reachable from the receive()/fallback() path without passing any caller authorization branch. `unflagged` is a weak signal by construction — the negatives in this dataset are rule-silent, never benignity-verified — so this is a plausible source-rule miss rather than a contradiction of a positive finding.</t>
+        </is>
+      </c>
+      <c r="AE104" s="12" t="inlineStr">
+        <is>
+          <t>96-byte runtime on ethereum exposing 0 dispatched function(s): &lt;no dispatcher recovered; analysed from pc=0&gt;
+Concern(s) found: the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×1</t>
+        </is>
+      </c>
+      <c r="AF104" s="12" t="inlineStr">
+        <is>
+          <t>• &lt;no dispatcher recovered; analysed from pc=0&gt;: an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG104" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=96 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 10, "address": "0xe0fcc47c3b4fb4d77174b3f9da7b6e88c95dd751"}]</t>
+        </is>
+      </c>
+      <c r="AH104" s="12" t="inlineStr">
+        <is>
+          <t>unauthenticated call(s) forwarding only msg.value to a fixed destination ([('&lt;no dispatcher recovered; analysed from pc=0&gt;', 32, '0xe0fcc47c3b4fb4d77174b3f9da7b6e88c95dd751')]) — a caller can only donate their own ETH, so this is not by itself a path to the account's assets</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
@@ -13997,6 +20069,57 @@
       <c r="W105" s="9" t="inlineStr"/>
       <c r="X105" s="8" t="inlineStr"/>
       <c r="Y105" s="8" t="inlineStr"/>
+      <c r="Z105" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA105" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB105" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: every dispatched function analysed to completion with no reachable sensitive operation. The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC105" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD105" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE105" s="12" t="inlineStr">
+        <is>
+          <t>464-byte runtime on bnb exposing 2 dispatched function(s): ping(), initialize()
+Instruction census (whole contract): CALLER×1</t>
+        </is>
+      </c>
+      <c r="AF105" s="12" t="inlineStr">
+        <is>
+          <t>• ping(): no sensitive operation reachable
+• initialize(): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG105" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=464 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]</t>
+        </is>
+      </c>
+      <c r="AH105" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
@@ -14124,6 +20247,69 @@
       <c r="W106" s="6" t="inlineStr"/>
       <c r="X106" s="8" t="inlineStr"/>
       <c r="Y106" s="8" t="inlineStr"/>
+      <c r="Z106" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA106" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB106" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x0a5491b4: msg.sender must equal the hardcoded address 0x0bb9ad9357565a592668e6c41463b05a17c68a09. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC106" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD106" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE106" s="12" t="inlineStr">
+        <is>
+          <t>7186-byte runtime on bnb exposing 11 dispatched function(s): 0x0a5491b4, token0(), poolAddress(), 0x2e24f896, 0x5b5dc217, 0x69dd9807, positionInfo(), pancakeV3MintCallback(uint256,uint256,bytes), 0xcab2e64e, token1()
+Concern(s) found: 0x0a5491b4: msg.sender must equal the hardcoded address 0x0bb9ad9357565a592668e6c41463b05a17c68a09. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0xcab2e64e: msg.sender must equal the hardcoded address 0x0bb9ad9357565a592668e6c41463b05a17c68a09. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; setPoolAddress(address): msg.sender must equal the hardcoded address 0x0bb9ad9357565a592668e6c41463b05a17c68a09. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x2e24f896: SSTORE to slot 0x3 at pc=4316 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x5b5dc217: SSTORE to slot 0x3 at pc=3797 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls
+Protection(s) found: msg.sender compared against a stored authority on pancakeV3MintCallback(uint256,uint256,bytes)
+Instruction census (whole contract): ADDRESS×9, CALL×5, CALLER×4, SSTORE×12, STATICCALL×10</t>
+        </is>
+      </c>
+      <c r="AF106" s="12" t="inlineStr">
+        <is>
+          <t>• 0x0a5491b4: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0bb9ad9357565a592668e6c41463b05a17c68a09; storage_condition
+• token0(): no sensitive operation reachable
+• poolAddress(): no sensitive operation reachable
+• 0x2e24f896: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• 0x5b5dc217: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• 0x69dd9807: no sensitive operation reachable — check found: storage_condition; storage_condition
+• positionInfo(): no sensitive operation reachable
+• pancakeV3MintCallback(uint256,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_condition
+• 0xcab2e64e: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0bb9ad9357565a592668e6c41463b05a17c68a09
+• token1(): no sensitive operation reachable
+• setPoolAddress(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0bb9ad9357565a592668e6c41463b05a17c68a09</t>
+        </is>
+      </c>
+      <c r="AG106" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=7186 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 6, "n_writes": 2}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "address", "n_reads": 5, "n_writes": 2}, {"slot": "00000000000</t>
+        </is>
+      </c>
+      <c r="AH106" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: 0x0a5491b4 (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); 0x0a5491b4 (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); 0x0a5491b4 (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x2e24f896, 0x5b5dc217; unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: 0x2e24f896 pc=3578 -&gt; stored(sload) (value=0, data=memory); 0x2e24f896 pc=3661 -&gt; stored(sload) (value=0, data=memory); 0x2e24f896 pc=4537 -&gt; stored(sload) (value=0, data=memory); 0x5b5dc217 pc=4537 -&gt; stored(sload) (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
@@ -14251,6 +20437,59 @@
       <c r="W107" s="9" t="inlineStr"/>
       <c r="X107" s="8" t="inlineStr"/>
       <c r="Y107" s="8" t="inlineStr"/>
+      <c r="Z107" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA107" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB107" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: self-call restriction (msg.sender == address(this)) on execute((address,uint256,bytes)[]) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC107" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD107" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE107" s="12" t="inlineStr">
+        <is>
+          <t>2103-byte runtime on bnb exposing 2 dispatched function(s): 0x1d92e4b6, execute((address,uint256,bytes)[]) Embedded strings mention: Signed Message.
+Protection(s) found: self-call restriction (msg.sender == address(this)) on execute((address,uint256,bytes)[]) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent; signature-derived authorization branch (ecrecover) on 0x1d92e4b6
+Instruction census (whole contract): ADDRESS×4, CALL×1, CALLER×1, SSTORE×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF107" s="12" t="inlineStr">
+        <is>
+          <t>• 0x1d92e4b6: every path to a sensitive operation passes an authorization check — check found: signature_authorization; storage_condition
+• execute((address,uint256,bytes)[]): every path to a sensitive operation passes an authorization check — check found: self_call_check; storage_condition</t>
+        </is>
+      </c>
+      <c r="AG107" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=2103 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "mapping(address =&gt; uint256)", "n_reads": 0, "n_writes": 2}]</t>
+        </is>
+      </c>
+      <c r="AH107" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
@@ -14378,6 +20617,58 @@
       <c r="W108" s="6" t="inlineStr"/>
       <c r="X108" s="8" t="inlineStr"/>
       <c r="Y108" s="8" t="inlineStr"/>
+      <c r="Z108" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA108" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB108" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: rescue(): CALL at pc=527 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC108" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD108" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE108" s="12" t="inlineStr">
+        <is>
+          <t>1493-byte runtime on ethereum exposing 1 dispatched function(s): rescue()
+Concern(s) found: rescue(): CALL at pc=527 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; rescue(): CALL at pc=345 to unresolved with value from calldata, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; rescue(): CALL at pc=692 to unresolved with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time
+Instruction census (whole contract): ADDRESS×1, CALL×4, CALLER×1, ORIGIN×2, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF108" s="12" t="inlineStr">
+        <is>
+          <t>• rescue(): an unauthenticated path to a sensitive operation exists — check found: tx_origin_check
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG108" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=1493 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH108" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [885]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
@@ -14505,6 +20796,62 @@
       <c r="W109" s="9" t="inlineStr"/>
       <c r="X109" s="8" t="inlineStr"/>
       <c r="Y109" s="8" t="inlineStr"/>
+      <c r="Z109" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA109" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB109" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0xe6fb99ea: CALL at pc=357 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC109" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD109" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE109" s="12" t="inlineStr">
+        <is>
+          <t>1291-byte runtime on base exposing 4 dispatched function(s): 0x46bd1e9b, 0x5d3d957f, counter(), 0xe6fb99ea
+Concern(s) found: 0xe6fb99ea: CALL at pc=357 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0xe6fb99ea: CALL at pc=572 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0x46bd1e9b: SSTORE to slot 0x0 at pc=183 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x5d3d957f: SSTORE to slot 0x0 at pc=183 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls
+Instruction census (whole contract): CALL×2, CALLER×2, SSTORE×1</t>
+        </is>
+      </c>
+      <c r="AF109" s="12" t="inlineStr">
+        <is>
+          <t>• 0x46bd1e9b: an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• 0x5d3d957f: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• counter(): no sensitive operation reachable
+• 0xe6fb99ea: an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]</t>
+        </is>
+      </c>
+      <c r="AG109" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=1291 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "uint256", "n_reads": 3, "n_writes": 2}]
+addresses embedded in the code: [{"bytecode_offset": 230, "address": "0x49403f388c16fa54578843510e2a73238d6b7802"}]</t>
+        </is>
+      </c>
+      <c r="AH109" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0xe6fb99ea</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
@@ -14632,6 +20979,65 @@
       <c r="W110" s="6" t="inlineStr"/>
       <c r="X110" s="8" t="inlineStr"/>
       <c r="Y110" s="8" t="inlineStr"/>
+      <c r="Z110" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA110" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB110" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: msg.sender compared against a stored authority on 0x089b0aeb, 0x90c48649, 0x974ee7c2, 0xac8ebd8f The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC110" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD110" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE110" s="12" t="inlineStr">
+        <is>
+          <t>3284-byte runtime on base exposing 8 dispatched function(s): 0x089b0aeb, 0x2859ecaf, 0x73a8c682, owner(), 0x90c48649, 0x974ee7c2, 0xac8ebd8f, 0xe0615b01 Embedded strings mention: Not owner.
+Protection(s) found: msg.sender compared against a stored authority on 0x089b0aeb, 0x90c48649, 0x974ee7c2, 0xac8ebd8f
+Instruction census (whole contract): CALL×1, CALLER×6, SSTORE×3</t>
+        </is>
+      </c>
+      <c r="AF110" s="12" t="inlineStr">
+        <is>
+          <t>• 0x089b0aeb: every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_condition
+• 0x2859ecaf: no sensitive operation reachable
+• 0x73a8c682: no sensitive operation reachable
+• owner(): no sensitive operation reachable
+• 0x90c48649: every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check
+• 0x974ee7c2: every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check
+• 0xac8ebd8f: every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check
+• 0xe0615b01: no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG110" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=3284 bytes
+verified source=True
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 4, "n_writes": 0}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "address", "n_reads": 2, "n_writes": 1}, {"slot": "00000000000</t>
+        </is>
+      </c>
+      <c r="AH110" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
@@ -14739,6 +21145,59 @@
       <c r="W111" s="9" t="inlineStr"/>
       <c r="X111" s="8" t="inlineStr"/>
       <c r="Y111" s="8" t="inlineStr"/>
+      <c r="Z111" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA111" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB111" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: &lt;no dispatcher recovered; analysed from pc=0&gt;: CALL at pc=106 to 0x4050bdbef63a00415e67b2f691bd8ff52e4215bb with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time The source static analyzer's verdict was assessed as CONTRADICTED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC111" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONTRADICTED</t>
+        </is>
+      </c>
+      <c r="AD111" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: The source analyzer did not flag this contract, yet an external call is reachable from the receive()/fallback() path without passing any caller authorization branch. `unflagged` is a weak signal by construction — the negatives in this dataset are rule-silent, never benignity-verified — so this is a plausible source-rule miss rather than a contradiction of a positive finding.</t>
+        </is>
+      </c>
+      <c r="AE111" s="12" t="inlineStr">
+        <is>
+          <t>468-byte runtime on ethereum exposing 0 dispatched function(s): &lt;no dispatcher recovered; analysed from pc=0&gt;
+Concern(s) found: &lt;no dispatcher recovered; analysed from pc=0&gt;: CALL at pc=106 to 0x4050bdbef63a00415e67b2f691bd8ff52e4215bb with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 1, 'CALLCODE': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx1, CALLCODEx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×1, CALLCODE×1</t>
+        </is>
+      </c>
+      <c r="AF111" s="12" t="inlineStr">
+        <is>
+          <t>• &lt;no dispatcher recovered; analysed from pc=0&gt;: an unauthenticated path to a sensitive operation exists
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG111" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=468 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 39, "address": "0x4050bdbef63a00415e67b2f691bd8ff52e4215bb"}]</t>
+        </is>
+      </c>
+      <c r="AH111" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALLCODE': [435]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
@@ -14866,6 +21325,58 @@
       <c r="W112" s="6" t="inlineStr"/>
       <c r="X112" s="8" t="inlineStr"/>
       <c r="Y112" s="8" t="inlineStr"/>
+      <c r="Z112" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA112" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB112" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x471857b8: tx.origin must equal the hardcoded address 0x757bcedab1f6594015c38bd880db1848bd7c947e. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC112" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD112" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE112" s="12" t="inlineStr">
+        <is>
+          <t>429-byte runtime on ethereum exposing 1 dispatched function(s): 0x471857b8
+Concern(s) found: 0x471857b8: tx.origin must equal the hardcoded address 0x757bcedab1f6594015c38bd880db1848bd7c947e. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×1, CALLER×1, ORIGIN×1</t>
+        </is>
+      </c>
+      <c r="AF112" s="12" t="inlineStr">
+        <is>
+          <t>• 0x471857b8: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x757bcedab1f6594015c38bd880db1848bd7c947e</t>
+        </is>
+      </c>
+      <c r="AG112" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=429 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 77, "address": "0x757bcedab1f6594015c38bd880db1848bd7c947e"}]</t>
+        </is>
+      </c>
+      <c r="AH112" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
@@ -14993,6 +21504,65 @@
       <c r="W113" s="9" t="inlineStr"/>
       <c r="X113" s="8" t="inlineStr"/>
       <c r="Y113" s="8" t="inlineStr"/>
+      <c r="Z113" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA113" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB113" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CREATE2': [2345]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC113" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD113" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE113" s="12" t="inlineStr">
+        <is>
+          <t>2386-byte runtime on ethereum exposing 7 dispatched function(s): readSlot(uint256), owner(), 0xa1af26e9, 0xb5786fde, 0xd7266ec4, emergencyWithdraw(), 0xfbc0d035
+Protection(s) found: msg.sender compared against a stored authority on 0xa1af26e9, 0xb5786fde, 0xfbc0d035, emergencyWithdraw()
+Instruction census (whole contract): CALL×1, CALLER×6, CREATE2×1, SSTORE×3</t>
+        </is>
+      </c>
+      <c r="AF113" s="12" t="inlineStr">
+        <is>
+          <t>• readSlot(uint256): no sensitive operation reachable
+• owner(): no sensitive operation reachable
+• 0xa1af26e9: every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check
+• 0xb5786fde: every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check
+• 0xd7266ec4: no sensitive operation reachable
+• emergencyWithdraw(): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_condition
+• 0xfbc0d035: every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG113" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=2386 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 7, "n_writes": 3}]</t>
+        </is>
+      </c>
+      <c r="AH113" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CREATE2': [2345]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
@@ -15120,6 +21690,100 @@
       <c r="W114" s="6" t="inlineStr"/>
       <c r="X114" s="8" t="inlineStr"/>
       <c r="Y114" s="8" t="inlineStr"/>
+      <c r="Z114" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA114" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB114" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: sendViaTransfer(address): CALL at pc=6209 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC114" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD114" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE114" s="12" t="inlineStr">
+        <is>
+          <t>10059-byte runtime on bnb exposing 42 dispatched function(s): 0x0252971b, 0x1896a129, 0x1f0e6452, 0x1f6b2719, 0x271e6a10, 0x2d4ca026, 0x2d72f306, 0x2de12dc8, 0x33cbec40, 0x3df1abd0 Embedded strings mention: Signed Message.
+Concern(s) found: sendViaTransfer(address): CALL at pc=6209 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; sendViaSend(address): CALL at pc=6371 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; sendViaCall(address): CALL at pc=6760 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; call(address): CALL at pc=8233 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0x3f2a4030: DELEGATECALL at pc=6074 to ['calldata'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; transfer(): CALL at pc=7063 to unresolved with value from literal 1000, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; send(): CALL at pc=7625 to unresolved with value from literal 1000, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time
+Protection(s) found: signature-derived authorization branch (ecrecover) on 0xb1779070
+Instruction census (whole contract): ADDRESS×3, CALL×6, CALLER×10, DELEGATECALL×1, ORIGIN×1, SSTORE×6, STATICCALL×4</t>
+        </is>
+      </c>
+      <c r="AF114" s="12" t="inlineStr">
+        <is>
+          <t>• 0x0252971b: no sensitive operation reachable [analysis incomplete for this function]
+• 0x1896a129: no sensitive operation reachable
+• 0x1f0e6452: no sensitive operation reachable
+• 0x1f6b2719: no sensitive operation reachable
+• 0x271e6a10: no sensitive operation reachable [analysis incomplete for this function]
+• 0x2d4ca026: no sensitive operation reachable
+• 0x2d72f306: no sensitive operation reachable
+• 0x2de12dc8: no sensitive operation reachable
+• 0x33cbec40: no sensitive operation reachable
+• 0x3df1abd0: no sensitive operation reachable
+• 0x3ea7ef55: no sensitive operation reachable
+• 0x3f1f12d1: no sensitive operation reachable
+• 0x3f2a4030: an unauthenticated path to a sensitive operation exists
+• value(): no sensitive operation reachable
+• balanceThis(): no sensitive operation reachable
+• num(): no sensitive operation reachable
+• sendViaTransfer(address): an unauthenticated path to a sensitive operation exists
+• sender(): no sensitive operation reachable
+• 0x731a4f3d: no sensitive operation reachable [analysis incomplete for this function]
+• sendViaSend(address): an unauthenticated path to a sensitive operation exists
+• 0x7a9f75d1: no sensitive operation reachable
+• 0x7f846529: no sensitive operation reachable
+• 0x82b4b235: no sensitive operation reachable
+• sendViaCall(address): an unauthenticated path to a sensitive operation exists
+• 0x8a0c7548: no sensitive operation reachable
+• transfer(): an unauthenticated path to a sensitive operation exists — check found: caller_check
+• get_block_timestamp(): no sensitive operation reachable
+• 0x95f146a2: no sensitive operation reachable
+• 0x9724283f: no sensitive operation reachable
+• check_balance(): no sensitive operation reachable
+• 0xa1e5855d: no sensitive operation reachable [analysis incomplete for this function]
+• 0xa815af09: no sensitive operation reachable
+• 0xb1779070: no sensitive operation reachable — check found: signature_authorization
+• send(): an unauthenticated path to a sensitive operation exists
+• balance(): no sensitive operation reachable
+• 0xbad49bbd: no sensitive operation reachable
+• 0xc70cf32d: no sensitive operation reachable
+• 0xc7e47246: no sensitive operation reachable [analysis incomplete for this function]
+• get_msg_sender(): no sensitive operation reachable
+• 0xefc9b76b: no sensitive operation reachable [analysis incomplete for this function]
+• call(address): an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• get_block_number(): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG114" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=10059 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000002", "offset": 0, "type": "uint256", "n_reads": 1, "n_writes": 0}, {"slot": "0000000000000000000000000000000000000000000000000000000000000003", "offset": 0, "type": "address", "n_reads": 1, "n_writes": 0}, {"slot": "00000000000</t>
+        </is>
+      </c>
+      <c r="AH114" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x0252971b, 0x271e6a10, 0x731a4f3d, 0xa1e5855d, 0xc7e47246, 0xefc9b76b, call(address)</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
@@ -15247,6 +21911,57 @@
       <c r="W115" s="9" t="inlineStr"/>
       <c r="X115" s="8" t="inlineStr"/>
       <c r="Y115" s="8" t="inlineStr"/>
+      <c r="Z115" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA115" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB115" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [598, 3207], 'CREATE': [3200], 'SELFDESTRUCT': [3205]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC115" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD115" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE115" s="12" t="inlineStr">
+        <is>
+          <t>3242-byte runtime on base exposing 1 dispatched function(s): 0xcb3a0d5c
+Instruction census (whole contract): CALL×2, CALLER×1, CREATE×1, ORIGIN×1, SELFDESTRUCT×1, STATICCALL×4</t>
+        </is>
+      </c>
+      <c r="AF115" s="12" t="inlineStr">
+        <is>
+          <t>• 0xcb3a0d5c: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 4 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG115" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=3242 bytes
+verified source=False
+other chains with identical bytecode: ["base"]</t>
+        </is>
+      </c>
+      <c r="AH115" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [598, 3207], 'CREATE': [3200], 'SELFDESTRUCT': [3205]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
@@ -15374,6 +22089,64 @@
       <c r="W116" s="6" t="inlineStr"/>
       <c r="X116" s="8" t="inlineStr"/>
       <c r="Y116" s="8" t="inlineStr"/>
+      <c r="Z116" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA116" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB116" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: self-call restriction (msg.sender == address(this)) on 0xb6b416e9, 0xd655ecfe, executeTransaction(address,uint256,bytes,uint256), withdraw(uint256) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC116" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD116" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE116" s="12" t="inlineStr">
+        <is>
+          <t>6736-byte runtime on bnb exposing 8 dispatched function(s): executeTransaction(address,uint256,bytes,uint256), getBalance(), 0x2045e862, withdraw(uint256), recoverSigner(bytes32,bytes), 0xadf5d5f0, 0xb6b416e9, 0xd655ecfe Embedded strings mention: Signed Message.
+Protection(s) found: self-call restriction (msg.sender == address(this)) on 0xb6b416e9, 0xd655ecfe, executeTransaction(address,uint256,bytes,uint256), withdraw(uint256) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent; signature-derived authorization branch (ecrecover) on 0xadf5d5f0, 0xb6b416e9, recoverSigner(bytes32,bytes)
+Instruction census (whole contract): ADDRESS×5, CALL×3, CALLER×5, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF116" s="12" t="inlineStr">
+        <is>
+          <t>• executeTransaction(address,uint256,bytes,uint256): every path to a sensitive operation passes an authorization check — check found: self_call_check [analysis incomplete for this function]
+• getBalance(): no sensitive operation reachable
+• 0x2045e862: no sensitive operation reachable
+• withdraw(uint256): every path to a sensitive operation passes an authorization check — check found: self_call_check; caller_check
+• recoverSigner(bytes32,bytes): no sensitive operation reachable — check found: signature_authorization
+• 0xadf5d5f0: no sensitive operation reachable — check found: signature_authorization
+• 0xb6b416e9: every path to a sensitive operation passes an authorization check — check found: signature_authorization; self_call_check [analysis incomplete for this function]
+• 0xd655ecfe: every path to a sensitive operation passes an authorization check — check found: self_call_check [analysis incomplete for this function]</t>
+        </is>
+      </c>
+      <c r="AG116" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=6736 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]</t>
+        </is>
+      </c>
+      <c r="AH116" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0xb6b416e9, 0xd655ecfe, executeTransaction(address,uint256,bytes,uint256)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
@@ -15481,6 +22254,58 @@
       <c r="W117" s="9" t="inlineStr"/>
       <c r="X117" s="8" t="inlineStr"/>
       <c r="Y117" s="8" t="inlineStr"/>
+      <c r="Z117" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA117" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB117" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [246]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONTRADICTED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC117" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONTRADICTED</t>
+        </is>
+      </c>
+      <c r="AD117" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: The source analyzer did not flag this contract, yet an external call is reachable from the receive()/fallback() path without passing any caller authorization branch. `unflagged` is a weak signal by construction — the negatives in this dataset are rule-silent, never benignity-verified — so this is a plausible source-rule miss rather than a contradiction of a positive finding.</t>
+        </is>
+      </c>
+      <c r="AE117" s="12" t="inlineStr">
+        <is>
+          <t>633-byte runtime on bnb exposing 0 dispatched function(s): &lt;no dispatcher recovered; analysed from pc=0&gt;
+Instruction census (whole contract): CALL×2, CALLER×1, ORIGIN×1</t>
+        </is>
+      </c>
+      <c r="AF117" s="12" t="inlineStr">
+        <is>
+          <t>• &lt;no dispatcher recovered; analysed from pc=0&gt;: an unauthenticated path to a sensitive operation exists
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG117" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=633 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+addresses embedded in the code: [{"bytecode_offset": 46, "address": "0x5d28e96243e50c8a5d92b07c79e5a61b2b7c46b6"}, {"bytecode_offset": 179, "address": "0x6a81a1ba2c6946ed296c4ccade3d4b2bbd1b324e"}]</t>
+        </is>
+      </c>
+      <c r="AH117" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [246]}) — capability here is a lower bound; unauthenticated call(s) forwarding only msg.value to a fixed destination ([('&lt;no dispatcher recovered; analysed from pc=0&gt;', 113, '0x5d28e96243e50c8a5d92b07c79e5a61b2b7c46b6')]) — a caller can only donate their own ETH, so this is not by itself a path to the account's assets</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
@@ -15608,6 +22433,62 @@
       <c r="W118" s="6" t="inlineStr"/>
       <c r="X118" s="8" t="inlineStr"/>
       <c r="Y118" s="8" t="inlineStr"/>
+      <c r="Z118" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA118" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB118" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: initialize(): SSTORE to slot 0x0 at pc=909 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC118" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD118" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE118" s="12" t="inlineStr">
+        <is>
+          <t>2018-byte runtime on ethereum exposing 4 dispatched function(s): initialized(), sweepToken(address,address,uint256), initialize(), 0xcf87a0df
+Concern(s) found: initialize(): SSTORE to slot 0x0 at pc=909 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; initialize(): SSTORE to slot 0x0 at pc=935 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls
+Instruction census (whole contract): CALL×1, CALLER×1, ORIGIN×2, SELFDESTRUCT×1, SSTORE×2</t>
+        </is>
+      </c>
+      <c r="AF118" s="12" t="inlineStr">
+        <is>
+          <t>• initialized(): no sensitive operation reachable
+• sweepToken(address,address,uint256): no sensitive operation reachable
+• initialize(): an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• 0xcf87a0df: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG118" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=2018 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 4, "n_writes": 1}, {"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 20, "type": "bool", "n_reads": 3, "n_writes": 1}]</t>
+        </is>
+      </c>
+      <c r="AH118" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [645], 'SELFDESTRUCT': [2000]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
@@ -15735,6 +22616,57 @@
       <c r="W119" s="9" t="inlineStr"/>
       <c r="X119" s="8" t="inlineStr"/>
       <c r="Y119" s="8" t="inlineStr"/>
+      <c r="Z119" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA119" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB119" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored. The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC119" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD119" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE119" s="12" t="inlineStr">
+        <is>
+          <t>1602-byte runtime on optimism exposing 1 dispatched function(s): 0x4bf530c8
+Concern(s) found: the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×1</t>
+        </is>
+      </c>
+      <c r="AF119" s="12" t="inlineStr">
+        <is>
+          <t>• 0x4bf530c8: an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]</t>
+        </is>
+      </c>
+      <c r="AG119" s="12" t="inlineStr">
+        <is>
+          <t>chain=optimism
+runtime size=1602 bytes
+verified source=True
+other chains with identical bytecode: ["optimism"]</t>
+        </is>
+      </c>
+      <c r="AH119" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x4bf530c8; unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: 0x4bf530c8 pc=212 -&gt; unresolved (value=memory, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
@@ -15862,6 +22794,62 @@
       <c r="W120" s="6" t="inlineStr"/>
       <c r="X120" s="8" t="inlineStr"/>
       <c r="Y120" s="8" t="inlineStr"/>
+      <c r="Z120" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA120" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB120" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: multicall(address,(address,bytes)[]): CALL at pc=444 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC120" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD120" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE120" s="12" t="inlineStr">
+        <is>
+          <t>1118-byte runtime on arbitrum exposing 4 dispatched function(s): get_block_hash_257335279069929(uint256), swapExactTokensForTokens(uint256,uint256,address[],address,uint256), allowance(address,address), multicall(address,(address,bytes)[])
+Concern(s) found: multicall(address,(address,bytes)[]): CALL at pc=444 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; get_block_hash_257335279069929(uint256): SSTORE to slot 0x0 at pc=522 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls
+Protection(s) found: self-call restriction (msg.sender == address(this)) on multicall(address,(address,bytes)[]) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent
+Instruction census (whole contract): ADDRESS×4, CALL×1, CALLER×1, SSTORE×1, STATICCALL×2</t>
+        </is>
+      </c>
+      <c r="AF120" s="12" t="inlineStr">
+        <is>
+          <t>• get_block_hash_257335279069929(uint256): an unauthenticated path to a sensitive operation exists
+• swapExactTokensForTokens(uint256,uint256,address[],address,uint256): no sensitive operation reachable
+• allowance(address,address): no sensitive operation reachable
+• multicall(address,(address,bytes)[]): an unauthenticated path to a sensitive operation exists — check found: self_call_check</t>
+        </is>
+      </c>
+      <c r="AG120" s="12" t="inlineStr">
+        <is>
+          <t>chain=arbitrum
+runtime size=1118 bytes
+verified source=False
+other chains with identical bytecode: ["arbitrum", "base", "ethereum", "polygon"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "uint256", "n_reads": 1, "n_writes": 0}]</t>
+        </is>
+      </c>
+      <c r="AH120" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
@@ -15989,6 +22977,57 @@
       <c r="W121" s="9" t="inlineStr"/>
       <c r="X121" s="8" t="inlineStr"/>
       <c r="Y121" s="8" t="inlineStr"/>
+      <c r="Z121" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA121" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB121" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'DELEGATECALL': [414], 'CALLCODE': [2550]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC121" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD121" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE121" s="12" t="inlineStr">
+        <is>
+          <t>2574-byte runtime on base exposing 1 dispatched function(s): executeBatch((address,uint256,bytes)[])
+Instruction census (whole contract): ADDRESS×1, CALLCODE×1, CALLER×2, DELEGATECALL×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF121" s="12" t="inlineStr">
+        <is>
+          <t>• executeBatch((address,uint256,bytes)[]): no sensitive operation reachable [analysis incomplete for this function]
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG121" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=2574 bytes
+verified source=False
+other chains with identical bytecode: ["base"]</t>
+        </is>
+      </c>
+      <c r="AH121" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'DELEGATECALL': [414], 'CALLCODE': [2550]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: executeBatch((address,uint256,bytes)[])</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
@@ -16116,6 +23155,73 @@
       <c r="W122" s="6" t="inlineStr"/>
       <c r="X122" s="8" t="inlineStr"/>
       <c r="Y122" s="8" t="inlineStr"/>
+      <c r="Z122" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA122" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB122" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x94d6639f: SSTORE to slot 0x4 at pc=2065 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC122" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD122" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE122" s="12" t="inlineStr">
+        <is>
+          <t>7507-byte runtime on bnb exposing 15 dispatched function(s): reward(), 0x23751c62, 0x661e1e92, 0x94d6639f, 0x96713416, 0x9d31acad, 0xa4cd4d54, 0xb176dcae, balance(), 0xba24b5f3
+Concern(s) found: 0x94d6639f: SSTORE to slot 0x4 at pc=2065 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x96713416: SSTORE to slot 0x5 at pc=2236 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0xd83dc88c: SSTORE to slot 0x5 at pc=4886 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls
+Instruction census (whole contract): CALL×1, ORIGIN×12, SSTORE×3, STATICCALL×24</t>
+        </is>
+      </c>
+      <c r="AF122" s="12" t="inlineStr">
+        <is>
+          <t>• reward(): no sensitive operation reachable
+• 0x23751c62: no sensitive operation reachable — check found: storage_condition; storage_condition
+• 0x661e1e92: no sensitive operation reachable — check found: storage_condition; storage_condition
+• 0x94d6639f: an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• 0x96713416: an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• 0x9d31acad: no sensitive operation reachable — check found: storage_condition; storage_condition
+• 0xa4cd4d54: no sensitive operation reachable — check found: storage_condition; storage_condition
+• 0xb176dcae: no sensitive operation reachable — check found: storage_condition; storage_condition
+• balance(): no sensitive operation reachable
+• 0xba24b5f3: no sensitive operation reachable — check found: storage_condition; storage_condition
+• 0xc05ad474: no sensitive operation reachable — check found: storage_condition; storage_condition
+• 0xce418d79: no sensitive operation reachable — check found: storage_condition; storage_condition
+• 0xd83dc88c: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• init(): no sensitive operation reachable
+• 0xf8551285: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG122" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=7507 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 4, "n_writes": 0}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "address", "n_reads": 3, "n_writes": 0}, {"slot": "00000000000</t>
+        </is>
+      </c>
+      <c r="AH122" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [4945]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
@@ -16243,6 +23349,72 @@
       <c r="W123" s="9" t="inlineStr"/>
       <c r="X123" s="8" t="inlineStr"/>
       <c r="Y123" s="8" t="inlineStr"/>
+      <c r="Z123" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA123" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB123" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: aggregate3Value((address,bool,uint256,bytes)[]): CALL at pc=967 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC123" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD123" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE123" s="12" t="inlineStr">
+        <is>
+          <t>3750-byte runtime on bnb exposing 16 dispatched function(s): getCurrentBlockTimestamp(), aggregate3Value((address,bool,uint256,bytes)[]), aggregate((address,bytes)[]), getLastBlockHash(), getChainId(), tryBlockAndAggregate(bool,(address,bytes)[]), getBasefee(), getBlockNumber(), getEthBalance(address), getCurrentBlockDifficulty() Embedded strings mention: Multicall.
+Concern(s) found: aggregate3Value((address,bool,uint256,bytes)[]): CALL at pc=967 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; aggregate((address,bytes)[]): CALL at pc=1474 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; tryBlockAndAggregate(bool,(address,bytes)[]): CALL at pc=2335 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; aggregate3((address,bool,bytes)[]): CALL at pc=1904 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; tryAggregate(bool,(address,bytes)[]): CALL at pc=2335 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; blockAndAggregate((address,bytes)[]): CALL at pc=2335 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call
+Instruction census (whole contract): CALL×4, CALLER×1</t>
+        </is>
+      </c>
+      <c r="AF123" s="12" t="inlineStr">
+        <is>
+          <t>• getCurrentBlockTimestamp(): no sensitive operation reachable
+• aggregate3Value((address,bool,uint256,bytes)[]): an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• aggregate((address,bytes)[]): an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• getLastBlockHash(): no sensitive operation reachable
+• getChainId(): no sensitive operation reachable
+• tryBlockAndAggregate(bool,(address,bytes)[]): an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• getBasefee(): no sensitive operation reachable
+• getBlockNumber(): no sensitive operation reachable
+• getEthBalance(address): no sensitive operation reachable
+• getCurrentBlockDifficulty(): no sensitive operation reachable
+• aggregate3((address,bool,bytes)[]): an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• getCurrentBlockGasLimit(): no sensitive operation reachable
+• getCurrentBlockCoinbase(): no sensitive operation reachable
+• tryAggregate(bool,(address,bytes)[]): an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• blockAndAggregate((address,bytes)[]): an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• getBlockHash(uint256): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG123" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=3750 bytes
+verified source=True
+other chains with identical bytecode: ["bnb", "ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH123" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: aggregate((address,bytes)[]), aggregate3((address,bool,bytes)[]), aggregate3Value((address,bool,uint256,bytes)[]), blockAndAggregate((address,bytes)[]), tryAggregate(bool,(address,bytes)[]), tryBlockAndAggregate(bool,(address,bytes)[])</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
@@ -16370,6 +23542,64 @@
       <c r="W124" s="6" t="inlineStr"/>
       <c r="X124" s="8" t="inlineStr"/>
       <c r="Y124" s="8" t="inlineStr"/>
+      <c r="Z124" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA124" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB124" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALLCODE': [4923]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC124" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD124" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE124" s="12" t="inlineStr">
+        <is>
+          <t>4957-byte runtime on bnb exposing 6 dispatched function(s): allowedCallers(address), nonces(address), 0xa239d6d9, 0xb13febc6, updateCaller(address,bool), admin() Embedded strings mention: Signed Message.
+Protection(s) found: signature-derived authorization branch (ecrecover) on 0xb13febc6; msg.sender compared against a stored authority on updateCaller(address,bool)
+Instruction census (whole contract): CALLCODE×1, CALLER×1, DELEGATECALL×1, SSTORE×2, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF124" s="12" t="inlineStr">
+        <is>
+          <t>• allowedCallers(address): no sensitive operation reachable
+• nonces(address): no sensitive operation reachable
+• 0xa239d6d9: no sensitive operation reachable
+• 0xb13febc6: every path to a sensitive operation passes an authorization check — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• updateCaller(address,bool): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check
+• admin(): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG124" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=4957 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 2, "n_writes": 0}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "mapping(address =&gt; bool)", "n_reads": 2, "n_writes": 1}, {"sl</t>
+        </is>
+      </c>
+      <c r="AH124" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALLCODE': [4923]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0xb13febc6</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
@@ -16497,6 +23727,61 @@
       <c r="W125" s="9" t="inlineStr"/>
       <c r="X125" s="8" t="inlineStr"/>
       <c r="Y125" s="8" t="inlineStr"/>
+      <c r="Z125" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA125" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB125" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x46b1788d: tx.origin must equal the hardcoded address 0xf56a9c9c160fefbd147118b618962e811b077d5c. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC125" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD125" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE125" s="12" t="inlineStr">
+        <is>
+          <t>4146-byte runtime on polygon exposing 4 dispatched function(s): onERC721Received(address,address,uint256,bytes), 0x46b1788d, onERC1155BatchReceived(address,address,uint256[],uint256[],bytes), onERC1155Received(address,address,uint256,uint256,bytes) Embedded strings mention: Not owner.
+Concern(s) found: 0x46b1788d: tx.origin must equal the hardcoded address 0xf56a9c9c160fefbd147118b618962e811b077d5c. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×1, CALL×3, CALLER×1, ORIGIN×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF125" s="12" t="inlineStr">
+        <is>
+          <t>• onERC721Received(address,address,uint256,bytes): no sensitive operation reachable
+• 0x46b1788d: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xf56a9c9c160fefbd147118b618962e811b077d5c [analysis incomplete for this function]
+• onERC1155BatchReceived(address,address,uint256[],uint256[],bytes): no sensitive operation reachable
+• onERC1155Received(address,address,uint256,uint256,bytes): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG125" s="12" t="inlineStr">
+        <is>
+          <t>chain=polygon
+runtime size=4146 bytes
+verified source=False
+other chains with identical bytecode: ["polygon"]</t>
+        </is>
+      </c>
+      <c r="AH125" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [879]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x46b1788d</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
@@ -16624,6 +23909,61 @@
       <c r="W126" s="6" t="inlineStr"/>
       <c r="X126" s="8" t="inlineStr"/>
       <c r="Y126" s="8" t="inlineStr"/>
+      <c r="Z126" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA126" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB126" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: initialize(address): SSTORE to slot 0x0 at pc=628 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC126" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD126" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE126" s="12" t="inlineStr">
+        <is>
+          <t>1903-byte runtime on bnb exposing 3 dispatched function(s): call(address[],bytes[]), owner(), initialize(address)
+Concern(s) found: initialize(address): SSTORE to slot 0x0 at pc=628 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls
+Protection(s) found: msg.sender compared against a stored authority on call(address[],bytes[])
+Instruction census (whole contract): CALL×1, CALLER×1, SSTORE×1</t>
+        </is>
+      </c>
+      <c r="AF126" s="12" t="inlineStr">
+        <is>
+          <t>• call(address[],bytes[]): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check [analysis incomplete for this function]
+• owner(): no sensitive operation reachable
+• initialize(address): an unauthenticated path to a sensitive operation exists — check found: storage_condition</t>
+        </is>
+      </c>
+      <c r="AG126" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=1903 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 3, "n_writes": 1}]</t>
+        </is>
+      </c>
+      <c r="AH126" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: call(address[],bytes[])</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
@@ -16751,6 +24091,78 @@
       <c r="W127" s="9" t="inlineStr"/>
       <c r="X127" s="8" t="inlineStr"/>
       <c r="Y127" s="8" t="inlineStr"/>
+      <c r="Z127" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA127" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB127" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x0a5491b4: msg.sender must equal the hardcoded address 0x3d0ef8f0911e975b9726d7728e7b61d4561f1725. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC127" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD127" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE127" s="12" t="inlineStr">
+        <is>
+          <t>13991-byte runtime on bnb exposing 19 dispatched function(s): 0x0a5491b4, token0(), 0x116210c6, poolAddress(), 0x241e4344, 0x2d803566, 0x2e24f896, withdraw(), lastTick(), 0x5b5dc217 Embedded strings mention: Not owner, not owner.
+Concern(s) found: 0x0a5491b4: msg.sender must equal the hardcoded address 0x3d0ef8f0911e975b9726d7728e7b61d4561f1725. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x241e4344: msg.sender must equal the hardcoded address 0x3d0ef8f0911e975b9726d7728e7b61d4561f1725. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; withdraw(): msg.sender must equal the hardcoded address 0x3d0ef8f0911e975b9726d7728e7b61d4561f1725. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; withdrawToken(address): msg.sender must equal the hardcoded address 0x3d0ef8f0911e975b9726d7728e7b61d4561f1725. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; setPoolAddress(address): msg.sender must equal the hardcoded address 0x3d0ef8f0911e975b9726d7728e7b61d4561f1725. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x2e24f896: SSTORE to slot 0x2 at pc=7396 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x2e24f896: SSTORE to slot 0x2 at pc=7430 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x2e24f896: SSTORE to slot 0x2 at pc=7542 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x5b5dc217: SSTORE to slot 0x3 at pc=3932 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x5b5dc217: SSTORE to slot 0x2 at pc=7396 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x5b5dc217: SSTORE to slot 0x2 at pc=7430 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x5b5dc217: SSTORE to slot 0x2 at pc=7542 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls
+Protection(s) found: callback entry point(s) restricted to a fixed protocol address: pancakeV3MintCallback(uint256,uint256,bytes) — pancakeV3MintCallback(uint256,uint256,bytes) is a callback-shaped entry point restricted to the fixed address 0x3d0ef8f0911e975b9726d7728e7b61d4561f1725; a callback is invoked by a protocol during an operation the account itself started, so this reads as the protocol's prescribed restriction rather than standing third-party access. The identity of 0x3d0ef8f0911e975b9726d7728e7b61d4561f1725 was not independently confirmed.; msg.sender compared against a stored authority on pancakeV3MintCallback(uint256,uint256,bytes)
+Instruction census (whole contract): ADDRESS×9, CALL×11, CALLER×6, ORIGIN×1, SSTORE×11, STATICCALL×13</t>
+        </is>
+      </c>
+      <c r="AF127" s="12" t="inlineStr">
+        <is>
+          <t>• 0x0a5491b4: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x3d0ef8f0911e975b9726d7728e7b61d4561f1725; storage_condition
+• token0(): no sensitive operation reachable
+• 0x116210c6: no sensitive operation reachable
+• poolAddress(): no sensitive operation reachable
+• 0x241e4344: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x3d0ef8f0911e975b9726d7728e7b61d4561f1725
+• 0x2d803566: no sensitive operation reachable
+• 0x2e24f896: an unauthenticated path to a sensitive operation exists — check found: hardcoded_address_check against 0x3d0ef8f0911e975b9726d7728e7b61d4561f1725; storage_condition [analysis incomplete for this function]
+• withdraw(): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x3d0ef8f0911e975b9726d7728e7b61d4561f1725
+• lastTick(): no sensitive operation reachable
+• 0x5b5dc217: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• 0x69dd9807: no sensitive operation reachable — check found: storage_condition
+• 0x85eda707: no sensitive operation reachable
+• withdrawToken(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x3d0ef8f0911e975b9726d7728e7b61d4561f1725
+• isStop(): no sensitive operation reachable
+• pancakeV3MintCallback(uint256,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; hardcoded_address_check against 0x3d0ef8f0911e975b9726d7728e7b61d4561f1725
+• 0xc1ea76d7: no sensitive operation reachable [analysis incomplete for this function]
+• tickSpacing(): no sensitive operation reachable
+• token1(): no sensitive operation reachable
+• setPoolAddress(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x3d0ef8f0911e975b9726d7728e7b61d4561f1725; storage_condition
+• COVERAGE GAP: the analysis never reached 4 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG127" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=13991 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 7, "n_writes": 1}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "address", "n_reads": 5, "n_writes": 1}, {"slot": "00000000000</t>
+        </is>
+      </c>
+      <c r="AH127" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: 0x0a5491b4 (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); 0x0a5491b4 (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); 0x0a5491b4 (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); 0x0a5491b4 (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [3112, 5738, 7088, 7308]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x2e24f896, 0x5b5dc217, 0xc1ea76d7; unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: 0x2e24f896 pc=2905 -&gt; stored(sload) (value=0, data=memory); 0x2e24f896 pc=7741 -&gt; stored(sload) (value=0, data=memory); 0x5b5dc217 pc=7741 -&gt; stored(sload) (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
@@ -16878,6 +24290,58 @@
       <c r="W128" s="6" t="inlineStr"/>
       <c r="X128" s="8" t="inlineStr"/>
       <c r="Y128" s="8" t="inlineStr"/>
+      <c r="Z128" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA128" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB128" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: self-call restriction (msg.sender == address(this)) on execute((address,uint256,bytes)[]) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC128" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD128" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE128" s="12" t="inlineStr">
+        <is>
+          <t>2043-byte runtime on base exposing 1 dispatched function(s): execute((address,uint256,bytes)[])
+Protection(s) found: self-call restriction (msg.sender == address(this)) on execute((address,uint256,bytes)[]) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent
+Instruction census (whole contract): ADDRESS×1, CALL×1, CALLER×4</t>
+        </is>
+      </c>
+      <c r="AF128" s="12" t="inlineStr">
+        <is>
+          <t>• execute((address,uint256,bytes)[]): every path to a sensitive operation passes an authorization check — check found: self_call_check; self_call_check [analysis incomplete for this function]</t>
+        </is>
+      </c>
+      <c r="AG128" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=2043 bytes
+verified source=False
+other chains with identical bytecode: ["base", "bnb", "ethereum", "optimism", "polygon"]
+addresses embedded in the code: [{"bytecode_offset": 124, "address": "0x768f2ebd51176ad3783602dc86cca7c8355cdf94"}]</t>
+        </is>
+      </c>
+      <c r="AH128" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: execute((address,uint256,bytes)[])</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
@@ -17005,6 +24469,62 @@
       <c r="W129" s="9" t="inlineStr"/>
       <c r="X129" s="8" t="inlineStr"/>
       <c r="Y129" s="8" t="inlineStr"/>
+      <c r="Z129" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA129" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB129" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x0ef296c1: CALL at pc=763 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC129" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD129" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE129" s="12" t="inlineStr">
+        <is>
+          <t>1769-byte runtime on bnb exposing 3 dispatched function(s): 0x056b692b, 0x0ef296c1, 0xbce7e77d
+Concern(s) found: 0x0ef296c1: CALL at pc=763 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call
+Protection(s) found: self-call restriction (msg.sender == address(this)) on 0x056b692b, 0x0ef296c1 — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent
+Instruction census (whole contract): ADDRESS×2, CALL×1, CALLCODE×1, CALLER×5, SSTORE×1</t>
+        </is>
+      </c>
+      <c r="AF129" s="12" t="inlineStr">
+        <is>
+          <t>• 0x056b692b: an unauthenticated path to a sensitive operation exists — check found: storage_condition; self_call_check
+• 0x0ef296c1: an unauthenticated path to a sensitive operation exists — check found: storage_condition; self_call_check [analysis incomplete for this function]
+• 0xbce7e77d: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG129" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=1769 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "mapping(address =&gt; bool)", "n_reads": 3, "n_writes": 1}]</t>
+        </is>
+      </c>
+      <c r="AH129" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALLCODE': [1745]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x0ef296c1</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
@@ -17132,6 +24652,68 @@
       <c r="W130" s="6" t="inlineStr"/>
       <c r="X130" s="8" t="inlineStr"/>
       <c r="Y130" s="8" t="inlineStr"/>
+      <c r="Z130" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA130" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB130" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x0c0bf4c1: CALL at pc=503 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC130" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD130" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE130" s="12" t="inlineStr">
+        <is>
+          <t>3211-byte runtime on base exposing 9 dispatched function(s): 0x0c0bf4c1, addVault(address), 0x403c098c, vaults(uint256), factoryAddress(), getVaultsCount(), _factory(), removeVault(uint256), transferOwnership(address)
+Concern(s) found: 0x0c0bf4c1: CALL at pc=503 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call
+Protection(s) found: msg.sender compared against a stored authority on addVault(address), removeVault(uint256), transferOwnership(address)
+Instruction census (whole contract): CALL×2, CALLER×3, DELEGATECALL×1, ORIGIN×3, SSTORE×6</t>
+        </is>
+      </c>
+      <c r="AF130" s="12" t="inlineStr">
+        <is>
+          <t>• 0x0c0bf4c1: an unauthenticated path to a sensitive operation exists
+• addVault(address): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• 0x403c098c: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• vaults(uint256): no sensitive operation reachable — check found: storage_condition
+• factoryAddress(): no sensitive operation reachable
+• getVaultsCount(): no sensitive operation reachable
+• _factory(): no sensitive operation reachable
+• removeVault(uint256): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• transferOwnership(address): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG130" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=3211 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 1, "n_writes": 0}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "address[]", "n_reads": 4, "n_writes": 2}, {"slot": "000000000</t>
+        </is>
+      </c>
+      <c r="AH130" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'DELEGATECALL': [3171]}) — capability here is a lower bound; unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: 0x403c098c pc=1013 -&gt; stored(sload) (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
@@ -17259,6 +24841,62 @@
       <c r="W131" s="9" t="inlineStr"/>
       <c r="X131" s="8" t="inlineStr"/>
       <c r="Y131" s="8" t="inlineStr"/>
+      <c r="Z131" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA131" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB131" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x526ed76e: msg.sender must equal the hardcoded address 0x9300e82d3cad16602eee21c1068accf9a2b2a23c. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC131" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD131" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE131" s="12" t="inlineStr">
+        <is>
+          <t>2923-byte runtime on bnb exposing 3 dispatched function(s): 0x526ed76e, 0x56603732, receiveFlashLoan(address[],uint256[],uint256[],bytes)
+Concern(s) found: 0x526ed76e: msg.sender must equal the hardcoded address 0x9300e82d3cad16602eee21c1068accf9a2b2a23c. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x56603732: tx.origin must equal the hardcoded address 0xea385cdb0db867f0981690332f10a977a6c511ba. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×1, CALL×2, CALLER×2, ORIGIN×1, SSTORE×2</t>
+        </is>
+      </c>
+      <c r="AF131" s="12" t="inlineStr">
+        <is>
+          <t>• 0x526ed76e: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x9300e82d3cad16602eee21c1068accf9a2b2a23c; storage_condition
+• 0x56603732: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xea385cdb0db867f0981690332f10a977a6c511ba; storage_condition
+• receiveFlashLoan(address[],uint256[],uint256[],bytes): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG131" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=2923 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "uint256", "n_reads": 0, "n_writes": 2}]
+addresses embedded in the code: [{"bytecode_offset": 116, "address": "0x9300e82d3cad16602eee21c1068accf9a2b2a23c"}, {"bytecode_offset": 217, "address": "0xea385cdb0db867f0981690332f10a977a6c511ba"}, {"bytecode_offset": 470, "address": "0x8ac76a51cc950d9822d68b83fe1ad97b32cd580d"}, {"bytecode_offset": 601, "address": "0xba122222222</t>
+        </is>
+      </c>
+      <c r="AH131" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: 0x526ed76e (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); 0x56603732 (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [911]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
@@ -17386,6 +25024,56 @@
       <c r="W132" s="6" t="inlineStr"/>
       <c r="X132" s="8" t="inlineStr"/>
       <c r="Y132" s="8" t="inlineStr"/>
+      <c r="Z132" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA132" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB132" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: every dispatched function analysed to completion with no reachable sensitive operation. The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC132" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD132" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE132" s="12" t="inlineStr">
+        <is>
+          <t>1722-byte runtime on base exposing 1 dispatched function(s): execute((bytes,address,uint256)[])
+Instruction census (whole contract): CALL×1, CALLER×1</t>
+        </is>
+      </c>
+      <c r="AF132" s="12" t="inlineStr">
+        <is>
+          <t>• execute((bytes,address,uint256)[]): an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG132" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=1722 bytes
+verified source=False
+other chains with identical bytecode: ["base", "ethereum", "optimism"]</t>
+        </is>
+      </c>
+      <c r="AH132" s="12" t="inlineStr">
+        <is>
+          <t>unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: execute((bytes,address,uint256)[]) pc=188 -&gt; unresolved (value=memory, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
@@ -17493,6 +25181,58 @@
       <c r="W133" s="9" t="inlineStr"/>
       <c r="X133" s="8" t="inlineStr"/>
       <c r="Y133" s="8" t="inlineStr"/>
+      <c r="Z133" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA133" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB133" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: &lt;no dispatcher recovered; analysed from pc=0&gt;: CALL at pc=32 to 0x4d59cd593f6982fdb2eb08bb4e761514b320c14c with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time The source static analyzer's verdict was assessed as CONTRADICTED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC133" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONTRADICTED</t>
+        </is>
+      </c>
+      <c r="AD133" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: The source analyzer did not flag this contract, yet an external call is reachable from the receive()/fallback() path without passing any caller authorization branch. `unflagged` is a weak signal by construction — the negatives in this dataset are rule-silent, never benignity-verified — so this is a plausible source-rule miss rather than a contradiction of a positive finding.</t>
+        </is>
+      </c>
+      <c r="AE133" s="12" t="inlineStr">
+        <is>
+          <t>45-byte runtime on ethereum exposing 0 dispatched function(s): &lt;no dispatcher recovered; analysed from pc=0&gt;
+Concern(s) found: &lt;no dispatcher recovered; analysed from pc=0&gt;: CALL at pc=32 to 0x4d59cd593f6982fdb2eb08bb4e761514b320c14c with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×1</t>
+        </is>
+      </c>
+      <c r="AF133" s="12" t="inlineStr">
+        <is>
+          <t>• &lt;no dispatcher recovered; analysed from pc=0&gt;: an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG133" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=45 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 10, "address": "0x4d59cd593f6982fdb2eb08bb4e761514b320c14c"}]</t>
+        </is>
+      </c>
+      <c r="AH133" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
@@ -17620,6 +25360,80 @@
       <c r="W134" s="6" t="inlineStr"/>
       <c r="X134" s="8" t="inlineStr"/>
       <c r="Y134" s="8" t="inlineStr"/>
+      <c r="Z134" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA134" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB134" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x0a5491b4: msg.sender must equal the hardcoded address 0x58a98a98557adc8aa54d1efd792cc35129bc8ae1. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC134" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD134" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE134" s="12" t="inlineStr">
+        <is>
+          <t>14976-byte runtime on bnb exposing 21 dispatched function(s): 0x0a5491b4, token0(), 0x116210c6, poolAddress(), pancakeV3SwapCallback(int256,int256,bytes), 0x241e4344, 0x2d803566, 0x2e24f896, withdraw(), lastTick() Embedded strings mention: Not owner, not owner.
+Concern(s) found: 0x0a5491b4: msg.sender must equal the hardcoded address 0x58a98a98557adc8aa54d1efd792cc35129bc8ae1. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x241e4344: msg.sender must equal the hardcoded address 0x58a98a98557adc8aa54d1efd792cc35129bc8ae1. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; withdraw(): msg.sender must equal the hardcoded address 0x58a98a98557adc8aa54d1efd792cc35129bc8ae1. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; withdrawToken(address): msg.sender must equal the hardcoded address 0x58a98a98557adc8aa54d1efd792cc35129bc8ae1. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0xcbfa11a2: msg.sender must equal the hardcoded address 0x58a98a98557adc8aa54d1efd792cc35129bc8ae1. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x2e24f896: SSTORE to slot 0x2 at pc=8164 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x2e24f896: SSTORE to slot 0x2 at pc=8198 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x2e24f896: SSTORE to slot 0x2 at pc=8310 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x5b5dc217: SSTORE to slot 0x3 at pc=4654 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x5b5dc217: SSTORE to slot 0x2 at pc=8164 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x5b5dc217: SSTORE to slot 0x2 at pc=8198 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x5b5dc217: SSTORE to slot 0x2 at pc=8310 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls
+Protection(s) found: callback entry point(s) restricted to a fixed protocol address: pancakeV3SwapCallback(int256,int256,bytes) — pancakeV3SwapCallback(int256,int256,bytes) is a callback-shaped entry point restricted to the fixed address 0x58a98a98557adc8aa54d1efd792cc35129bc8ae1; a callback is invoked by a protocol during an operation the account itself started, so this reads as the protocol's prescribed restriction rather than standing third-party access. The identity of 0x58a98a98557adc8aa54d1efd792cc35129bc8ae1 was not independently confirmed.; pancakeV3MintCallback(uint256,uint256,bytes) — pancakeV3MintCallback(uint256,uint256,bytes) is a callback-shaped entry point restricted to the fixed address 0x58a98a98557adc8aa54d1efd792cc35129bc8ae1; a callback is invoked by a protocol during an operation the account itself started, so this reads as the protocol's prescribed restriction rather than standing third-party access. The identity of 0x58a98a98557adc8aa54d1efd792cc35129bc8ae1 was not independently confirmed.; msg.sender compared against a stored authority on pancakeV3MintCallback(uint256,uint256,bytes), pancakeV3SwapCallback(int256,int256,bytes)
+Instruction census (whole contract): ADDRESS×11, CALL×13, CALLER×7, ORIGIN×3, SSTORE×12, STATICCALL×13</t>
+        </is>
+      </c>
+      <c r="AF134" s="12" t="inlineStr">
+        <is>
+          <t>• 0x0a5491b4: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x58a98a98557adc8aa54d1efd792cc35129bc8ae1; storage_condition
+• token0(): no sensitive operation reachable
+• 0x116210c6: no sensitive operation reachable
+• poolAddress(): no sensitive operation reachable
+• pancakeV3SwapCallback(int256,int256,bytes): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; hardcoded_address_check against 0x58a98a98557adc8aa54d1efd792cc35129bc8ae1
+• 0x241e4344: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x58a98a98557adc8aa54d1efd792cc35129bc8ae1
+• 0x2d803566: no sensitive operation reachable
+• 0x2e24f896: an unauthenticated path to a sensitive operation exists — check found: hardcoded_address_check against 0x58a98a98557adc8aa54d1efd792cc35129bc8ae1; storage_condition [analysis incomplete for this function]
+• withdraw(): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x58a98a98557adc8aa54d1efd792cc35129bc8ae1
+• lastTick(): no sensitive operation reachable
+• 0x5b5dc217: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• 0x69dd9807: no sensitive operation reachable — check found: storage_condition
+• 0x85eda707: no sensitive operation reachable
+• withdrawToken(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x58a98a98557adc8aa54d1efd792cc35129bc8ae1
+• isStop(): no sensitive operation reachable
+• pancakeV3MintCallback(uint256,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; hardcoded_address_check against 0x58a98a98557adc8aa54d1efd792cc35129bc8ae1
+• 0xb9f79aa6: no sensitive operation reachable
+• 0xc1ea76d7: no sensitive operation reachable [analysis incomplete for this function]
+• 0xcbfa11a2: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x58a98a98557adc8aa54d1efd792cc35129bc8ae1; storage_condition
+• tickSpacing(): no sensitive operation reachable
+• token1(): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 4 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG134" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=14976 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 8, "n_writes": 1}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "address", "n_reads": 6, "n_writes": 1}, {"slot": "00000000000</t>
+        </is>
+      </c>
+      <c r="AH134" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: 0x0a5491b4 (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); 0x0a5491b4 (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); 0x0a5491b4 (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); 0xcbfa11a2 (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [2484, 6460, 7773, 7993]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x2e24f896, 0x5b5dc217, 0xc1ea76d7; unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: 0x2e24f896 pc=3628 -&gt; stored(sload) (value=0, data=memory); 0x2e24f896 pc=3835 -&gt; stored(sload) (value=0, data=memory); 0x2e24f896 pc=8509 -&gt; stored(sload) (value=0, data=memory); 0x5b5dc217 pc=8509 -&gt; stored(sload) (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
@@ -17747,6 +25561,61 @@
       <c r="W135" s="9" t="inlineStr"/>
       <c r="X135" s="8" t="inlineStr"/>
       <c r="Y135" s="8" t="inlineStr"/>
+      <c r="Z135" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA135" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB135" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: initialize(): SSTORE to slot 0x0 at pc=666 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC135" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD135" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE135" s="12" t="inlineStr">
+        <is>
+          <t>1585-byte runtime on ethereum exposing 3 dispatched function(s): initialized(), sweepToken(address,address,uint256), initialize()
+Concern(s) found: initialize(): SSTORE to slot 0x0 at pc=666 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls
+Instruction census (whole contract): CALL×1, CALLER×1, SSTORE×1</t>
+        </is>
+      </c>
+      <c r="AF135" s="12" t="inlineStr">
+        <is>
+          <t>• initialized(): no sensitive operation reachable
+• sweepToken(address,address,uint256): no sensitive operation reachable
+• initialize(): an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG135" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=1585 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "bool", "n_reads": 3, "n_writes": 1}]</t>
+        </is>
+      </c>
+      <c r="AH135" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [446]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
@@ -17874,6 +25743,57 @@
       <c r="W136" s="6" t="inlineStr"/>
       <c r="X136" s="8" t="inlineStr"/>
       <c r="Y136" s="8" t="inlineStr"/>
+      <c r="Z136" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA136" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB136" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [453, 825]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC136" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD136" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE136" s="12" t="inlineStr">
+        <is>
+          <t>2160-byte runtime on ethereum exposing 1 dispatched function(s): 0x02879e8c
+Instruction census (whole contract): CALL×2, CALLER×4</t>
+        </is>
+      </c>
+      <c r="AF136" s="12" t="inlineStr">
+        <is>
+          <t>• 0x02879e8c: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG136" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=2160 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH136" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [453, 825]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
@@ -18001,6 +25921,59 @@
       <c r="W137" s="9" t="inlineStr"/>
       <c r="X137" s="8" t="inlineStr"/>
       <c r="Y137" s="8" t="inlineStr"/>
+      <c r="Z137" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA137" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB137" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: self-call restriction (msg.sender == address(this)) on 0xf6906e8a — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC137" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD137" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE137" s="12" t="inlineStr">
+        <is>
+          <t>1806-byte runtime on bnb exposing 2 dispatched function(s): unlockCallback(bytes), 0xf6906e8a
+Protection(s) found: self-call restriction (msg.sender == address(this)) on 0xf6906e8a — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent; callback entry point(s) restricted to a fixed protocol address: unlockCallback(bytes) — unlockCallback(bytes) is a callback-shaped entry point restricted to the fixed address 0x28e2ea090877bf75740558f6bfb36a5ffee9e9df; a callback is invoked by a protocol during an operation the account itself started, so this reads as the protocol's prescribed restriction rather than standing third-party access. The identity of 0x28e2ea090877bf75740558f6bfb36a5ffee9e9df was not independently confirmed.
+Instruction census (whole contract): ADDRESS×2, CALL×8, CALLER×2</t>
+        </is>
+      </c>
+      <c r="AF137" s="12" t="inlineStr">
+        <is>
+          <t>• unlockCallback(bytes): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x28e2ea090877bf75740558f6bfb36a5ffee9e9df
+• 0xf6906e8a: every path to a sensitive operation passes an authorization check — check found: self_call_check</t>
+        </is>
+      </c>
+      <c r="AG137" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=1806 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+addresses embedded in the code: [{"bytecode_offset": 133, "address": "0x28e2ea090877bf75740558f6bfb36a5ffee9e9df"}, {"bytecode_offset": 296, "address": "0xede5bfb26399b46d8837ab265e8c4ba5c1705127"}, {"bytecode_offset": 997, "address": "0x105083929bf9bb22c26cb1777ec92661170d4285"}]</t>
+        </is>
+      </c>
+      <c r="AH137" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
@@ -18128,6 +26101,60 @@
       <c r="W138" s="6" t="inlineStr"/>
       <c r="X138" s="8" t="inlineStr"/>
       <c r="Y138" s="8" t="inlineStr"/>
+      <c r="Z138" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA138" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB138" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0xdfb89c37: msg.sender must equal the hardcoded address 0x424242dbaa0d839ab79b5f7cdfa89222c84e18bd. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC138" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD138" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE138" s="12" t="inlineStr">
+        <is>
+          <t>1610-byte runtime on arbitrum exposing 2 dispatched function(s): owner(), 0xdfb89c37
+Concern(s) found: 0xdfb89c37: msg.sender must equal the hardcoded address 0x424242dbaa0d839ab79b5f7cdfa89222c84e18bd. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×1, CALL×3, CALLER×2, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF138" s="12" t="inlineStr">
+        <is>
+          <t>• owner(): no sensitive operation reachable
+• 0xdfb89c37: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x424242dbaa0d839ab79b5f7cdfa89222c84e18bd
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG138" s="12" t="inlineStr">
+        <is>
+          <t>chain=arbitrum
+runtime size=1610 bytes
+verified source=False
+other chains with identical bytecode: ["arbitrum"]
+addresses embedded in the code: [{"bytecode_offset": 383, "address": "0x93f52c811734908a8c186ef26624c6dd968320a8"}, {"bytecode_offset": 495, "address": "0xbc4c97fb9befaa8b41448e1dfcc5236da543217f"}, {"bytecode_offset": 844, "address": "0x45b9ba680e75607626435fde22fdf9d42623c76d"}]</t>
+        </is>
+      </c>
+      <c r="AH138" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [907]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
@@ -18255,6 +26282,57 @@
       <c r="W139" s="9" t="inlineStr"/>
       <c r="X139" s="8" t="inlineStr"/>
       <c r="Y139" s="8" t="inlineStr"/>
+      <c r="Z139" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA139" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB139" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: every dispatched function analysed to completion with no reachable sensitive operation. The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC139" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD139" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE139" s="12" t="inlineStr">
+        <is>
+          <t>464-byte runtime on polygon exposing 2 dispatched function(s): ping(), initialize()
+Instruction census (whole contract): CALLER×1</t>
+        </is>
+      </c>
+      <c r="AF139" s="12" t="inlineStr">
+        <is>
+          <t>• ping(): no sensitive operation reachable
+• initialize(): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG139" s="12" t="inlineStr">
+        <is>
+          <t>chain=polygon
+runtime size=464 bytes
+verified source=True
+other chains with identical bytecode: ["polygon"]</t>
+        </is>
+      </c>
+      <c r="AH139" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
@@ -18382,6 +26460,67 @@
       <c r="W140" s="6" t="inlineStr"/>
       <c r="X140" s="8" t="inlineStr"/>
       <c r="Y140" s="8" t="inlineStr"/>
+      <c r="Z140" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA140" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB140" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [957]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC140" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD140" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE140" s="12" t="inlineStr">
+        <is>
+          <t>4578-byte runtime on ethereum exposing 8 dispatched function(s): tokensReceived(address,address,address,uint256,bytes,bytes), canImplementInterfaceForAddress(bytes32,address), wallets(uint256), owner(), 0xaa77e88b, 0xb37c2d8d, calldatas(uint256), 0xf327de80 Embedded strings mention: Not owner.
+Protection(s) found: msg.sender compared against a stored authority on 0xaa77e88b
+Instruction census (whole contract): CALL×1, CALLER×1, SSTORE×11</t>
+        </is>
+      </c>
+      <c r="AF140" s="12" t="inlineStr">
+        <is>
+          <t>• tokensReceived(address,address,address,uint256,bytes,bytes): no sensitive operation reachable
+• canImplementInterfaceForAddress(bytes32,address): no sensitive operation reachable
+• wallets(uint256): no sensitive operation reachable — check found: storage_condition; storage_condition
+• owner(): no sensitive operation reachable
+• 0xaa77e88b: every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_condition
+• 0xb37c2d8d: no sensitive operation reachable
+• calldatas(uint256): no sensitive operation reachable — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• 0xf327de80: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG140" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=4578 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 2, "n_writes": 0}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "address[]", "n_reads": 4, "n_writes": 1}, {"slot": "000000000
+addresses embedded in the code: [{"bytecode_offset": 4548, "address": "0x3fb55b5d0427b1faa51c1d95117c2d1321e16473"}]</t>
+        </is>
+      </c>
+      <c r="AH140" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [957]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: calldatas(uint256)</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
@@ -18509,6 +26648,78 @@
       <c r="W141" s="9" t="inlineStr"/>
       <c r="X141" s="8" t="inlineStr"/>
       <c r="Y141" s="8" t="inlineStr"/>
+      <c r="Z141" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA141" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB141" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates:  The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC141" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD141" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE141" s="12" t="inlineStr">
+        <is>
+          <t>7997-byte runtime on bnb exposing 21 dispatched function(s): supportsInterface(bytes4), getMessageHash(bytes), onERC721Received(address,address,uint256,bytes), isValidSignature(bytes32,bytes), executeBatch(address[],bytes[]), validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256), executeBatch(address[],uint256[],bytes[]), addDeposit(), withdrawDepositTo(address,uint256), upgradeToAndCall(address,bytes) Embedded strings mention: EntryPoint, Signed Message.
+Protection(s) found: self-call restriction (msg.sender == address(this)) on execute(address,uint256,bytes), executeBatch(address[],bytes[]), executeBatch(address[],uint256[],bytes[]), transferOwnership(address), upgradeToAndCall(address,bytes), withdrawDepositTo(address,uint256) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent; signature-derived authorization branch (ecrecover) on isValidSignature(bytes32,bytes), validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256); caller restricted to a recognized ERC-4337 EntryPoint on execute(address,uint256,bytes), executeBatch(address[],bytes[]), executeBatch(address[],uint256[],bytes[]), transferOwnership(address), upgradeToAndCall(address,bytes), validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256); msg.sender compared against a stored authority on execute(address,uint256,bytes), executeBatch(address[],bytes[]), executeBatch(address[],uint256[],bytes[]), transferOwnership(address), upgradeToAndCall(address,bytes), withdrawDepositTo(address,uint256)
+Instruction census (whole contract): ADDRESS×11, CALL×5, CALLER×6, DELEGATECALL×1, SSTORE×6, STATICCALL×5</t>
+        </is>
+      </c>
+      <c r="AF141" s="12" t="inlineStr">
+        <is>
+          <t>• supportsInterface(bytes4): no sensitive operation reachable
+• getMessageHash(bytes): no sensitive operation reachable
+• onERC721Received(address,address,uint256,bytes): no sensitive operation reachable
+• isValidSignature(bytes32,bytes): no sensitive operation reachable — check found: storage_condition; storage_condition [analysis incomplete for this function]
+• executeBatch(address[],bytes[]): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032; self_call_check
+• validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032; storage_condition [analysis incomplete for this function]
+• executeBatch(address[],uint256[],bytes[]): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032; self_call_check
+• addDeposit(): an unauthenticated path to a sensitive operation exists
+• withdrawDepositTo(address,uint256): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032; self_call_check
+• upgradeToAndCall(address,bytes): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032; self_call_check
+• proxiableUUID(): no sensitive operation reachable
+• eip712Domain(): no sensitive operation reachable [analysis incomplete for this function]
+• owner(): no sensitive operation reachable
+• entryPoint(): no sensitive operation reachable
+• execute(address,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032; self_call_check
+• onERC1155BatchReceived(address,address,uint256[],uint256[],bytes): no sensitive operation reachable
+• getDeposit(): no sensitive operation reachable
+• initialize(address): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• getNonce(): no sensitive operation reachable
+• onERC1155Received(address,address,uint256,uint256,bytes): no sensitive operation reachable
+• transferOwnership(address): every path to a sensitive operation passes an authorization check — check found: storage_condition; hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032</t>
+        </is>
+      </c>
+      <c r="AG141" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=7997 bytes
+verified source=True
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "33e4b41198cc5b8053630ed667ea7c0c4c873f7fc8d9a478b5d7259cec0a4a00", "offset": 0, "type": "uint64", "n_reads": 0, "n_writes": 1}, {"slot": "33e4b41198cc5b8053630ed667ea7c0c4c873f7fc8d9a478b5d7259cec0a4a00", "offset": 8, "type": "bool", "n_reads": 1, "n_writes": 0}, {"slot": "360894a13ba1a32</t>
+        </is>
+      </c>
+      <c r="AH141" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: eip712Domain(), isValidSignature(bytes32,bytes), validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256); unauthenticated call(s) forwarding only msg.value to a fixed destination ([('addDeposit()', 3618, '0x0000000071727de22e5e9d8baf0edac6f37da032')]) — a caller can only donate their own ETH, so this is not by itself a path to the account's assets</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
@@ -18636,6 +26847,63 @@
       <c r="W142" s="6" t="inlineStr"/>
       <c r="X142" s="8" t="inlineStr"/>
       <c r="Y142" s="8" t="inlineStr"/>
+      <c r="Z142" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA142" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB142" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0xac9249b3: CALL at pc=688 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC142" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD142" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE142" s="12" t="inlineStr">
+        <is>
+          <t>3266-byte runtime on polygon exposing 4 dispatched function(s): 0x683fe68d, owner(), 0xac9249b3, 0xbeb744e4
+Concern(s) found: 0xac9249b3: CALL at pc=688 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 6, 'ADDRESS': 1, 'STATICCALL': 2, 'CALLCODE': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx6, CALLCODEx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): ADDRESS×1, CALL×6, CALLCODE×1, STATICCALL×2</t>
+        </is>
+      </c>
+      <c r="AF142" s="12" t="inlineStr">
+        <is>
+          <t>• 0x683fe68d: no sensitive operation reachable
+• owner(): no sensitive operation reachable
+• 0xac9249b3: an unauthenticated path to a sensitive operation exists
+• 0xbeb744e4: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 6 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG142" s="12" t="inlineStr">
+        <is>
+          <t>chain=polygon
+runtime size=3266 bytes
+verified source=False
+other chains with identical bytecode: ["polygon"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 2, "n_writes": 0}]
+addresses embedded in the code: [{"bytecode_offset": 474, "address": "0xa2829b28b6cf2f93c32403f722a60633624e8073"}]</t>
+        </is>
+      </c>
+      <c r="AH142" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [256, 537, 1030, 1442], 'CALLCODE': [3243]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
@@ -18763,6 +27031,58 @@
       <c r="W143" s="9" t="inlineStr"/>
       <c r="X143" s="8" t="inlineStr"/>
       <c r="Y143" s="8" t="inlineStr"/>
+      <c r="Z143" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA143" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB143" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: call(address,bytes): msg.sender must equal the hardcoded address 0x9ccc2f3ecde026230e11a5c8799ac7524f2bb294. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC143" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD143" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE143" s="12" t="inlineStr">
+        <is>
+          <t>1065-byte runtime on ethereum exposing 2 dispatched function(s): call(address,bytes), 0x52137255
+Concern(s) found: call(address,bytes): msg.sender must equal the hardcoded address 0x9ccc2f3ecde026230e11a5c8799ac7524f2bb294. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; call(address,bytes): msg.sender must equal the hardcoded address 0x9ccc2f3ecde026230e11a5c8799ac7524f2bb294. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×1, CALL×1, CALLER×3</t>
+        </is>
+      </c>
+      <c r="AF143" s="12" t="inlineStr">
+        <is>
+          <t>• call(address,bytes): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x9ccc2f3ecde026230e11a5c8799ac7524f2bb294; hardcoded_address_check against 0x9ccc2f3ecde026230e11a5c8799ac7524f2bb294
+• 0x52137255: no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG143" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=1065 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH143" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
@@ -18890,6 +27210,56 @@
       <c r="W144" s="6" t="inlineStr"/>
       <c r="X144" s="8" t="inlineStr"/>
       <c r="Y144" s="8" t="inlineStr"/>
+      <c r="Z144" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA144" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB144" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: every dispatched function analysed to completion with no reachable sensitive operation. The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC144" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD144" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE144" s="12" t="inlineStr">
+        <is>
+          <t>1725-byte runtime on bnb exposing 1 dispatched function(s): execute((bytes,address,uint256)[])
+Instruction census (whole contract): ADDRESS×1, CALL×1, CALLER×1</t>
+        </is>
+      </c>
+      <c r="AF144" s="12" t="inlineStr">
+        <is>
+          <t>• execute((bytes,address,uint256)[]): an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG144" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=1725 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]</t>
+        </is>
+      </c>
+      <c r="AH144" s="12" t="inlineStr">
+        <is>
+          <t>unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: execute((bytes,address,uint256)[]) pc=191 -&gt; unresolved (value=memory, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
@@ -19017,6 +27387,88 @@
       <c r="W145" s="9" t="inlineStr"/>
       <c r="X145" s="8" t="inlineStr"/>
       <c r="Y145" s="8" t="inlineStr"/>
+      <c r="Z145" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA145" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB145" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: executeFromExecutor(bytes32,bytes): msg.sender must equal the hardcoded address 0xdb9b1e94b5b69df7e401ddbede43491141047db3. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC145" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD145" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE145" s="12" t="inlineStr">
+        <is>
+          <t>11185-byte runtime on base exposing 29 dispatched function(s): supportsInterface(bytes4), 0x06394d67, onERC721Received(address,address,uint256,bytes), isValidSignature(bytes32,bytes), validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256), 0x2b3afd99, getNonce(uint192), 0x3ed01015, 0x445140b8, 0x49934047. Bytecode matches the documented project MetaMask_EIP7702StatelessDeleGator (VERIFIED_LEGITIMATE_CONTROL, provenance HIGH).
+Concern(s) found: executeFromExecutor(bytes32,bytes): msg.sender must equal the hardcoded address 0xdb9b1e94b5b69df7e401ddbede43491141047db3. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Protection(s) found: signature-derived authorization branch (ecrecover) on isValidSignature(bytes32,bytes), validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256); caller restricted to a recognized ERC-4337 EntryPoint on 0x3ed01015, 0x49934047, execute((address,uint256,bytes)), execute(bytes32,bytes), redeemDelegations(bytes[],bytes32[],bytes[]), validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256)
+Instruction census (whole contract): ADDRESS×21, CALL×6, CALLER×17, ORIGIN×1, STATICCALL×4</t>
+        </is>
+      </c>
+      <c r="AF145" s="12" t="inlineStr">
+        <is>
+          <t>• supportsInterface(bytes4): no sensitive operation reachable
+• 0x06394d67: no sensitive operation reachable
+• onERC721Received(address,address,uint256,bytes): no sensitive operation reachable
+• isValidSignature(bytes32,bytes): no sensitive operation reachable — check found: signature_authorization
+• validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032; signature_authorization
+• 0x2b3afd99: no sensitive operation reachable
+• getNonce(uint192): no sensitive operation reachable
+• 0x3ed01015: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032; hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032
+• 0x445140b8: no sensitive operation reachable
+• 0x49934047: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032; hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032
+• addDeposit(): an unauthenticated path to a sensitive operation exists
+• execute((address,uint256,bytes)): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032; hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032
+• withdrawDeposit(address,uint256): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032; hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032
+• getDomainHash(): no sensitive operation reachable
+• eip712Domain(): no sensitive operation reachable [analysis incomplete for this function]
+• NAME(): no sensitive operation reachable [analysis incomplete for this function]
+• DOMAIN_VERSION(): no sensitive operation reachable [analysis incomplete for this function]
+• entryPoint(): no sensitive operation reachable
+• onERC1155BatchReceived(address,address,uint256[],uint256[],bytes): no sensitive operation reachable
+• getDeposit(): no sensitive operation reachable
+• redeemDelegations(bytes[],bytes32[],bytes[]): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032; hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032 [analysis incomplete for this function]
+• supportsExecutionMode(bytes32): no sensitive operation reachable
+• getNonce(): no sensitive operation reachable
+• executeFromExecutor(bytes32,bytes): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xdb9b1e94b5b69df7e401ddbede43491141047db3 [analysis incomplete for this function]
+• execute(bytes32,bytes): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032; hardcoded_address_check against 0x0000000071727de22e5e9d8baf0edac6f37da032 [analysis incomplete for this function]
+• delegationManager(): no sensitive operation reachable
+• 0xed8101b5: no sensitive operation reachable
+• onERC1155Received(address,address,uint256,uint256,bytes): no sensitive operation reachable
+• VERSION(): no sensitive operation reachable [analysis incomplete for this function]</t>
+        </is>
+      </c>
+      <c r="AG145" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=11185 bytes
+verified source=True
+other chains with identical bytecode: ["base"]
+documented project: MetaMask_EIP7702StatelessDeleGator (VERIFIED_LEGITIMATE_CONTROL, provenance HIGH); docs: https://github.com/MetaMask/delegation-framework/blob/main/documents/Deployments.md
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "string", "n_reads": 1, "n_writes": 0}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "string", "n_reads": 1, "n_writes": 0}]</t>
+        </is>
+      </c>
+      <c r="AH145" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: DOMAIN_VERSION(), NAME(), VERSION(), eip712Domain(), execute(bytes32,bytes), executeFromExecutor(bytes32,bytes), redeemDelegations(bytes[],bytes32[],bytes[]); unauthenticated call(s) forwarding only msg.value to a fixed destination ([('addDeposit()', 2549, '0x0000000071727de22e5e9d8baf0edac6f37da032')]) — a caller can only donate their own ETH, so this is not by itself a path to the account's assets</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
@@ -19124,6 +27576,57 @@
       <c r="W146" s="6" t="inlineStr"/>
       <c r="X146" s="8" t="inlineStr"/>
       <c r="Y146" s="8" t="inlineStr"/>
+      <c r="Z146" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA146" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB146" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: no concrete unauthenticated dangerous path was demonstrated, and no positive authorization control was confirmed either. The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC146" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD146" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE146" s="12" t="inlineStr">
+        <is>
+          <t>166-byte runtime on ethereum exposing 0 dispatched function(s): &lt;no dispatcher recovered; analysed from pc=0&gt;
+Instruction census (whole contract): CALLER×3</t>
+        </is>
+      </c>
+      <c r="AF146" s="12" t="inlineStr">
+        <is>
+          <t>• &lt;no dispatcher recovered; analysed from pc=0&gt;: no sensitive operation reachable — check found: hardcoded_address_check against 0x145de1595d3c10168c7f1d22d026da85e50b718c; hardcoded_address_check against 0x145de1595d3c10168c7f1d22d026da85e50b718c</t>
+        </is>
+      </c>
+      <c r="AG146" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=166 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 10, "address": "0x145de1595d3c10168c7f1d22d026da85e50b718c"}]</t>
+        </is>
+      </c>
+      <c r="AH146" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
@@ -19251,6 +27754,68 @@
       <c r="W147" s="9" t="inlineStr"/>
       <c r="X147" s="8" t="inlineStr"/>
       <c r="Y147" s="8" t="inlineStr"/>
+      <c r="Z147" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA147" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB147" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: msg.sender compared against a stored authority on renounceOwnership(), transferOwnership(address) The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC147" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD147" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE147" s="12" t="inlineStr">
+        <is>
+          <t>3179-byte runtime on gnosis exposing 11 dispatched function(s): getCurrentBlockTimestamp(), getLastBlockHash(), getEthBalance(address), renounceOwnership(), getCurrentBlockDifficulty(), getCurrentBlockGasLimit(), owner(), getCurrentBlockCoinbase(), 0xb889afa4, getBlockHash(uint256)
+Protection(s) found: msg.sender compared against a stored authority on renounceOwnership(), transferOwnership(address)
+Instruction census (whole contract): CALL×1, CALLER×1, SSTORE×1</t>
+        </is>
+      </c>
+      <c r="AF147" s="12" t="inlineStr">
+        <is>
+          <t>• getCurrentBlockTimestamp(): no sensitive operation reachable
+• getLastBlockHash(): no sensitive operation reachable
+• getEthBalance(address): no sensitive operation reachable
+• renounceOwnership(): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check
+• getCurrentBlockDifficulty(): no sensitive operation reachable
+• getCurrentBlockGasLimit(): no sensitive operation reachable
+• owner(): no sensitive operation reachable
+• getCurrentBlockCoinbase(): no sensitive operation reachable
+• 0xb889afa4: an unauthenticated path to a sensitive operation exists
+• getBlockHash(uint256): no sensitive operation reachable
+• transferOwnership(address): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check</t>
+        </is>
+      </c>
+      <c r="AG147" s="12" t="inlineStr">
+        <is>
+          <t>chain=gnosis
+runtime size=3179 bytes
+verified source=False
+other chains with identical bytecode: ["gnosis"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 3, "n_writes": 2}]</t>
+        </is>
+      </c>
+      <c r="AH147" s="12" t="inlineStr">
+        <is>
+          <t>unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: 0xb889afa4 pc=883 -&gt; unresolved (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
@@ -19378,6 +27943,60 @@
       <c r="W148" s="6" t="inlineStr"/>
       <c r="X148" s="8" t="inlineStr"/>
       <c r="Y148" s="8" t="inlineStr"/>
+      <c r="Z148" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA148" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB148" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x5ee9acc7: CALL at pc=562 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC148" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD148" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE148" s="12" t="inlineStr">
+        <is>
+          <t>3545-byte runtime on arbitrum exposing 3 dispatched function(s): 0x5ee9acc7, multicall(address[],bytes[]), owner()
+Concern(s) found: 0x5ee9acc7: CALL at pc=562 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; multicall(address[],bytes[]): CALL at pc=915 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 2}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx2 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×2</t>
+        </is>
+      </c>
+      <c r="AF148" s="12" t="inlineStr">
+        <is>
+          <t>• 0x5ee9acc7: an unauthenticated path to a sensitive operation exists
+• multicall(address[],bytes[]): an unauthenticated path to a sensitive operation exists
+• owner(): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG148" s="12" t="inlineStr">
+        <is>
+          <t>chain=arbitrum
+runtime size=3545 bytes
+verified source=False
+other chains with identical bytecode: ["arbitrum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 1, "n_writes": 0}]</t>
+        </is>
+      </c>
+      <c r="AH148" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
@@ -19505,6 +28124,71 @@
       <c r="W149" s="9" t="inlineStr"/>
       <c r="X149" s="8" t="inlineStr"/>
       <c r="Y149" s="8" t="inlineStr"/>
+      <c r="Z149" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA149" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB149" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x0c0bf4c1: CALL at pc=565 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC149" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD149" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE149" s="12" t="inlineStr">
+        <is>
+          <t>6458-byte runtime on base exposing 11 dispatched function(s): 0x0c0bf4c1, addVault(address), 0x52312364, vaults(uint256), factoryAddress(), getVaultsCount(), _factory(), 0xc72896ac, removeVault(uint256), transferOwnership(address)
+Concern(s) found: 0x0c0bf4c1: CALL at pc=565 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call
+Protection(s) found: msg.sender compared against a stored authority on addVault(address), removeVault(uint256), transferOwnership(address)
+Instruction census (whole contract): CALL×7, CALLER×4, ORIGIN×3, SSTORE×6, STATICCALL×11</t>
+        </is>
+      </c>
+      <c r="AF149" s="12" t="inlineStr">
+        <is>
+          <t>• 0x0c0bf4c1: an unauthenticated path to a sensitive operation exists
+• addVault(address): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• 0x52312364: no sensitive operation reachable
+• vaults(uint256): no sensitive operation reachable — check found: storage_condition
+• factoryAddress(): no sensitive operation reachable
+• getVaultsCount(): no sensitive operation reachable
+• _factory(): no sensitive operation reachable
+• 0xc72896ac: an unauthenticated path to a sensitive operation exists
+• removeVault(uint256): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• transferOwnership(address): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• getVaultData(): no sensitive operation reachable — check found: storage_condition; storage_condition
+• COVERAGE GAP: the analysis never reached 3 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG149" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=6458 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 1, "n_writes": 0}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "address[]", "n_reads": 3, "n_writes": 2}, {"slot": "000000000
+addresses embedded in the code: [{"bytecode_offset": 1260, "address": "0x776236aead8a58ac9ec3cf214cda3c6335f46b2d"}, {"bytecode_offset": 1375, "address": "0xb556ee2761f5d2887b8f35a7dda367abd20503bf"}, {"bytecode_offset": 1490, "address": "0x042c37762d1d126bc61eac2f5ceb7a96318f5db9"}]</t>
+        </is>
+      </c>
+      <c r="AH149" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [994, 1089, 6417]}) — capability here is a lower bound; unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: 0xc72896ac pc=1354 -&gt; 0x776236aead8a58ac9ec3cf214cda3c6335f46b2d (value=0, data=memory); 0xc72896ac pc=1469 -&gt; 0xb556ee2761f5d2887b8f35a7dda367abd20503bf (value=0, data=memory); 0xc72896ac pc=1584 -&gt; 0x042c37762d1d126bc61eac2f5ceb7a96318f5db9 (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
@@ -19632,6 +28316,69 @@
       <c r="W150" s="6" t="inlineStr"/>
       <c r="X150" s="8" t="inlineStr"/>
       <c r="Y150" s="8" t="inlineStr"/>
+      <c r="Z150" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA150" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB150" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: self-call restriction (msg.sender == address(this)) on execute(bytes32,bytes), invalidateNonce(uint256) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC150" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD150" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE150" s="12" t="inlineStr">
+        <is>
+          <t>7314-byte runtime on ethereum exposing 12 dispatched function(s): supportsInterface(bytes4), onERC721Received(address,address,uint256,bytes), isValidSignature(bytes32,bytes), 0x4abb262a, isNonceUsed(uint256), eip712Domain(), isPaused(), invalidateNonce(uint256), onERC1155BatchReceived(address,address,uint256[],uint256[],bytes), supportsExecutionMode(bytes32)
+Protection(s) found: self-call restriction (msg.sender == address(this)) on execute(bytes32,bytes), invalidateNonce(uint256) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent; signature-derived authorization branch (ecrecover) on execute(bytes32,bytes), isValidSignature(bytes32,bytes)
+Instruction census (whole contract): ADDRESS×15, CALL×1, CALLER×4, SSTORE×1, STATICCALL×3</t>
+        </is>
+      </c>
+      <c r="AF150" s="12" t="inlineStr">
+        <is>
+          <t>• supportsInterface(bytes4): no sensitive operation reachable
+• onERC721Received(address,address,uint256,bytes): no sensitive operation reachable
+• isValidSignature(bytes32,bytes): no sensitive operation reachable — check found: signature_authorization
+• 0x4abb262a: no sensitive operation reachable
+• isNonceUsed(uint256): no sensitive operation reachable
+• eip712Domain(): no sensitive operation reachable [analysis incomplete for this function]
+• isPaused(): no sensitive operation reachable
+• invalidateNonce(uint256): every path to a sensitive operation passes an authorization check — check found: self_call_check; storage_condition
+• onERC1155BatchReceived(address,address,uint256[],uint256[],bytes): no sensitive operation reachable
+• supportsExecutionMode(bytes32): no sensitive operation reachable
+• execute(bytes32,bytes): an unauthenticated path to a sensitive operation exists — check found: self_call_check; storage_condition [analysis incomplete for this function]
+• onERC1155Received(address,address,uint256,uint256,bytes): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG150" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=7314 bytes
+verified source=True
+other chains with identical bytecode: ["ethereum"]
+on-chain storage read during evidence collection: [{"slot": "b035242b6a1b64fd1e2d869c03a3cc0e80fe7f55db29c2560bab38e489fab700", "offset": 0, "type": "mapping(uint248 =&gt; uint256)", "n_reads": 4, "n_writes": 2}]</t>
+        </is>
+      </c>
+      <c r="AH150" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: eip712Domain(), execute(bytes32,bytes)</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
@@ -19759,6 +28506,61 @@
       <c r="W151" s="9" t="inlineStr"/>
       <c r="X151" s="8" t="inlineStr"/>
       <c r="Y151" s="8" t="inlineStr"/>
+      <c r="Z151" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA151" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB151" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x46b1788d: tx.origin must equal the hardcoded address 0xecb6a178c32de18799c03f6f9229604a36d30e79. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC151" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD151" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE151" s="12" t="inlineStr">
+        <is>
+          <t>4146-byte runtime on polygon exposing 4 dispatched function(s): onERC721Received(address,address,uint256,bytes), 0x46b1788d, onERC1155BatchReceived(address,address,uint256[],uint256[],bytes), onERC1155Received(address,address,uint256,uint256,bytes) Embedded strings mention: Not owner.
+Concern(s) found: 0x46b1788d: tx.origin must equal the hardcoded address 0xecb6a178c32de18799c03f6f9229604a36d30e79. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×1, CALL×3, CALLER×1, ORIGIN×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF151" s="12" t="inlineStr">
+        <is>
+          <t>• onERC721Received(address,address,uint256,bytes): no sensitive operation reachable
+• 0x46b1788d: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xecb6a178c32de18799c03f6f9229604a36d30e79 [analysis incomplete for this function]
+• onERC1155BatchReceived(address,address,uint256[],uint256[],bytes): no sensitive operation reachable
+• onERC1155Received(address,address,uint256,uint256,bytes): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG151" s="12" t="inlineStr">
+        <is>
+          <t>chain=polygon
+runtime size=4146 bytes
+verified source=False
+other chains with identical bytecode: ["polygon"]</t>
+        </is>
+      </c>
+      <c r="AH151" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [879]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x46b1788d</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
